--- a/파프리카_병해충_방제정보_리스트.xlsx
+++ b/파프리카_병해충_방제정보_리스트.xlsx
@@ -1,15 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="방제정보 리스트" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="방제 정보 목록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분류 기준" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="목록_정보구분">'분류 기준'!$A$15:$A$26</definedName>
+    <definedName name="목록_방제분류">'분류 기준'!$B$15:$B$26</definedName>
+    <definedName name="목록_학교보유">'분류 기준'!$C$15:$C$26</definedName>
+    <definedName name="목록_혼용가능여부">'분류 기준'!$D$15:$D$26</definedName>
+    <definedName name="목록_제형">'분류 기준'!$E$15:$E$26</definedName>
+    <definedName name="목록_사용방법">'분류 기준'!$F$15:$F$26</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -22,7 +30,7 @@
     <numFmt numFmtId="166" formatCode="0&quot;회&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0&quot;원&quot;"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +48,17 @@
       <name val="맑은 고딕"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -54,7 +73,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -62,38 +81,114 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -103,7 +198,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="00FFF3B0"/>
+          <bgColor rgb="00FFF2CC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -187,8 +282,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="방제정보" displayName="방제정보" ref="A1:AM133" headerRowCount="1">
-  <autoFilter ref="A1:AM133"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="방제정보목록" displayName="방제정보목록" ref="A1:AM95" headerRowCount="1">
+  <autoFilter ref="A1:AM95"/>
   <tableColumns count="39">
     <tableColumn id="1" name="번호"/>
     <tableColumn id="2" name="정보 구분"/>
@@ -230,7 +325,7 @@
     <tableColumn id="38" name="출처"/>
     <tableColumn id="39" name="자료 조회일"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
 </file>
 
@@ -523,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM133"/>
+  <dimension ref="A1:AM95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -567,7 +662,7 @@
     <col width="12" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>번호</t>
@@ -764,7 +859,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1">
+    <row r="2" ht="49" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -840,7 +935,7 @@
       <c r="U2" s="3" t="n"/>
       <c r="V2" s="4" t="inlineStr">
         <is>
-          <t>1순위 추천(원문): 탄쟈비상  (Trifloxystrobin) [학교 미보유 - 구매 필요] 2000배 희석 · 경엽처리 · 안전사용기준: 수확3일전 / 3회</t>
+          <t>1순위 추천(원문): 탄쟈비상 (Trifloxystrobin) [학교 미보유 - 구매 필요] 2000배 희석 · 경엽처리 · 안전사용기준: 수확3일전 / 3회</t>
         </is>
       </c>
       <c r="W2" s="4" t="inlineStr">
@@ -856,9 +951,9 @@
       <c r="AC2" s="9" t="n"/>
       <c r="AD2" s="9" t="n"/>
       <c r="AE2" s="3" t="n"/>
-      <c r="AF2" s="3" t="n"/>
+      <c r="AF2" s="5" t="n"/>
       <c r="AG2" s="4" t="n"/>
-      <c r="AH2" s="3" t="n"/>
+      <c r="AH2" s="5" t="n"/>
       <c r="AI2" s="3" t="inlineStr">
         <is>
           <t>탄쟈비상 (액상수화제)</t>
@@ -877,7 +972,7 @@
       <c r="AL2" s="4" t="n"/>
       <c r="AM2" s="9" t="n"/>
     </row>
-    <row r="3" ht="48" customHeight="1">
+    <row r="3" ht="34" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -953,7 +1048,7 @@
       <c r="U3" s="3" t="n"/>
       <c r="V3" s="4" t="inlineStr">
         <is>
-          <t>1순위 추천(원문): 버픽스  (Florylpicoxamid) [학교 보유 중] 2000배 희석 · 경엽처리 · 안전사용기준: 수확3일전 / 3회</t>
+          <t>1순위 추천(원문): 버픽스 (Florylpicoxamid) [학교 보유 중] 2000배 희석 · 경엽처리 · 안전사용기준: 수확3일전 / 3회</t>
         </is>
       </c>
       <c r="W3" s="4" t="n"/>
@@ -965,9 +1060,9 @@
       <c r="AC3" s="9" t="n"/>
       <c r="AD3" s="9" t="n"/>
       <c r="AE3" s="3" t="n"/>
-      <c r="AF3" s="3" t="n"/>
+      <c r="AF3" s="5" t="n"/>
       <c r="AG3" s="4" t="n"/>
-      <c r="AH3" s="3" t="n"/>
+      <c r="AH3" s="5" t="n"/>
       <c r="AI3" s="3" t="inlineStr">
         <is>
           <t>버픽스(액상수화제)</t>
@@ -986,7 +1081,7 @@
       <c r="AL3" s="4" t="n"/>
       <c r="AM3" s="9" t="n"/>
     </row>
-    <row r="4" ht="33" customHeight="1">
+    <row r="4" ht="34" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -1070,9 +1165,9 @@
       <c r="AC4" s="9" t="n"/>
       <c r="AD4" s="9" t="n"/>
       <c r="AE4" s="3" t="n"/>
-      <c r="AF4" s="3" t="n"/>
+      <c r="AF4" s="5" t="n"/>
       <c r="AG4" s="4" t="n"/>
-      <c r="AH4" s="3" t="n"/>
+      <c r="AH4" s="5" t="n"/>
       <c r="AI4" s="3" t="inlineStr">
         <is>
           <t>벨리스플러스(입상수화제)</t>
@@ -1091,7 +1186,7 @@
       <c r="AL4" s="4" t="n"/>
       <c r="AM4" s="9" t="n"/>
     </row>
-    <row r="5" ht="33" customHeight="1">
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -1157,7 +1252,7 @@
       </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>갈색점무늬병, 잿빛곰팡이병, 탄저병, 역병, 차먼지 응애</t>
+          <t>갈색점무늬병, 잿빛곰팡이병, 탄저병, 역병, 차먼지응애</t>
         </is>
       </c>
       <c r="Q5" s="3" t="n"/>
@@ -1175,9 +1270,9 @@
       <c r="AC5" s="9" t="n"/>
       <c r="AD5" s="9" t="n"/>
       <c r="AE5" s="3" t="n"/>
-      <c r="AF5" s="3" t="n"/>
+      <c r="AF5" s="5" t="n"/>
       <c r="AG5" s="4" t="n"/>
-      <c r="AH5" s="3" t="n"/>
+      <c r="AH5" s="5" t="n"/>
       <c r="AI5" s="3" t="inlineStr">
         <is>
           <t>오조아 (수화제)</t>
@@ -1196,7 +1291,7 @@
       <c r="AL5" s="4" t="n"/>
       <c r="AM5" s="9" t="n"/>
     </row>
-    <row r="6" ht="33" customHeight="1">
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -1280,9 +1375,9 @@
       <c r="AC6" s="9" t="n"/>
       <c r="AD6" s="9" t="n"/>
       <c r="AE6" s="3" t="n"/>
-      <c r="AF6" s="3" t="n"/>
+      <c r="AF6" s="5" t="n"/>
       <c r="AG6" s="4" t="n"/>
-      <c r="AH6" s="3" t="n"/>
+      <c r="AH6" s="5" t="n"/>
       <c r="AI6" s="3" t="inlineStr">
         <is>
           <t>경탄 (액상수화제)</t>
@@ -1301,7 +1396,7 @@
       <c r="AL6" s="4" t="n"/>
       <c r="AM6" s="9" t="n"/>
     </row>
-    <row r="7" ht="48" customHeight="1">
+    <row r="7" ht="49" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -1377,7 +1472,7 @@
       <c r="U7" s="3" t="n"/>
       <c r="V7" s="4" t="inlineStr">
         <is>
-          <t>1순위 추천(원문): 스포르곤  (Prochloraz-manganese) [학교 미보유 - 구매 필요] 1000배 희석 · 관주처리 · 안전사용기준: 수확7일전 / 3회</t>
+          <t>1순위 추천(원문): 스포르곤 (Prochloraz-manganese) [학교 미보유 - 구매 필요] 1000배 희석 · 관주처리 · 안전사용기준: 수확7일전 / 3회</t>
         </is>
       </c>
       <c r="W7" s="4" t="n"/>
@@ -1389,9 +1484,9 @@
       <c r="AC7" s="9" t="n"/>
       <c r="AD7" s="9" t="n"/>
       <c r="AE7" s="3" t="n"/>
-      <c r="AF7" s="3" t="n"/>
+      <c r="AF7" s="5" t="n"/>
       <c r="AG7" s="4" t="n"/>
-      <c r="AH7" s="3" t="n"/>
+      <c r="AH7" s="5" t="n"/>
       <c r="AI7" s="3" t="inlineStr">
         <is>
           <t>스포르곤(수화제)</t>
@@ -1410,7 +1505,7 @@
       <c r="AL7" s="4" t="n"/>
       <c r="AM7" s="9" t="n"/>
     </row>
-    <row r="8" ht="33" customHeight="1">
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -1494,9 +1589,9 @@
       <c r="AC8" s="9" t="n"/>
       <c r="AD8" s="9" t="n"/>
       <c r="AE8" s="3" t="n"/>
-      <c r="AF8" s="3" t="n"/>
+      <c r="AF8" s="5" t="n"/>
       <c r="AG8" s="4" t="n"/>
-      <c r="AH8" s="3" t="n"/>
+      <c r="AH8" s="5" t="n"/>
       <c r="AI8" s="3" t="inlineStr">
         <is>
           <t>균디스(액상수화제)</t>
@@ -1515,7 +1610,7 @@
       <c r="AL8" s="4" t="n"/>
       <c r="AM8" s="9" t="n"/>
     </row>
-    <row r="9" ht="48" customHeight="1">
+    <row r="9" ht="49" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -1591,7 +1686,7 @@
       <c r="U9" s="3" t="n"/>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>1순위 추천(원문): 스포르곤  (Prochloraz-manganese) [학교 미보유 - 구매 필요] 1000배 희석 · 관주처리 · 안전사용기준: 수확7일전 / 3회</t>
+          <t>1순위 추천(원문): 스포르곤 (Prochloraz-manganese) [학교 미보유 - 구매 필요] 1000배 희석 · 관주처리 · 안전사용기준: 수확7일전 / 3회</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr">
@@ -1607,9 +1702,9 @@
       <c r="AC9" s="9" t="n"/>
       <c r="AD9" s="9" t="n"/>
       <c r="AE9" s="3" t="n"/>
-      <c r="AF9" s="3" t="n"/>
+      <c r="AF9" s="5" t="n"/>
       <c r="AG9" s="4" t="n"/>
-      <c r="AH9" s="3" t="n"/>
+      <c r="AH9" s="5" t="n"/>
       <c r="AI9" s="3" t="inlineStr">
         <is>
           <t>스포르곤(입제)</t>
@@ -1628,7 +1723,7 @@
       <c r="AL9" s="4" t="n"/>
       <c r="AM9" s="9" t="n"/>
     </row>
-    <row r="10" ht="48" customHeight="1">
+    <row r="10" ht="49" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -1704,7 +1799,7 @@
       <c r="U10" s="3" t="n"/>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>1순위 추천(원문): 무름반점뚝  (Oxolinic acid) [학교 보유 중] 1000배 희석 · 경엽처리 · 안전사용기준: 수확7일전 / 3회</t>
+          <t>1순위 추천(원문): 무름반점뚝 (Oxolinic acid) [학교 보유 중] 1000배 희석 · 경엽처리 · 안전사용기준: 수확7일전 / 3회</t>
         </is>
       </c>
       <c r="W10" s="4" t="n"/>
@@ -1716,9 +1811,9 @@
       <c r="AC10" s="9" t="n"/>
       <c r="AD10" s="9" t="n"/>
       <c r="AE10" s="3" t="n"/>
-      <c r="AF10" s="3" t="n"/>
+      <c r="AF10" s="5" t="n"/>
       <c r="AG10" s="4" t="n"/>
-      <c r="AH10" s="3" t="n"/>
+      <c r="AH10" s="5" t="n"/>
       <c r="AI10" s="3" t="inlineStr">
         <is>
           <t>무름반점뚝(수화제)</t>
@@ -1737,7 +1832,7 @@
       <c r="AL10" s="4" t="n"/>
       <c r="AM10" s="9" t="n"/>
     </row>
-    <row r="11" ht="33" customHeight="1">
+    <row r="11" ht="34" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -1821,9 +1916,9 @@
       <c r="AC11" s="9" t="n"/>
       <c r="AD11" s="9" t="n"/>
       <c r="AE11" s="3" t="n"/>
-      <c r="AF11" s="3" t="n"/>
+      <c r="AF11" s="5" t="n"/>
       <c r="AG11" s="4" t="n"/>
-      <c r="AH11" s="3" t="n"/>
+      <c r="AH11" s="5" t="n"/>
       <c r="AI11" s="3" t="inlineStr">
         <is>
           <t>미스타클린 수화제</t>
@@ -1842,7 +1937,7 @@
       <c r="AL11" s="4" t="n"/>
       <c r="AM11" s="9" t="n"/>
     </row>
-    <row r="12" ht="33" customHeight="1">
+    <row r="12" ht="34" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -1926,9 +2021,9 @@
       <c r="AC12" s="9" t="n"/>
       <c r="AD12" s="9" t="n"/>
       <c r="AE12" s="3" t="n"/>
-      <c r="AF12" s="3" t="n"/>
+      <c r="AF12" s="5" t="n"/>
       <c r="AG12" s="4" t="n"/>
-      <c r="AH12" s="3" t="n"/>
+      <c r="AH12" s="5" t="n"/>
       <c r="AI12" s="3" t="inlineStr">
         <is>
           <t>가스란(수화제)</t>
@@ -1947,7 +2042,7 @@
       <c r="AL12" s="4" t="n"/>
       <c r="AM12" s="9" t="n"/>
     </row>
-    <row r="13" ht="33" customHeight="1">
+    <row r="13" ht="34" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -2031,9 +2126,9 @@
       <c r="AC13" s="9" t="n"/>
       <c r="AD13" s="9" t="n"/>
       <c r="AE13" s="3" t="n"/>
-      <c r="AF13" s="3" t="n"/>
+      <c r="AF13" s="5" t="n"/>
       <c r="AG13" s="4" t="n"/>
-      <c r="AH13" s="3" t="n"/>
+      <c r="AH13" s="5" t="n"/>
       <c r="AI13" s="3" t="inlineStr">
         <is>
           <t>골든벨(액상수화제)</t>
@@ -2052,7 +2147,7 @@
       <c r="AL13" s="4" t="n"/>
       <c r="AM13" s="9" t="n"/>
     </row>
-    <row r="14" ht="48" customHeight="1">
+    <row r="14" ht="34" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -2128,7 +2223,7 @@
       <c r="U14" s="3" t="n"/>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>1순위 추천(원문): 버픽스  (Florylpicoxamid) [학교 보유 중] 2000배 희석 · 경엽처리 · 안전사용기준: 수확3일전 / 3회</t>
+          <t>1순위 추천(원문): 버픽스 (Florylpicoxamid) [학교 보유 중] 2000배 희석 · 경엽처리 · 안전사용기준: 수확3일전 / 3회</t>
         </is>
       </c>
       <c r="W14" s="4" t="n"/>
@@ -2140,9 +2235,9 @@
       <c r="AC14" s="9" t="n"/>
       <c r="AD14" s="9" t="n"/>
       <c r="AE14" s="3" t="n"/>
-      <c r="AF14" s="3" t="n"/>
+      <c r="AF14" s="5" t="n"/>
       <c r="AG14" s="4" t="n"/>
-      <c r="AH14" s="3" t="n"/>
+      <c r="AH14" s="5" t="n"/>
       <c r="AI14" s="3" t="inlineStr">
         <is>
           <t>버픽스 (액상수화제)</t>
@@ -2161,7 +2256,7 @@
       <c r="AL14" s="4" t="n"/>
       <c r="AM14" s="9" t="n"/>
     </row>
-    <row r="15" ht="33" customHeight="1">
+    <row r="15" ht="34" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -2245,9 +2340,9 @@
       <c r="AC15" s="9" t="n"/>
       <c r="AD15" s="9" t="n"/>
       <c r="AE15" s="3" t="n"/>
-      <c r="AF15" s="3" t="n"/>
+      <c r="AF15" s="5" t="n"/>
       <c r="AG15" s="4" t="n"/>
-      <c r="AH15" s="3" t="n"/>
+      <c r="AH15" s="5" t="n"/>
       <c r="AI15" s="3" t="inlineStr">
         <is>
           <t>미래빛 (액상수화제)</t>
@@ -2266,7 +2361,7 @@
       <c r="AL15" s="4" t="n"/>
       <c r="AM15" s="9" t="n"/>
     </row>
-    <row r="16" ht="33" customHeight="1">
+    <row r="16" ht="34" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -2350,9 +2445,9 @@
       <c r="AC16" s="9" t="n"/>
       <c r="AD16" s="9" t="n"/>
       <c r="AE16" s="3" t="n"/>
-      <c r="AF16" s="3" t="n"/>
+      <c r="AF16" s="5" t="n"/>
       <c r="AG16" s="4" t="n"/>
-      <c r="AH16" s="3" t="n"/>
+      <c r="AH16" s="5" t="n"/>
       <c r="AI16" s="3" t="inlineStr">
         <is>
           <t>사파이어 (액상수화제)</t>
@@ -2371,7 +2466,7 @@
       <c r="AL16" s="4" t="n"/>
       <c r="AM16" s="9" t="n"/>
     </row>
-    <row r="17" ht="33" customHeight="1">
+    <row r="17" ht="34" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -2455,9 +2550,9 @@
       <c r="AC17" s="9" t="n"/>
       <c r="AD17" s="9" t="n"/>
       <c r="AE17" s="3" t="n"/>
-      <c r="AF17" s="3" t="n"/>
+      <c r="AF17" s="5" t="n"/>
       <c r="AG17" s="4" t="n"/>
-      <c r="AH17" s="3" t="n"/>
+      <c r="AH17" s="5" t="n"/>
       <c r="AI17" s="3" t="inlineStr">
         <is>
           <t>오조아 (수화제)</t>
@@ -2476,7 +2571,7 @@
       <c r="AL17" s="4" t="n"/>
       <c r="AM17" s="9" t="n"/>
     </row>
-    <row r="18" ht="48" customHeight="1">
+    <row r="18" ht="49" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -2552,7 +2647,7 @@
       <c r="U18" s="3" t="n"/>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>1순위 추천(원문): 벨리스플러스  (Boscalid+Pyraclostrobin) [학교 보유 중] 2000배 희석 · 경엽처리 · 안전사용기준: 수확5일전 / 2회</t>
+          <t>1순위 추천(원문): 벨리스플러스 (Boscalid+Pyraclostrobin) [학교 보유 중] 2000배 희석 · 경엽처리 · 안전사용기준: 수확5일전 / 2회</t>
         </is>
       </c>
       <c r="W18" s="4" t="n"/>
@@ -2564,9 +2659,9 @@
       <c r="AC18" s="9" t="n"/>
       <c r="AD18" s="9" t="n"/>
       <c r="AE18" s="3" t="n"/>
-      <c r="AF18" s="3" t="n"/>
+      <c r="AF18" s="5" t="n"/>
       <c r="AG18" s="4" t="n"/>
-      <c r="AH18" s="3" t="n"/>
+      <c r="AH18" s="5" t="n"/>
       <c r="AI18" s="3" t="inlineStr">
         <is>
           <t>벨리스플러스(입상수화제)</t>
@@ -2585,7 +2680,7 @@
       <c r="AL18" s="4" t="n"/>
       <c r="AM18" s="9" t="n"/>
     </row>
-    <row r="19" ht="33" customHeight="1">
+    <row r="19" ht="34" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -2657,9 +2752,9 @@
       <c r="AC19" s="9" t="n"/>
       <c r="AD19" s="9" t="n"/>
       <c r="AE19" s="3" t="n"/>
-      <c r="AF19" s="3" t="n"/>
+      <c r="AF19" s="5" t="n"/>
       <c r="AG19" s="4" t="n"/>
-      <c r="AH19" s="3" t="n"/>
+      <c r="AH19" s="5" t="n"/>
       <c r="AI19" s="3" t="inlineStr">
         <is>
           <t>다놀라 (액상)</t>
@@ -2678,7 +2773,7 @@
       <c r="AL19" s="4" t="n"/>
       <c r="AM19" s="9" t="n"/>
     </row>
-    <row r="20" ht="33" customHeight="1">
+    <row r="20" ht="34" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
@@ -2746,9 +2841,9 @@
       <c r="AC20" s="9" t="n"/>
       <c r="AD20" s="9" t="n"/>
       <c r="AE20" s="3" t="n"/>
-      <c r="AF20" s="3" t="n"/>
+      <c r="AF20" s="5" t="n"/>
       <c r="AG20" s="4" t="n"/>
-      <c r="AH20" s="3" t="n"/>
+      <c r="AH20" s="5" t="n"/>
       <c r="AI20" s="3" t="inlineStr">
         <is>
           <t>미리본</t>
@@ -2767,7 +2862,7 @@
       <c r="AL20" s="4" t="n"/>
       <c r="AM20" s="9" t="n"/>
     </row>
-    <row r="21" ht="33" customHeight="1">
+    <row r="21" ht="34" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
@@ -2839,9 +2934,9 @@
       <c r="AC21" s="9" t="n"/>
       <c r="AD21" s="9" t="n"/>
       <c r="AE21" s="3" t="n"/>
-      <c r="AF21" s="3" t="n"/>
+      <c r="AF21" s="5" t="n"/>
       <c r="AG21" s="4" t="n"/>
-      <c r="AH21" s="3" t="n"/>
+      <c r="AH21" s="5" t="n"/>
       <c r="AI21" s="3" t="inlineStr">
         <is>
           <t>벨쿠트(수화제)</t>
@@ -2860,7 +2955,7 @@
       <c r="AL21" s="4" t="n"/>
       <c r="AM21" s="9" t="n"/>
     </row>
-    <row r="22" ht="33" customHeight="1">
+    <row r="22" ht="34" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
@@ -2934,7 +3029,7 @@
       <c r="U22" s="3" t="n"/>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>1순위 추천(원문): 크린쏘일  (Metam-sodium) [학교 미보유 - 구매 필요]  관주처리 · 안전사용기준: 정식4주전 / 1회</t>
+          <t>1순위 추천(원문): 크린쏘일 (Metam-sodium) [학교 미보유 - 구매 필요]  관주처리 · 안전사용기준: 정식4주전 / 1회</t>
         </is>
       </c>
       <c r="W22" s="4" t="n"/>
@@ -2946,9 +3041,9 @@
       <c r="AC22" s="9" t="n"/>
       <c r="AD22" s="9" t="n"/>
       <c r="AE22" s="3" t="n"/>
-      <c r="AF22" s="3" t="n"/>
+      <c r="AF22" s="5" t="n"/>
       <c r="AG22" s="4" t="n"/>
-      <c r="AH22" s="3" t="n"/>
+      <c r="AH22" s="5" t="n"/>
       <c r="AI22" s="3" t="inlineStr">
         <is>
           <t>크린쏘일 (입제)</t>
@@ -2967,7 +3062,7 @@
       <c r="AL22" s="4" t="n"/>
       <c r="AM22" s="9" t="n"/>
     </row>
-    <row r="23" ht="33" customHeight="1">
+    <row r="23" ht="34" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
@@ -3041,7 +3136,7 @@
       <c r="U23" s="3" t="n"/>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>1순위 추천(원문): 쏘버린  (Carbosulfan) [학교 미보유 - 구매 필요] 토양처리 · 안전사용기준: 정식기 / 1회</t>
+          <t>1순위 추천(원문): 쏘버린 (Carbosulfan) [학교 미보유 - 구매 필요] 토양처리 · 안전사용기준: 정식기 / 1회</t>
         </is>
       </c>
       <c r="W23" s="4" t="n"/>
@@ -3053,9 +3148,9 @@
       <c r="AC23" s="9" t="n"/>
       <c r="AD23" s="9" t="n"/>
       <c r="AE23" s="3" t="n"/>
-      <c r="AF23" s="3" t="n"/>
+      <c r="AF23" s="5" t="n"/>
       <c r="AG23" s="4" t="n"/>
-      <c r="AH23" s="3" t="n"/>
+      <c r="AH23" s="5" t="n"/>
       <c r="AI23" s="3" t="inlineStr">
         <is>
           <t>쏘버린 (입제)</t>
@@ -3074,7 +3169,7 @@
       <c r="AL23" s="4" t="n"/>
       <c r="AM23" s="9" t="n"/>
     </row>
-    <row r="24" ht="33" customHeight="1">
+    <row r="24" ht="34" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
@@ -3156,9 +3251,9 @@
       <c r="AC24" s="9" t="n"/>
       <c r="AD24" s="9" t="n"/>
       <c r="AE24" s="3" t="n"/>
-      <c r="AF24" s="3" t="n"/>
+      <c r="AF24" s="5" t="n"/>
       <c r="AG24" s="4" t="n"/>
-      <c r="AH24" s="3" t="n"/>
+      <c r="AH24" s="5" t="n"/>
       <c r="AI24" s="3" t="inlineStr">
         <is>
           <t>보라충 (입제)</t>
@@ -3177,7 +3272,7 @@
       <c r="AL24" s="4" t="n"/>
       <c r="AM24" s="9" t="n"/>
     </row>
-    <row r="25" ht="33" customHeight="1">
+    <row r="25" ht="34" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
@@ -3259,9 +3354,9 @@
       <c r="AC25" s="9" t="n"/>
       <c r="AD25" s="9" t="n"/>
       <c r="AE25" s="3" t="n"/>
-      <c r="AF25" s="3" t="n"/>
+      <c r="AF25" s="5" t="n"/>
       <c r="AG25" s="4" t="n"/>
-      <c r="AH25" s="3" t="n"/>
+      <c r="AH25" s="5" t="n"/>
       <c r="AI25" s="3" t="inlineStr">
         <is>
           <t>싸이포스 (입제)</t>
@@ -3280,7 +3375,7 @@
       <c r="AL25" s="4" t="n"/>
       <c r="AM25" s="9" t="n"/>
     </row>
-    <row r="26" ht="48" customHeight="1">
+    <row r="26" ht="49" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
@@ -3356,7 +3451,7 @@
       <c r="U26" s="3" t="n"/>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t>1순위 추천(원문): 모스피란  (아세타미프리드 (Acetamiprid)) [학교 보유 중] 2000배 희석 · 경엽처리 · 안전사용기준: 수확5일전 / 3회</t>
+          <t>1순위 추천(원문): 모스피란 (아세타미프리드 (Acetamiprid)) [학교 보유 중] 2000배 희석 · 경엽처리 · 안전사용기준: 수확5일전 / 3회</t>
         </is>
       </c>
       <c r="W26" s="4" t="n"/>
@@ -3368,9 +3463,9 @@
       <c r="AC26" s="9" t="n"/>
       <c r="AD26" s="9" t="n"/>
       <c r="AE26" s="3" t="n"/>
-      <c r="AF26" s="3" t="n"/>
+      <c r="AF26" s="5" t="n"/>
       <c r="AG26" s="4" t="n"/>
-      <c r="AH26" s="3" t="n"/>
+      <c r="AH26" s="5" t="n"/>
       <c r="AI26" s="3" t="inlineStr">
         <is>
           <t>모스피란 (수화제)</t>
@@ -3389,7 +3484,7 @@
       <c r="AL26" s="4" t="n"/>
       <c r="AM26" s="9" t="n"/>
     </row>
-    <row r="27" ht="33" customHeight="1">
+    <row r="27" ht="34" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
@@ -3473,9 +3568,9 @@
       <c r="AC27" s="9" t="n"/>
       <c r="AD27" s="9" t="n"/>
       <c r="AE27" s="3" t="n"/>
-      <c r="AF27" s="3" t="n"/>
+      <c r="AF27" s="5" t="n"/>
       <c r="AG27" s="4" t="n"/>
-      <c r="AH27" s="3" t="n"/>
+      <c r="AH27" s="5" t="n"/>
       <c r="AI27" s="3" t="inlineStr">
         <is>
           <t>동작그만 (유제)</t>
@@ -3494,7 +3589,7 @@
       <c r="AL27" s="4" t="n"/>
       <c r="AM27" s="9" t="n"/>
     </row>
-    <row r="28" ht="33" customHeight="1">
+    <row r="28" ht="34" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
@@ -3578,9 +3673,9 @@
       <c r="AC28" s="9" t="n"/>
       <c r="AD28" s="9" t="n"/>
       <c r="AE28" s="3" t="n"/>
-      <c r="AF28" s="3" t="n"/>
+      <c r="AF28" s="5" t="n"/>
       <c r="AG28" s="4" t="n"/>
-      <c r="AH28" s="3" t="n"/>
+      <c r="AH28" s="5" t="n"/>
       <c r="AI28" s="3" t="inlineStr">
         <is>
           <t>델리게이트 (입상수화제)</t>
@@ -3599,7 +3694,7 @@
       <c r="AL28" s="4" t="n"/>
       <c r="AM28" s="9" t="n"/>
     </row>
-    <row r="29" ht="33" customHeight="1">
+    <row r="29" ht="34" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
@@ -3671,9 +3766,9 @@
       <c r="AC29" s="9" t="n"/>
       <c r="AD29" s="9" t="n"/>
       <c r="AE29" s="3" t="n"/>
-      <c r="AF29" s="3" t="n"/>
+      <c r="AF29" s="5" t="n"/>
       <c r="AG29" s="4" t="n"/>
-      <c r="AH29" s="3" t="n"/>
+      <c r="AH29" s="5" t="n"/>
       <c r="AI29" s="3" t="inlineStr">
         <is>
           <t>뉴증원군 (유제)</t>
@@ -3692,7 +3787,7 @@
       <c r="AL29" s="4" t="n"/>
       <c r="AM29" s="9" t="n"/>
     </row>
-    <row r="30" ht="48" customHeight="1">
+    <row r="30" ht="49" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
@@ -3768,7 +3863,7 @@
       <c r="U30" s="3" t="n"/>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>1순위 추천(원문): 모스피란  (아세타미프리드 (Acetamiprid)) [학교 보유 중] 2000배 희석 · 경엽처리 · 안전사용기준: 수확5일전 / 3회</t>
+          <t>1순위 추천(원문): 모스피란 (아세타미프리드 (Acetamiprid)) [학교 보유 중] 2000배 희석 · 경엽처리 · 안전사용기준: 수확5일전 / 3회</t>
         </is>
       </c>
       <c r="W30" s="4" t="n"/>
@@ -3780,9 +3875,9 @@
       <c r="AC30" s="9" t="n"/>
       <c r="AD30" s="9" t="n"/>
       <c r="AE30" s="3" t="n"/>
-      <c r="AF30" s="3" t="n"/>
+      <c r="AF30" s="5" t="n"/>
       <c r="AG30" s="4" t="n"/>
-      <c r="AH30" s="3" t="n"/>
+      <c r="AH30" s="5" t="n"/>
       <c r="AI30" s="3" t="inlineStr">
         <is>
           <t>모스피란 (수화제)</t>
@@ -3801,7 +3896,7 @@
       <c r="AL30" s="4" t="n"/>
       <c r="AM30" s="9" t="n"/>
     </row>
-    <row r="31" ht="33" customHeight="1">
+    <row r="31" ht="34" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
@@ -3885,9 +3980,9 @@
       <c r="AC31" s="9" t="n"/>
       <c r="AD31" s="9" t="n"/>
       <c r="AE31" s="3" t="n"/>
-      <c r="AF31" s="3" t="n"/>
+      <c r="AF31" s="5" t="n"/>
       <c r="AG31" s="4" t="n"/>
-      <c r="AH31" s="3" t="n"/>
+      <c r="AH31" s="5" t="n"/>
       <c r="AI31" s="3" t="inlineStr">
         <is>
           <t>동작그만 (유제)</t>
@@ -3906,7 +4001,7 @@
       <c r="AL31" s="4" t="n"/>
       <c r="AM31" s="9" t="n"/>
     </row>
-    <row r="32" ht="33" customHeight="1">
+    <row r="32" ht="34" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
@@ -3990,9 +4085,9 @@
       <c r="AC32" s="9" t="n"/>
       <c r="AD32" s="9" t="n"/>
       <c r="AE32" s="3" t="n"/>
-      <c r="AF32" s="3" t="n"/>
+      <c r="AF32" s="5" t="n"/>
       <c r="AG32" s="4" t="n"/>
-      <c r="AH32" s="3" t="n"/>
+      <c r="AH32" s="5" t="n"/>
       <c r="AI32" s="3" t="inlineStr">
         <is>
           <t>디져스 (유제)</t>
@@ -4011,7 +4106,7 @@
       <c r="AL32" s="4" t="n"/>
       <c r="AM32" s="9" t="n"/>
     </row>
-    <row r="33" ht="33" customHeight="1">
+    <row r="33" ht="34" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
@@ -4095,9 +4190,9 @@
       <c r="AC33" s="9" t="n"/>
       <c r="AD33" s="9" t="n"/>
       <c r="AE33" s="3" t="n"/>
-      <c r="AF33" s="3" t="n"/>
+      <c r="AF33" s="5" t="n"/>
       <c r="AG33" s="4" t="n"/>
-      <c r="AH33" s="3" t="n"/>
+      <c r="AH33" s="5" t="n"/>
       <c r="AI33" s="3" t="inlineStr">
         <is>
           <t>강철비 (액상수화제)</t>
@@ -4116,7 +4211,7 @@
       <c r="AL33" s="4" t="n"/>
       <c r="AM33" s="9" t="n"/>
     </row>
-    <row r="34" ht="48" customHeight="1">
+    <row r="34" ht="49" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
@@ -4192,7 +4287,7 @@
       <c r="U34" s="3" t="n"/>
       <c r="V34" s="4" t="inlineStr">
         <is>
-          <t>1순위 추천(원문): 모스피란  (아세타미프리드 (Acetamiprid)) [학교 보유 중] 2000배 희석 · 경엽처리 · 안전사용기준: 수확5일전 / 3회</t>
+          <t>1순위 추천(원문): 모스피란 (아세타미프리드 (Acetamiprid)) [학교 보유 중] 2000배 희석 · 경엽처리 · 안전사용기준: 수확5일전 / 3회</t>
         </is>
       </c>
       <c r="W34" s="4" t="n"/>
@@ -4204,9 +4299,9 @@
       <c r="AC34" s="9" t="n"/>
       <c r="AD34" s="9" t="n"/>
       <c r="AE34" s="3" t="n"/>
-      <c r="AF34" s="3" t="n"/>
+      <c r="AF34" s="5" t="n"/>
       <c r="AG34" s="4" t="n"/>
-      <c r="AH34" s="3" t="n"/>
+      <c r="AH34" s="5" t="n"/>
       <c r="AI34" s="3" t="inlineStr">
         <is>
           <t>모스피란 (수화제)</t>
@@ -4225,7 +4320,7 @@
       <c r="AL34" s="4" t="n"/>
       <c r="AM34" s="9" t="n"/>
     </row>
-    <row r="35" ht="33" customHeight="1">
+    <row r="35" ht="34" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
@@ -4309,9 +4404,9 @@
       <c r="AC35" s="9" t="n"/>
       <c r="AD35" s="9" t="n"/>
       <c r="AE35" s="3" t="n"/>
-      <c r="AF35" s="3" t="n"/>
+      <c r="AF35" s="5" t="n"/>
       <c r="AG35" s="4" t="n"/>
-      <c r="AH35" s="3" t="n"/>
+      <c r="AH35" s="5" t="n"/>
       <c r="AI35" s="3" t="inlineStr">
         <is>
           <t>동작그만 (유제)</t>
@@ -4330,7 +4425,7 @@
       <c r="AL35" s="4" t="n"/>
       <c r="AM35" s="9" t="n"/>
     </row>
-    <row r="36" ht="33" customHeight="1">
+    <row r="36" ht="34" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
@@ -4414,9 +4509,9 @@
       <c r="AC36" s="9" t="n"/>
       <c r="AD36" s="9" t="n"/>
       <c r="AE36" s="3" t="n"/>
-      <c r="AF36" s="3" t="n"/>
+      <c r="AF36" s="5" t="n"/>
       <c r="AG36" s="4" t="n"/>
-      <c r="AH36" s="3" t="n"/>
+      <c r="AH36" s="5" t="n"/>
       <c r="AI36" s="3" t="inlineStr">
         <is>
           <t>디져스 (유제)</t>
@@ -4435,7 +4530,7 @@
       <c r="AL36" s="4" t="n"/>
       <c r="AM36" s="9" t="n"/>
     </row>
-    <row r="37" ht="33" customHeight="1">
+    <row r="37" ht="34" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
@@ -4519,9 +4614,9 @@
       <c r="AC37" s="9" t="n"/>
       <c r="AD37" s="9" t="n"/>
       <c r="AE37" s="3" t="n"/>
-      <c r="AF37" s="3" t="n"/>
+      <c r="AF37" s="5" t="n"/>
       <c r="AG37" s="4" t="n"/>
-      <c r="AH37" s="3" t="n"/>
+      <c r="AH37" s="5" t="n"/>
       <c r="AI37" s="3" t="inlineStr">
         <is>
           <t>산마루 (수화제)</t>
@@ -4540,7 +4635,7 @@
       <c r="AL37" s="4" t="n"/>
       <c r="AM37" s="9" t="n"/>
     </row>
-    <row r="38" ht="48" customHeight="1">
+    <row r="38" ht="49" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
@@ -4616,7 +4711,7 @@
       <c r="U38" s="3" t="n"/>
       <c r="V38" s="4" t="inlineStr">
         <is>
-          <t>1순위 추천(원문): 모스피란  (아세타미프리드 (Acetamiprid)) [학교 보유 중] 2000배 희석 · 경엽처리 · 안전사용기준: 수확5일전 / 3회</t>
+          <t>1순위 추천(원문): 모스피란 (아세타미프리드 (Acetamiprid)) [학교 보유 중] 2000배 희석 · 경엽처리 · 안전사용기준: 수확5일전 / 3회</t>
         </is>
       </c>
       <c r="W38" s="4" t="n"/>
@@ -4628,9 +4723,9 @@
       <c r="AC38" s="9" t="n"/>
       <c r="AD38" s="9" t="n"/>
       <c r="AE38" s="3" t="n"/>
-      <c r="AF38" s="3" t="n"/>
+      <c r="AF38" s="5" t="n"/>
       <c r="AG38" s="4" t="n"/>
-      <c r="AH38" s="3" t="n"/>
+      <c r="AH38" s="5" t="n"/>
       <c r="AI38" s="3" t="inlineStr">
         <is>
           <t>모스피란 (수화제)</t>
@@ -4649,7 +4744,7 @@
       <c r="AL38" s="4" t="n"/>
       <c r="AM38" s="9" t="n"/>
     </row>
-    <row r="39" ht="33" customHeight="1">
+    <row r="39" ht="34" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
@@ -4733,9 +4828,9 @@
       <c r="AC39" s="9" t="n"/>
       <c r="AD39" s="9" t="n"/>
       <c r="AE39" s="3" t="n"/>
-      <c r="AF39" s="3" t="n"/>
+      <c r="AF39" s="5" t="n"/>
       <c r="AG39" s="4" t="n"/>
-      <c r="AH39" s="3" t="n"/>
+      <c r="AH39" s="5" t="n"/>
       <c r="AI39" s="3" t="inlineStr">
         <is>
           <t>디져스 (유제)</t>
@@ -4754,7 +4849,7 @@
       <c r="AL39" s="4" t="n"/>
       <c r="AM39" s="9" t="n"/>
     </row>
-    <row r="40" ht="33" customHeight="1">
+    <row r="40" ht="34" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
@@ -4838,9 +4933,9 @@
       <c r="AC40" s="9" t="n"/>
       <c r="AD40" s="9" t="n"/>
       <c r="AE40" s="3" t="n"/>
-      <c r="AF40" s="3" t="n"/>
+      <c r="AF40" s="5" t="n"/>
       <c r="AG40" s="4" t="n"/>
-      <c r="AH40" s="3" t="n"/>
+      <c r="AH40" s="5" t="n"/>
       <c r="AI40" s="3" t="inlineStr">
         <is>
           <t>기대찬 (입상수화제)</t>
@@ -4859,7 +4954,7 @@
       <c r="AL40" s="4" t="n"/>
       <c r="AM40" s="9" t="n"/>
     </row>
-    <row r="41" ht="33" customHeight="1">
+    <row r="41" ht="34" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
@@ -4939,9 +5034,9 @@
       <c r="AC41" s="9" t="n"/>
       <c r="AD41" s="9" t="n"/>
       <c r="AE41" s="3" t="n"/>
-      <c r="AF41" s="3" t="n"/>
+      <c r="AF41" s="5" t="n"/>
       <c r="AG41" s="4" t="n"/>
-      <c r="AH41" s="3" t="n"/>
+      <c r="AH41" s="5" t="n"/>
       <c r="AI41" s="3" t="inlineStr">
         <is>
           <t>세티스</t>
@@ -4960,7 +5055,7 @@
       <c r="AL41" s="4" t="n"/>
       <c r="AM41" s="9" t="n"/>
     </row>
-    <row r="42" ht="48" customHeight="1">
+    <row r="42" ht="49" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
@@ -5036,7 +5131,7 @@
       <c r="U42" s="3" t="n"/>
       <c r="V42" s="4" t="inlineStr">
         <is>
-          <t>1순위 추천(원문): 코니도  (Imidacloprid) [학교 미보유 - 구매 필요] 2000배 희석 · 경엽처리 · 안전사용기준: 수확5일전 / 3회</t>
+          <t>1순위 추천(원문): 코니도 (Imidacloprid) [학교 미보유 - 구매 필요] 2000배 희석 · 경엽처리 · 안전사용기준: 수확5일전 / 3회</t>
         </is>
       </c>
       <c r="W42" s="4" t="n"/>
@@ -5048,9 +5143,9 @@
       <c r="AC42" s="9" t="n"/>
       <c r="AD42" s="9" t="n"/>
       <c r="AE42" s="3" t="n"/>
-      <c r="AF42" s="3" t="n"/>
+      <c r="AF42" s="5" t="n"/>
       <c r="AG42" s="4" t="n"/>
-      <c r="AH42" s="3" t="n"/>
+      <c r="AH42" s="5" t="n"/>
       <c r="AI42" s="3" t="inlineStr">
         <is>
           <t>코니도 (수화제)</t>
@@ -5069,7 +5164,7 @@
       <c r="AL42" s="4" t="n"/>
       <c r="AM42" s="9" t="n"/>
     </row>
-    <row r="43" ht="48" customHeight="1">
+    <row r="43" ht="49" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
@@ -5157,9 +5252,9 @@
       <c r="AC43" s="9" t="n"/>
       <c r="AD43" s="9" t="n"/>
       <c r="AE43" s="3" t="n"/>
-      <c r="AF43" s="3" t="n"/>
+      <c r="AF43" s="5" t="n"/>
       <c r="AG43" s="4" t="n"/>
-      <c r="AH43" s="3" t="n"/>
+      <c r="AH43" s="5" t="n"/>
       <c r="AI43" s="3" t="inlineStr">
         <is>
           <t>아라치 (입상수화제)</t>
@@ -5178,7 +5273,7 @@
       <c r="AL43" s="4" t="n"/>
       <c r="AM43" s="9" t="n"/>
     </row>
-    <row r="44" ht="48" customHeight="1">
+    <row r="44" ht="49" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
@@ -5262,9 +5357,9 @@
       <c r="AC44" s="9" t="n"/>
       <c r="AD44" s="9" t="n"/>
       <c r="AE44" s="3" t="n"/>
-      <c r="AF44" s="3" t="n"/>
+      <c r="AF44" s="5" t="n"/>
       <c r="AG44" s="4" t="n"/>
-      <c r="AH44" s="3" t="n"/>
+      <c r="AH44" s="5" t="n"/>
       <c r="AI44" s="3" t="inlineStr">
         <is>
           <t>주렁 (유제)</t>
@@ -5283,7 +5378,7 @@
       <c r="AL44" s="4" t="n"/>
       <c r="AM44" s="9" t="n"/>
     </row>
-    <row r="45" ht="48" customHeight="1">
+    <row r="45" ht="49" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
@@ -5359,7 +5454,7 @@
       <c r="U45" s="3" t="n"/>
       <c r="V45" s="4" t="inlineStr">
         <is>
-          <t>1순위 추천(원문): 지금 바로 이거: 강철비  (Chlorantraniliprole+Emamectin benzoate) [학교 보유 중] 2000배 희석 · 경엽처리 · 안전사용기준: 수확2일전 / 2회</t>
+          <t>1순위 추천(원문): 지금 바로 이거: 강철비 (Chlorantraniliprole+Emamectin benzoate) [학교 보유 중] 2000배 희석 · 경엽처리 · 안전사용기준: 수확2일전 / 2회</t>
         </is>
       </c>
       <c r="W45" s="4" t="n"/>
@@ -5371,9 +5466,9 @@
       <c r="AC45" s="9" t="n"/>
       <c r="AD45" s="9" t="n"/>
       <c r="AE45" s="3" t="n"/>
-      <c r="AF45" s="3" t="n"/>
+      <c r="AF45" s="5" t="n"/>
       <c r="AG45" s="4" t="n"/>
-      <c r="AH45" s="3" t="n"/>
+      <c r="AH45" s="5" t="n"/>
       <c r="AI45" s="3" t="inlineStr">
         <is>
           <t>강철비 (액상수화제)</t>
@@ -5392,7 +5487,7 @@
       <c r="AL45" s="4" t="n"/>
       <c r="AM45" s="9" t="n"/>
     </row>
-    <row r="46" ht="33" customHeight="1">
+    <row r="46" ht="34" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
@@ -5476,9 +5571,9 @@
       <c r="AC46" s="9" t="n"/>
       <c r="AD46" s="9" t="n"/>
       <c r="AE46" s="3" t="n"/>
-      <c r="AF46" s="3" t="n"/>
+      <c r="AF46" s="5" t="n"/>
       <c r="AG46" s="4" t="n"/>
-      <c r="AH46" s="3" t="n"/>
+      <c r="AH46" s="5" t="n"/>
       <c r="AI46" s="3" t="inlineStr">
         <is>
           <t>산마루 (수화제)</t>
@@ -5497,7 +5592,7 @@
       <c r="AL46" s="4" t="n"/>
       <c r="AM46" s="9" t="n"/>
     </row>
-    <row r="47" ht="33" customHeight="1">
+    <row r="47" ht="34" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
@@ -5581,9 +5676,9 @@
       <c r="AC47" s="9" t="n"/>
       <c r="AD47" s="9" t="n"/>
       <c r="AE47" s="3" t="n"/>
-      <c r="AF47" s="3" t="n"/>
+      <c r="AF47" s="5" t="n"/>
       <c r="AG47" s="4" t="n"/>
-      <c r="AH47" s="3" t="n"/>
+      <c r="AH47" s="5" t="n"/>
       <c r="AI47" s="3" t="inlineStr">
         <is>
           <t>인도에마 (수화제)</t>
@@ -5602,7 +5697,7 @@
       <c r="AL47" s="4" t="n"/>
       <c r="AM47" s="9" t="n"/>
     </row>
-    <row r="48" ht="33" customHeight="1">
+    <row r="48" ht="34" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
@@ -5686,9 +5781,9 @@
       <c r="AC48" s="9" t="n"/>
       <c r="AD48" s="9" t="n"/>
       <c r="AE48" s="3" t="n"/>
-      <c r="AF48" s="3" t="n"/>
+      <c r="AF48" s="5" t="n"/>
       <c r="AG48" s="4" t="n"/>
-      <c r="AH48" s="3" t="n"/>
+      <c r="AH48" s="5" t="n"/>
       <c r="AI48" s="3" t="inlineStr">
         <is>
           <t>인시피오 (액상수화제)</t>
@@ -5707,7 +5802,7 @@
       <c r="AL48" s="4" t="n"/>
       <c r="AM48" s="9" t="n"/>
     </row>
-    <row r="49" ht="33" customHeight="1">
+    <row r="49" ht="34" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
@@ -5789,9 +5884,9 @@
       <c r="AC49" s="9" t="n"/>
       <c r="AD49" s="9" t="n"/>
       <c r="AE49" s="3" t="n"/>
-      <c r="AF49" s="3" t="n"/>
+      <c r="AF49" s="5" t="n"/>
       <c r="AG49" s="4" t="n"/>
-      <c r="AH49" s="3" t="n"/>
+      <c r="AH49" s="5" t="n"/>
       <c r="AI49" s="3" t="inlineStr">
         <is>
           <t>가스란 수화제</t>
@@ -5810,7 +5905,7 @@
       <c r="AL49" s="4" t="n"/>
       <c r="AM49" s="9" t="n"/>
     </row>
-    <row r="50" ht="33" customHeight="1">
+    <row r="50" ht="34" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
@@ -5892,9 +5987,9 @@
       <c r="AC50" s="9" t="n"/>
       <c r="AD50" s="9" t="n"/>
       <c r="AE50" s="3" t="n"/>
-      <c r="AF50" s="3" t="n"/>
+      <c r="AF50" s="5" t="n"/>
       <c r="AG50" s="4" t="n"/>
-      <c r="AH50" s="3" t="n"/>
+      <c r="AH50" s="5" t="n"/>
       <c r="AI50" s="3" t="inlineStr">
         <is>
           <t>경탄 액상수화제</t>
@@ -5913,7 +6008,7 @@
       <c r="AL50" s="4" t="n"/>
       <c r="AM50" s="9" t="n"/>
     </row>
-    <row r="51" ht="33" customHeight="1">
+    <row r="51" ht="34" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
@@ -5995,9 +6090,9 @@
       <c r="AC51" s="9" t="n"/>
       <c r="AD51" s="9" t="n"/>
       <c r="AE51" s="3" t="n"/>
-      <c r="AF51" s="3" t="n"/>
+      <c r="AF51" s="5" t="n"/>
       <c r="AG51" s="4" t="n"/>
-      <c r="AH51" s="3" t="n"/>
+      <c r="AH51" s="5" t="n"/>
       <c r="AI51" s="3" t="inlineStr">
         <is>
           <t>골든벨 액상수화제</t>
@@ -6016,7 +6111,7 @@
       <c r="AL51" s="4" t="n"/>
       <c r="AM51" s="9" t="n"/>
     </row>
-    <row r="52" ht="33" customHeight="1">
+    <row r="52" ht="34" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
@@ -6098,9 +6193,9 @@
       <c r="AC52" s="9" t="n"/>
       <c r="AD52" s="9" t="n"/>
       <c r="AE52" s="3" t="n"/>
-      <c r="AF52" s="3" t="n"/>
+      <c r="AF52" s="5" t="n"/>
       <c r="AG52" s="4" t="n"/>
-      <c r="AH52" s="3" t="n"/>
+      <c r="AH52" s="5" t="n"/>
       <c r="AI52" s="3" t="inlineStr">
         <is>
           <t>균디스 액상수화제</t>
@@ -6119,7 +6214,7 @@
       <c r="AL52" s="4" t="n"/>
       <c r="AM52" s="9" t="n"/>
     </row>
-    <row r="53" ht="33" customHeight="1">
+    <row r="53" ht="34" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
@@ -6199,9 +6294,9 @@
       <c r="AC53" s="9" t="n"/>
       <c r="AD53" s="9" t="n"/>
       <c r="AE53" s="3" t="n"/>
-      <c r="AF53" s="3" t="n"/>
+      <c r="AF53" s="5" t="n"/>
       <c r="AG53" s="4" t="n"/>
-      <c r="AH53" s="3" t="n"/>
+      <c r="AH53" s="5" t="n"/>
       <c r="AI53" s="3" t="inlineStr">
         <is>
           <t>보라충 입제</t>
@@ -6220,7 +6315,7 @@
       <c r="AL53" s="4" t="n"/>
       <c r="AM53" s="9" t="n"/>
     </row>
-    <row r="54" ht="33" customHeight="1">
+    <row r="54" ht="34" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
@@ -6302,9 +6397,9 @@
       <c r="AC54" s="9" t="n"/>
       <c r="AD54" s="9" t="n"/>
       <c r="AE54" s="3" t="n"/>
-      <c r="AF54" s="3" t="n"/>
+      <c r="AF54" s="5" t="n"/>
       <c r="AG54" s="4" t="n"/>
-      <c r="AH54" s="3" t="n"/>
+      <c r="AH54" s="5" t="n"/>
       <c r="AI54" s="3" t="inlineStr">
         <is>
           <t>스포르곤 수화제</t>
@@ -6323,7 +6418,7 @@
       <c r="AL54" s="4" t="n"/>
       <c r="AM54" s="9" t="n"/>
     </row>
-    <row r="55" ht="33" customHeight="1">
+    <row r="55" ht="34" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
@@ -6405,9 +6500,9 @@
       <c r="AC55" s="9" t="n"/>
       <c r="AD55" s="9" t="n"/>
       <c r="AE55" s="3" t="n"/>
-      <c r="AF55" s="3" t="n"/>
+      <c r="AF55" s="5" t="n"/>
       <c r="AG55" s="4" t="n"/>
-      <c r="AH55" s="3" t="n"/>
+      <c r="AH55" s="5" t="n"/>
       <c r="AI55" s="3" t="inlineStr">
         <is>
           <t>스포르곤 수화제</t>
@@ -6426,7 +6521,7 @@
       <c r="AL55" s="4" t="n"/>
       <c r="AM55" s="9" t="n"/>
     </row>
-    <row r="56" ht="33" customHeight="1">
+    <row r="56" ht="34" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
@@ -6508,9 +6603,9 @@
       <c r="AC56" s="9" t="n"/>
       <c r="AD56" s="9" t="n"/>
       <c r="AE56" s="3" t="n"/>
-      <c r="AF56" s="3" t="n"/>
+      <c r="AF56" s="5" t="n"/>
       <c r="AG56" s="4" t="n"/>
-      <c r="AH56" s="3" t="n"/>
+      <c r="AH56" s="5" t="n"/>
       <c r="AI56" s="3" t="inlineStr">
         <is>
           <t>스포르곤 입제</t>
@@ -6529,7 +6624,7 @@
       <c r="AL56" s="4" t="n"/>
       <c r="AM56" s="9" t="n"/>
     </row>
-    <row r="57" ht="33" customHeight="1">
+    <row r="57" ht="34" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
@@ -6611,9 +6706,9 @@
       <c r="AC57" s="9" t="n"/>
       <c r="AD57" s="9" t="n"/>
       <c r="AE57" s="3" t="n"/>
-      <c r="AF57" s="3" t="n"/>
+      <c r="AF57" s="5" t="n"/>
       <c r="AG57" s="4" t="n"/>
-      <c r="AH57" s="3" t="n"/>
+      <c r="AH57" s="5" t="n"/>
       <c r="AI57" s="3" t="inlineStr">
         <is>
           <t>스포르곤 입제</t>
@@ -6632,7 +6727,7 @@
       <c r="AL57" s="4" t="n"/>
       <c r="AM57" s="9" t="n"/>
     </row>
-    <row r="58" ht="33" customHeight="1">
+    <row r="58" ht="34" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
@@ -6714,9 +6809,9 @@
       <c r="AC58" s="9" t="n"/>
       <c r="AD58" s="9" t="n"/>
       <c r="AE58" s="3" t="n"/>
-      <c r="AF58" s="3" t="n"/>
+      <c r="AF58" s="5" t="n"/>
       <c r="AG58" s="4" t="n"/>
-      <c r="AH58" s="3" t="n"/>
+      <c r="AH58" s="5" t="n"/>
       <c r="AI58" s="3" t="inlineStr">
         <is>
           <t>스포르곤 입제</t>
@@ -6735,7 +6830,7 @@
       <c r="AL58" s="4" t="n"/>
       <c r="AM58" s="9" t="n"/>
     </row>
-    <row r="59" ht="33" customHeight="1">
+    <row r="59" ht="34" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
@@ -6815,9 +6910,9 @@
       <c r="AC59" s="9" t="n"/>
       <c r="AD59" s="9" t="n"/>
       <c r="AE59" s="3" t="n"/>
-      <c r="AF59" s="3" t="n"/>
+      <c r="AF59" s="5" t="n"/>
       <c r="AG59" s="4" t="n"/>
-      <c r="AH59" s="3" t="n"/>
+      <c r="AH59" s="5" t="n"/>
       <c r="AI59" s="3" t="inlineStr">
         <is>
           <t>싸이포스 입제</t>
@@ -6836,7 +6931,7 @@
       <c r="AL59" s="4" t="n"/>
       <c r="AM59" s="9" t="n"/>
     </row>
-    <row r="60" ht="33" customHeight="1">
+    <row r="60" ht="34" customHeight="1">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
@@ -6916,9 +7011,9 @@
       <c r="AC60" s="9" t="n"/>
       <c r="AD60" s="9" t="n"/>
       <c r="AE60" s="3" t="n"/>
-      <c r="AF60" s="3" t="n"/>
+      <c r="AF60" s="5" t="n"/>
       <c r="AG60" s="4" t="n"/>
-      <c r="AH60" s="3" t="n"/>
+      <c r="AH60" s="5" t="n"/>
       <c r="AI60" s="3" t="inlineStr">
         <is>
           <t>쏘버린 입제</t>
@@ -6937,7 +7032,7 @@
       <c r="AL60" s="4" t="n"/>
       <c r="AM60" s="9" t="n"/>
     </row>
-    <row r="61" ht="33" customHeight="1">
+    <row r="61" ht="34" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
@@ -7019,9 +7114,9 @@
       <c r="AC61" s="9" t="n"/>
       <c r="AD61" s="9" t="n"/>
       <c r="AE61" s="3" t="n"/>
-      <c r="AF61" s="3" t="n"/>
+      <c r="AF61" s="5" t="n"/>
       <c r="AG61" s="4" t="n"/>
-      <c r="AH61" s="3" t="n"/>
+      <c r="AH61" s="5" t="n"/>
       <c r="AI61" s="3" t="inlineStr">
         <is>
           <t>아라치 입상수화제</t>
@@ -7040,7 +7135,7 @@
       <c r="AL61" s="4" t="n"/>
       <c r="AM61" s="9" t="n"/>
     </row>
-    <row r="62" ht="33" customHeight="1">
+    <row r="62" ht="34" customHeight="1">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
@@ -7122,9 +7217,9 @@
       <c r="AC62" s="9" t="n"/>
       <c r="AD62" s="9" t="n"/>
       <c r="AE62" s="3" t="n"/>
-      <c r="AF62" s="3" t="n"/>
+      <c r="AF62" s="5" t="n"/>
       <c r="AG62" s="4" t="n"/>
-      <c r="AH62" s="3" t="n"/>
+      <c r="AH62" s="5" t="n"/>
       <c r="AI62" s="3" t="inlineStr">
         <is>
           <t>오조아 수화제</t>
@@ -7143,7 +7238,7 @@
       <c r="AL62" s="4" t="n"/>
       <c r="AM62" s="9" t="n"/>
     </row>
-    <row r="63" ht="33" customHeight="1">
+    <row r="63" ht="34" customHeight="1">
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
@@ -7225,9 +7320,9 @@
       <c r="AC63" s="9" t="n"/>
       <c r="AD63" s="9" t="n"/>
       <c r="AE63" s="3" t="n"/>
-      <c r="AF63" s="3" t="n"/>
+      <c r="AF63" s="5" t="n"/>
       <c r="AG63" s="4" t="n"/>
-      <c r="AH63" s="3" t="n"/>
+      <c r="AH63" s="5" t="n"/>
       <c r="AI63" s="3" t="inlineStr">
         <is>
           <t>오조아 수화제</t>
@@ -7246,7 +7341,7 @@
       <c r="AL63" s="4" t="n"/>
       <c r="AM63" s="9" t="n"/>
     </row>
-    <row r="64" ht="33" customHeight="1">
+    <row r="64" ht="34" customHeight="1">
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
@@ -7328,9 +7423,9 @@
       <c r="AC64" s="9" t="n"/>
       <c r="AD64" s="9" t="n"/>
       <c r="AE64" s="3" t="n"/>
-      <c r="AF64" s="3" t="n"/>
+      <c r="AF64" s="5" t="n"/>
       <c r="AG64" s="4" t="n"/>
-      <c r="AH64" s="3" t="n"/>
+      <c r="AH64" s="5" t="n"/>
       <c r="AI64" s="3" t="inlineStr">
         <is>
           <t>주렁 유제</t>
@@ -7349,7 +7444,7 @@
       <c r="AL64" s="4" t="n"/>
       <c r="AM64" s="9" t="n"/>
     </row>
-    <row r="65" ht="33" customHeight="1">
+    <row r="65" ht="34" customHeight="1">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
@@ -7431,9 +7526,9 @@
       <c r="AC65" s="9" t="n"/>
       <c r="AD65" s="9" t="n"/>
       <c r="AE65" s="3" t="n"/>
-      <c r="AF65" s="3" t="n"/>
+      <c r="AF65" s="5" t="n"/>
       <c r="AG65" s="4" t="n"/>
-      <c r="AH65" s="3" t="n"/>
+      <c r="AH65" s="5" t="n"/>
       <c r="AI65" s="3" t="inlineStr">
         <is>
           <t>코니도 수화제</t>
@@ -7452,7 +7547,7 @@
       <c r="AL65" s="4" t="n"/>
       <c r="AM65" s="9" t="n"/>
     </row>
-    <row r="66" ht="33" customHeight="1">
+    <row r="66" ht="34" customHeight="1">
       <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
@@ -7532,9 +7627,9 @@
       <c r="AC66" s="9" t="n"/>
       <c r="AD66" s="9" t="n"/>
       <c r="AE66" s="3" t="n"/>
-      <c r="AF66" s="3" t="n"/>
+      <c r="AF66" s="5" t="n"/>
       <c r="AG66" s="4" t="n"/>
-      <c r="AH66" s="3" t="n"/>
+      <c r="AH66" s="5" t="n"/>
       <c r="AI66" s="3" t="inlineStr">
         <is>
           <t>크린쏘일 입제</t>
@@ -7553,7 +7648,7 @@
       <c r="AL66" s="4" t="n"/>
       <c r="AM66" s="9" t="n"/>
     </row>
-    <row r="67" ht="33" customHeight="1">
+    <row r="67" ht="34" customHeight="1">
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
@@ -7635,9 +7730,9 @@
       <c r="AC67" s="9" t="n"/>
       <c r="AD67" s="9" t="n"/>
       <c r="AE67" s="3" t="n"/>
-      <c r="AF67" s="3" t="n"/>
+      <c r="AF67" s="5" t="n"/>
       <c r="AG67" s="4" t="n"/>
-      <c r="AH67" s="3" t="n"/>
+      <c r="AH67" s="5" t="n"/>
       <c r="AI67" s="3" t="inlineStr">
         <is>
           <t>탄쟈비상 액상수화제</t>
@@ -7656,7 +7751,7 @@
       <c r="AL67" s="4" t="n"/>
       <c r="AM67" s="9" t="n"/>
     </row>
-    <row r="68" ht="63" customHeight="1">
+    <row r="68" ht="64" customHeight="1">
       <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
@@ -7760,7 +7855,7 @@
           <t>330-87-00896</t>
         </is>
       </c>
-      <c r="AF68" s="3" t="inlineStr">
+      <c r="AF68" s="5" t="inlineStr">
         <is>
           <t>- (미기재)</t>
         </is>
@@ -7770,7 +7865,7 @@
           <t>전북특별자치도 장수군 장수읍 논개로 242-10</t>
         </is>
       </c>
-      <c r="AH68" s="3" t="inlineStr">
+      <c r="AH68" s="5" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
@@ -7783,7 +7878,7 @@
       <c r="AJ68" s="3" t="n"/>
       <c r="AK68" s="4" t="inlineStr">
         <is>
-          <t>문서 앞부분 &gt; 유기농업자재 요약표</t>
+          <t>문서 앞부분 요약표 · PART 3. 유기농업자재 &gt; 요약 비교표 (동일 표 2회 수록)</t>
         </is>
       </c>
       <c r="AL68" s="4" t="inlineStr">
@@ -7795,7 +7890,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="69" ht="63" customHeight="1">
+    <row r="69" ht="64" customHeight="1">
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
@@ -7848,7 +7943,7 @@
       <c r="R69" s="5" t="n"/>
       <c r="S69" s="3" t="inlineStr">
         <is>
-          <t>60%이상</t>
+          <t>60% 이상</t>
         </is>
       </c>
       <c r="T69" s="3" t="inlineStr">
@@ -7899,7 +7994,7 @@
           <t>330-87-00896</t>
         </is>
       </c>
-      <c r="AF69" s="3" t="inlineStr">
+      <c r="AF69" s="5" t="inlineStr">
         <is>
           <t>- (미기재)</t>
         </is>
@@ -7909,7 +8004,7 @@
           <t>전북특별자치도 장수군 장수읍 논개로 242-10</t>
         </is>
       </c>
-      <c r="AH69" s="3" t="inlineStr">
+      <c r="AH69" s="5" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
@@ -7922,7 +8017,7 @@
       <c r="AJ69" s="3" t="n"/>
       <c r="AK69" s="4" t="inlineStr">
         <is>
-          <t>문서 앞부분 &gt; 유기농업자재 요약표</t>
+          <t>문서 앞부분 요약표 · PART 3. 유기농업자재 &gt; 요약 비교표 (동일 표 2회 수록)</t>
         </is>
       </c>
       <c r="AL69" s="4" t="inlineStr">
@@ -7934,7 +8029,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="70" ht="78" customHeight="1">
+    <row r="70" ht="79" customHeight="1">
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
@@ -7987,7 +8082,7 @@
       <c r="R70" s="5" t="n"/>
       <c r="S70" s="3" t="inlineStr">
         <is>
-          <t>50%이상</t>
+          <t>50% 이상</t>
         </is>
       </c>
       <c r="T70" s="3" t="inlineStr">
@@ -8038,7 +8133,7 @@
           <t>124-86-37020</t>
         </is>
       </c>
-      <c r="AF70" s="3" t="inlineStr">
+      <c r="AF70" s="5" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
@@ -8048,7 +8143,7 @@
           <t>경기도 화성시 효행구 정남면 정남동로 346</t>
         </is>
       </c>
-      <c r="AH70" s="3" t="inlineStr">
+      <c r="AH70" s="5" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
@@ -8061,7 +8156,7 @@
       <c r="AJ70" s="3" t="n"/>
       <c r="AK70" s="4" t="inlineStr">
         <is>
-          <t>문서 앞부분 &gt; 유기농업자재 요약표</t>
+          <t>문서 앞부분 요약표 · PART 3. 유기농업자재 &gt; 요약 비교표 (동일 표 2회 수록)</t>
         </is>
       </c>
       <c r="AL70" s="4" t="inlineStr">
@@ -8073,7 +8168,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="71" ht="78" customHeight="1">
+    <row r="71" ht="79" customHeight="1">
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
@@ -8126,7 +8221,7 @@
       <c r="R71" s="5" t="n"/>
       <c r="S71" s="3" t="inlineStr">
         <is>
-          <t>50%이상</t>
+          <t>50% 이상</t>
         </is>
       </c>
       <c r="T71" s="3" t="inlineStr">
@@ -8177,7 +8272,7 @@
           <t>124-86-37020</t>
         </is>
       </c>
-      <c r="AF71" s="3" t="inlineStr">
+      <c r="AF71" s="5" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
@@ -8187,7 +8282,7 @@
           <t>경기도 화성시 효행구 정남면 정남동로 346</t>
         </is>
       </c>
-      <c r="AH71" s="3" t="inlineStr">
+      <c r="AH71" s="5" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
@@ -8200,7 +8295,7 @@
       <c r="AJ71" s="3" t="n"/>
       <c r="AK71" s="4" t="inlineStr">
         <is>
-          <t>문서 앞부분 &gt; 유기농업자재 요약표</t>
+          <t>문서 앞부분 요약표 · PART 3. 유기농업자재 &gt; 요약 비교표 (동일 표 2회 수록)</t>
         </is>
       </c>
       <c r="AL71" s="4" t="inlineStr">
@@ -8212,7 +8307,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="72" ht="78" customHeight="1">
+    <row r="72" ht="79" customHeight="1">
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
@@ -8265,7 +8360,7 @@
       <c r="R72" s="5" t="n"/>
       <c r="S72" s="3" t="inlineStr">
         <is>
-          <t>50%이상</t>
+          <t>50% 이상</t>
         </is>
       </c>
       <c r="T72" s="3" t="inlineStr">
@@ -8316,7 +8411,7 @@
           <t>124-86-37020</t>
         </is>
       </c>
-      <c r="AF72" s="3" t="inlineStr">
+      <c r="AF72" s="5" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
@@ -8326,7 +8421,7 @@
           <t>경기도 화성시 효행구 정남면 정남동로 346</t>
         </is>
       </c>
-      <c r="AH72" s="3" t="inlineStr">
+      <c r="AH72" s="5" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
@@ -8339,7 +8434,7 @@
       <c r="AJ72" s="3" t="n"/>
       <c r="AK72" s="4" t="inlineStr">
         <is>
-          <t>문서 앞부분 &gt; 유기농업자재 요약표</t>
+          <t>문서 앞부분 요약표 · PART 3. 유기농업자재 &gt; 요약 비교표 (동일 표 2회 수록)</t>
         </is>
       </c>
       <c r="AL72" s="4" t="inlineStr">
@@ -8351,28 +8446,28 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="73" ht="63" customHeight="1">
+    <row r="73" ht="34" customHeight="1">
       <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
+          <t>유기농업자재(기타 방제효과)</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
           <t>유기농업자재</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>유기농업자재</t>
-        </is>
-      </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>꽃노랑총채벌레</t>
+          <t>점박이응애</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>고추</t>
+          <t>딸기</t>
         </is>
       </c>
       <c r="F73" s="2" t="n"/>
@@ -8385,18 +8480,12 @@
       <c r="I73" s="5" t="n"/>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>오렌지추출물 15%+파라핀오일 65%</t>
+          <t>오렌지추출물 15%, 파라핀오일 65%</t>
         </is>
       </c>
       <c r="K73" s="3" t="n"/>
-      <c r="L73" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M73" s="3" t="inlineStr">
-        <is>
-          <t>경엽처리</t>
-        </is>
-      </c>
+      <c r="L73" s="6" t="n"/>
+      <c r="M73" s="3" t="n"/>
       <c r="N73" s="3" t="n"/>
       <c r="O73" s="7" t="n"/>
       <c r="P73" s="4" t="n"/>
@@ -8404,7 +8493,7 @@
       <c r="R73" s="5" t="n"/>
       <c r="S73" s="3" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="T73" s="3" t="inlineStr">
@@ -8418,11 +8507,7 @@
         </is>
       </c>
       <c r="V73" s="4" t="n"/>
-      <c r="W73" s="4" t="inlineStr">
-        <is>
-          <t>관련 병해충·방제가(원문): 꽃노랑총채벌레(고추, 61.7%)온실가루이(오이 시험, 60%이상) / 희석·처리(원문): 1,000배 희석경엽처리</t>
-        </is>
-      </c>
+      <c r="W73" s="4" t="n"/>
       <c r="X73" s="3" t="inlineStr">
         <is>
           <t>공시-3-6-054(공시-1-6-036)</t>
@@ -8438,9 +8523,7 @@
           <t>식물추출물+파라핀오일</t>
         </is>
       </c>
-      <c r="AA73" s="8" t="n">
-        <v>44000</v>
-      </c>
+      <c r="AA73" s="8" t="n"/>
       <c r="AB73" s="9" t="n">
         <v>43518</v>
       </c>
@@ -8455,7 +8538,7 @@
           <t>330-87-00896</t>
         </is>
       </c>
-      <c r="AF73" s="3" t="inlineStr">
+      <c r="AF73" s="5" t="inlineStr">
         <is>
           <t>- (미기재)</t>
         </is>
@@ -8465,20 +8548,16 @@
           <t>전북특별자치도 장수군 장수읍 논개로 242-10</t>
         </is>
       </c>
-      <c r="AH73" s="3" t="inlineStr">
+      <c r="AH73" s="5" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="AI73" s="3" t="inlineStr">
-        <is>
-          <t>한방싹충도사</t>
-        </is>
-      </c>
+      <c r="AI73" s="3" t="n"/>
       <c r="AJ73" s="3" t="n"/>
       <c r="AK73" s="4" t="inlineStr">
         <is>
-          <t>PART 3. 유기농업자재 &gt; 요약 비교표</t>
+          <t>PART 3. 유기농업자재 &gt; 한방싹충도사 (병해충관리용)</t>
         </is>
       </c>
       <c r="AL73" s="4" t="inlineStr">
@@ -8490,28 +8569,28 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="74" ht="63" customHeight="1">
+    <row r="74" ht="34" customHeight="1">
       <c r="A74" s="2" t="n">
         <v>73</v>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
+          <t>유기농업자재(기타 방제효과)</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
           <t>유기농업자재</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>유기농업자재</t>
-        </is>
-      </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>온실가루이</t>
+          <t>조팝나무진딧물</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>오이(시험)</t>
+          <t>배</t>
         </is>
       </c>
       <c r="F74" s="2" t="n"/>
@@ -8524,18 +8603,12 @@
       <c r="I74" s="5" t="n"/>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>오렌지추출물 15%+파라핀오일 65%</t>
+          <t>오렌지추출물 15%, 파라핀오일 65%</t>
         </is>
       </c>
       <c r="K74" s="3" t="n"/>
-      <c r="L74" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M74" s="3" t="inlineStr">
-        <is>
-          <t>경엽처리</t>
-        </is>
-      </c>
+      <c r="L74" s="6" t="n"/>
+      <c r="M74" s="3" t="n"/>
       <c r="N74" s="3" t="n"/>
       <c r="O74" s="7" t="n"/>
       <c r="P74" s="4" t="n"/>
@@ -8543,7 +8616,7 @@
       <c r="R74" s="5" t="n"/>
       <c r="S74" s="3" t="inlineStr">
         <is>
-          <t>60%이상</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="T74" s="3" t="inlineStr">
@@ -8557,11 +8630,7 @@
         </is>
       </c>
       <c r="V74" s="4" t="n"/>
-      <c r="W74" s="4" t="inlineStr">
-        <is>
-          <t>관련 병해충·방제가(원문): 꽃노랑총채벌레(고추, 61.7%)온실가루이(오이 시험, 60%이상) / 희석·처리(원문): 1,000배 희석경엽처리</t>
-        </is>
-      </c>
+      <c r="W74" s="4" t="n"/>
       <c r="X74" s="3" t="inlineStr">
         <is>
           <t>공시-3-6-054(공시-1-6-036)</t>
@@ -8577,9 +8646,7 @@
           <t>식물추출물+파라핀오일</t>
         </is>
       </c>
-      <c r="AA74" s="8" t="n">
-        <v>44000</v>
-      </c>
+      <c r="AA74" s="8" t="n"/>
       <c r="AB74" s="9" t="n">
         <v>43518</v>
       </c>
@@ -8594,7 +8661,7 @@
           <t>330-87-00896</t>
         </is>
       </c>
-      <c r="AF74" s="3" t="inlineStr">
+      <c r="AF74" s="5" t="inlineStr">
         <is>
           <t>- (미기재)</t>
         </is>
@@ -8604,20 +8671,16 @@
           <t>전북특별자치도 장수군 장수읍 논개로 242-10</t>
         </is>
       </c>
-      <c r="AH74" s="3" t="inlineStr">
+      <c r="AH74" s="5" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="AI74" s="3" t="inlineStr">
-        <is>
-          <t>한방싹충도사</t>
-        </is>
-      </c>
+      <c r="AI74" s="3" t="n"/>
       <c r="AJ74" s="3" t="n"/>
       <c r="AK74" s="4" t="inlineStr">
         <is>
-          <t>PART 3. 유기농업자재 &gt; 요약 비교표</t>
+          <t>PART 3. 유기농업자재 &gt; 한방싹충도사 (병해충관리용)</t>
         </is>
       </c>
       <c r="AL74" s="4" t="inlineStr">
@@ -8629,52 +8692,46 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="75" ht="78" customHeight="1">
+    <row r="75" ht="34" customHeight="1">
       <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
+          <t>유기농업자재(기타 방제효과)</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
           <t>유기농업자재</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>유기농업자재</t>
-        </is>
-      </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>복숭아혹진딧물</t>
+          <t>배추흰나비</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>고추</t>
+          <t>양배추</t>
         </is>
       </c>
       <c r="F75" s="2" t="n"/>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>뉴응칠이</t>
+          <t>한방싹충도사</t>
         </is>
       </c>
       <c r="H75" s="5" t="n"/>
       <c r="I75" s="5" t="n"/>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>유칼립투스오일 30%+고삼추출물 50%</t>
+          <t>오렌지추출물 15%, 파라핀오일 65%</t>
         </is>
       </c>
       <c r="K75" s="3" t="n"/>
-      <c r="L75" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M75" s="3" t="inlineStr">
-        <is>
-          <t>경엽처리</t>
-        </is>
-      </c>
+      <c r="L75" s="6" t="n"/>
+      <c r="M75" s="3" t="n"/>
       <c r="N75" s="3" t="n"/>
       <c r="O75" s="7" t="n"/>
       <c r="P75" s="4" t="n"/>
@@ -8682,28 +8739,24 @@
       <c r="R75" s="5" t="n"/>
       <c r="S75" s="3" t="inlineStr">
         <is>
-          <t>50%이상</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="T75" s="3" t="inlineStr">
         <is>
-          <t>고려바이오㈜</t>
+          <t>농업회사법인 장수바이오(주)</t>
         </is>
       </c>
       <c r="U75" s="3" t="inlineStr">
         <is>
-          <t>031-354-8183</t>
+          <t>063-351-4081</t>
         </is>
       </c>
       <c r="V75" s="4" t="n"/>
-      <c r="W75" s="4" t="inlineStr">
-        <is>
-          <t>관련 병해충·방제가(원문): 복숭아혹진딧물(고추, 50%이상)꽃노랑총채벌레·온실가루이(오이 시험, 50%이상) / 희석·처리(원문): 1,000배 희석경엽처리</t>
-        </is>
-      </c>
+      <c r="W75" s="4" t="n"/>
       <c r="X75" s="3" t="inlineStr">
         <is>
-          <t>공시-2-6-061</t>
+          <t>공시-3-6-054(공시-1-6-036)</t>
         </is>
       </c>
       <c r="Y75" s="3" t="inlineStr">
@@ -8713,50 +8766,44 @@
       </c>
       <c r="Z75" s="3" t="inlineStr">
         <is>
-          <t>식물성오일+식물추출물</t>
-        </is>
-      </c>
-      <c r="AA75" s="8" t="n">
-        <v>45000</v>
-      </c>
+          <t>식물추출물+파라핀오일</t>
+        </is>
+      </c>
+      <c r="AA75" s="8" t="n"/>
       <c r="AB75" s="9" t="n">
-        <v>44280</v>
+        <v>43518</v>
       </c>
       <c r="AC75" s="9" t="n">
-        <v>45376</v>
+        <v>45710</v>
       </c>
       <c r="AD75" s="9" t="n">
-        <v>46470</v>
+        <v>46804</v>
       </c>
       <c r="AE75" s="3" t="inlineStr">
         <is>
-          <t>124-86-37020</t>
-        </is>
-      </c>
-      <c r="AF75" s="3" t="inlineStr">
-        <is>
-          <t>있음</t>
+          <t>330-87-00896</t>
+        </is>
+      </c>
+      <c r="AF75" s="5" t="inlineStr">
+        <is>
+          <t>- (미기재)</t>
         </is>
       </c>
       <c r="AG75" s="4" t="inlineStr">
         <is>
-          <t>경기도 화성시 효행구 정남면 정남동로 346</t>
-        </is>
-      </c>
-      <c r="AH75" s="3" t="inlineStr">
+          <t>전북특별자치도 장수군 장수읍 논개로 242-10</t>
+        </is>
+      </c>
+      <c r="AH75" s="5" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="AI75" s="3" t="inlineStr">
-        <is>
-          <t>뉴응칠이</t>
-        </is>
-      </c>
+      <c r="AI75" s="3" t="n"/>
       <c r="AJ75" s="3" t="n"/>
       <c r="AK75" s="4" t="inlineStr">
         <is>
-          <t>PART 3. 유기농업자재 &gt; 요약 비교표</t>
+          <t>PART 3. 유기농업자재 &gt; 한방싹충도사 (병해충관리용)</t>
         </is>
       </c>
       <c r="AL75" s="4" t="inlineStr">
@@ -8768,52 +8815,46 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="76" ht="78" customHeight="1">
+    <row r="76" ht="34" customHeight="1">
       <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
+          <t>유기농업자재(기타 방제효과)</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
           <t>유기농업자재</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>유기농업자재</t>
-        </is>
-      </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>꽃노랑총채벌레</t>
+          <t>복숭아순나방</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>오이(시험)</t>
+          <t>복숭아</t>
         </is>
       </c>
       <c r="F76" s="2" t="n"/>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>뉴응칠이</t>
+          <t>한방싹충도사</t>
         </is>
       </c>
       <c r="H76" s="5" t="n"/>
       <c r="I76" s="5" t="n"/>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>유칼립투스오일 30%+고삼추출물 50%</t>
+          <t>오렌지추출물 15%, 파라핀오일 65%</t>
         </is>
       </c>
       <c r="K76" s="3" t="n"/>
-      <c r="L76" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M76" s="3" t="inlineStr">
-        <is>
-          <t>경엽처리</t>
-        </is>
-      </c>
+      <c r="L76" s="6" t="n"/>
+      <c r="M76" s="3" t="n"/>
       <c r="N76" s="3" t="n"/>
       <c r="O76" s="7" t="n"/>
       <c r="P76" s="4" t="n"/>
@@ -8821,28 +8862,24 @@
       <c r="R76" s="5" t="n"/>
       <c r="S76" s="3" t="inlineStr">
         <is>
-          <t>50%이상</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="T76" s="3" t="inlineStr">
         <is>
-          <t>고려바이오㈜</t>
+          <t>농업회사법인 장수바이오(주)</t>
         </is>
       </c>
       <c r="U76" s="3" t="inlineStr">
         <is>
-          <t>031-354-8183</t>
+          <t>063-351-4081</t>
         </is>
       </c>
       <c r="V76" s="4" t="n"/>
-      <c r="W76" s="4" t="inlineStr">
-        <is>
-          <t>관련 병해충·방제가(원문): 복숭아혹진딧물(고추, 50%이상)꽃노랑총채벌레·온실가루이(오이 시험, 50%이상) / 희석·처리(원문): 1,000배 희석경엽처리</t>
-        </is>
-      </c>
+      <c r="W76" s="4" t="n"/>
       <c r="X76" s="3" t="inlineStr">
         <is>
-          <t>공시-2-6-061</t>
+          <t>공시-3-6-054(공시-1-6-036)</t>
         </is>
       </c>
       <c r="Y76" s="3" t="inlineStr">
@@ -8852,50 +8889,44 @@
       </c>
       <c r="Z76" s="3" t="inlineStr">
         <is>
-          <t>식물성오일+식물추출물</t>
-        </is>
-      </c>
-      <c r="AA76" s="8" t="n">
-        <v>45000</v>
-      </c>
+          <t>식물추출물+파라핀오일</t>
+        </is>
+      </c>
+      <c r="AA76" s="8" t="n"/>
       <c r="AB76" s="9" t="n">
-        <v>44280</v>
+        <v>43518</v>
       </c>
       <c r="AC76" s="9" t="n">
-        <v>45376</v>
+        <v>45710</v>
       </c>
       <c r="AD76" s="9" t="n">
-        <v>46470</v>
+        <v>46804</v>
       </c>
       <c r="AE76" s="3" t="inlineStr">
         <is>
-          <t>124-86-37020</t>
-        </is>
-      </c>
-      <c r="AF76" s="3" t="inlineStr">
-        <is>
-          <t>있음</t>
+          <t>330-87-00896</t>
+        </is>
+      </c>
+      <c r="AF76" s="5" t="inlineStr">
+        <is>
+          <t>- (미기재)</t>
         </is>
       </c>
       <c r="AG76" s="4" t="inlineStr">
         <is>
-          <t>경기도 화성시 효행구 정남면 정남동로 346</t>
-        </is>
-      </c>
-      <c r="AH76" s="3" t="inlineStr">
+          <t>전북특별자치도 장수군 장수읍 논개로 242-10</t>
+        </is>
+      </c>
+      <c r="AH76" s="5" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="AI76" s="3" t="inlineStr">
-        <is>
-          <t>뉴응칠이</t>
-        </is>
-      </c>
+      <c r="AI76" s="3" t="n"/>
       <c r="AJ76" s="3" t="n"/>
       <c r="AK76" s="4" t="inlineStr">
         <is>
-          <t>PART 3. 유기농업자재 &gt; 요약 비교표</t>
+          <t>PART 3. 유기농업자재 &gt; 한방싹충도사 (병해충관리용)</t>
         </is>
       </c>
       <c r="AL76" s="4" t="inlineStr">
@@ -8907,52 +8938,46 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="77" ht="78" customHeight="1">
+    <row r="77" ht="34" customHeight="1">
       <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
+          <t>유기농업자재(기타 방제효과)</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
           <t>유기농업자재</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>유기농업자재</t>
-        </is>
-      </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>온실가루이</t>
+          <t>꽃매미</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>오이(시험)</t>
+          <t>포도</t>
         </is>
       </c>
       <c r="F77" s="2" t="n"/>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>뉴응칠이</t>
+          <t>한방싹충도사</t>
         </is>
       </c>
       <c r="H77" s="5" t="n"/>
       <c r="I77" s="5" t="n"/>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>유칼립투스오일 30%+고삼추출물 50%</t>
+          <t>오렌지추출물 15%, 파라핀오일 65%</t>
         </is>
       </c>
       <c r="K77" s="3" t="n"/>
-      <c r="L77" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M77" s="3" t="inlineStr">
-        <is>
-          <t>경엽처리</t>
-        </is>
-      </c>
+      <c r="L77" s="6" t="n"/>
+      <c r="M77" s="3" t="n"/>
       <c r="N77" s="3" t="n"/>
       <c r="O77" s="7" t="n"/>
       <c r="P77" s="4" t="n"/>
@@ -8960,28 +8985,24 @@
       <c r="R77" s="5" t="n"/>
       <c r="S77" s="3" t="inlineStr">
         <is>
-          <t>50%이상</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="T77" s="3" t="inlineStr">
         <is>
-          <t>고려바이오㈜</t>
+          <t>농업회사법인 장수바이오(주)</t>
         </is>
       </c>
       <c r="U77" s="3" t="inlineStr">
         <is>
-          <t>031-354-8183</t>
+          <t>063-351-4081</t>
         </is>
       </c>
       <c r="V77" s="4" t="n"/>
-      <c r="W77" s="4" t="inlineStr">
-        <is>
-          <t>관련 병해충·방제가(원문): 복숭아혹진딧물(고추, 50%이상)꽃노랑총채벌레·온실가루이(오이 시험, 50%이상) / 희석·처리(원문): 1,000배 희석경엽처리</t>
-        </is>
-      </c>
+      <c r="W77" s="4" t="n"/>
       <c r="X77" s="3" t="inlineStr">
         <is>
-          <t>공시-2-6-061</t>
+          <t>공시-3-6-054(공시-1-6-036)</t>
         </is>
       </c>
       <c r="Y77" s="3" t="inlineStr">
@@ -8991,50 +9012,44 @@
       </c>
       <c r="Z77" s="3" t="inlineStr">
         <is>
-          <t>식물성오일+식물추출물</t>
-        </is>
-      </c>
-      <c r="AA77" s="8" t="n">
-        <v>45000</v>
-      </c>
+          <t>식물추출물+파라핀오일</t>
+        </is>
+      </c>
+      <c r="AA77" s="8" t="n"/>
       <c r="AB77" s="9" t="n">
-        <v>44280</v>
+        <v>43518</v>
       </c>
       <c r="AC77" s="9" t="n">
-        <v>45376</v>
+        <v>45710</v>
       </c>
       <c r="AD77" s="9" t="n">
-        <v>46470</v>
+        <v>46804</v>
       </c>
       <c r="AE77" s="3" t="inlineStr">
         <is>
-          <t>124-86-37020</t>
-        </is>
-      </c>
-      <c r="AF77" s="3" t="inlineStr">
-        <is>
-          <t>있음</t>
+          <t>330-87-00896</t>
+        </is>
+      </c>
+      <c r="AF77" s="5" t="inlineStr">
+        <is>
+          <t>- (미기재)</t>
         </is>
       </c>
       <c r="AG77" s="4" t="inlineStr">
         <is>
-          <t>경기도 화성시 효행구 정남면 정남동로 346</t>
-        </is>
-      </c>
-      <c r="AH77" s="3" t="inlineStr">
+          <t>전북특별자치도 장수군 장수읍 논개로 242-10</t>
+        </is>
+      </c>
+      <c r="AH77" s="5" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="AI77" s="3" t="inlineStr">
-        <is>
-          <t>뉴응칠이</t>
-        </is>
-      </c>
+      <c r="AI77" s="3" t="n"/>
       <c r="AJ77" s="3" t="n"/>
       <c r="AK77" s="4" t="inlineStr">
         <is>
-          <t>PART 3. 유기농업자재 &gt; 요약 비교표</t>
+          <t>PART 3. 유기농업자재 &gt; 한방싹충도사 (병해충관리용)</t>
         </is>
       </c>
       <c r="AL77" s="4" t="inlineStr">
@@ -9046,7 +9061,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="78" ht="33" customHeight="1">
+    <row r="78" ht="34" customHeight="1">
       <c r="A78" s="2" t="n">
         <v>77</v>
       </c>
@@ -9062,12 +9077,12 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>점박이응애</t>
+          <t>갈색날개매미충</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>딸기</t>
+          <t>사과</t>
         </is>
       </c>
       <c r="F78" s="2" t="n"/>
@@ -9093,7 +9108,7 @@
       <c r="R78" s="5" t="n"/>
       <c r="S78" s="3" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="T78" s="3" t="inlineStr">
@@ -9138,7 +9153,7 @@
           <t>330-87-00896</t>
         </is>
       </c>
-      <c r="AF78" s="3" t="inlineStr">
+      <c r="AF78" s="5" t="inlineStr">
         <is>
           <t>- (미기재)</t>
         </is>
@@ -9148,7 +9163,7 @@
           <t>전북특별자치도 장수군 장수읍 논개로 242-10</t>
         </is>
       </c>
-      <c r="AH78" s="3" t="inlineStr">
+      <c r="AH78" s="5" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
@@ -9169,7 +9184,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="79" ht="33" customHeight="1">
+    <row r="79" ht="34" customHeight="1">
       <c r="A79" s="2" t="n">
         <v>78</v>
       </c>
@@ -9185,12 +9200,12 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>조팝나무진딧물</t>
+          <t>온실가루이</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>배</t>
+          <t>오이</t>
         </is>
       </c>
       <c r="F79" s="2" t="n"/>
@@ -9216,7 +9231,7 @@
       <c r="R79" s="5" t="n"/>
       <c r="S79" s="3" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>60% 이상</t>
         </is>
       </c>
       <c r="T79" s="3" t="inlineStr">
@@ -9261,7 +9276,7 @@
           <t>330-87-00896</t>
         </is>
       </c>
-      <c r="AF79" s="3" t="inlineStr">
+      <c r="AF79" s="5" t="inlineStr">
         <is>
           <t>- (미기재)</t>
         </is>
@@ -9271,7 +9286,7 @@
           <t>전북특별자치도 장수군 장수읍 논개로 242-10</t>
         </is>
       </c>
-      <c r="AH79" s="3" t="inlineStr">
+      <c r="AH79" s="5" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
@@ -9292,7 +9307,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="80" ht="33" customHeight="1">
+    <row r="80" ht="34" customHeight="1">
       <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
@@ -9308,12 +9323,12 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>배추흰나비</t>
+          <t>이세리아깍지벌레</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>양배추</t>
+          <t>감귤</t>
         </is>
       </c>
       <c r="F80" s="2" t="n"/>
@@ -9339,7 +9354,7 @@
       <c r="R80" s="5" t="n"/>
       <c r="S80" s="3" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>60% 이상</t>
         </is>
       </c>
       <c r="T80" s="3" t="inlineStr">
@@ -9384,7 +9399,7 @@
           <t>330-87-00896</t>
         </is>
       </c>
-      <c r="AF80" s="3" t="inlineStr">
+      <c r="AF80" s="5" t="inlineStr">
         <is>
           <t>- (미기재)</t>
         </is>
@@ -9394,7 +9409,7 @@
           <t>전북특별자치도 장수군 장수읍 논개로 242-10</t>
         </is>
       </c>
-      <c r="AH80" s="3" t="inlineStr">
+      <c r="AH80" s="5" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
@@ -9415,7 +9430,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="81" ht="33" customHeight="1">
+    <row r="81" ht="34" customHeight="1">
       <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
@@ -9431,25 +9446,25 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>복숭아순나방</t>
+          <t>꽃노랑총채벌레</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>복숭아</t>
+          <t>오이(시험)</t>
         </is>
       </c>
       <c r="F81" s="2" t="n"/>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>한방싹충도사</t>
+          <t>뉴응칠이</t>
         </is>
       </c>
       <c r="H81" s="5" t="n"/>
       <c r="I81" s="5" t="n"/>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>오렌지추출물 15%, 파라핀오일 65%</t>
+          <t>유칼립투스오일 30%, 고삼추출물 50%</t>
         </is>
       </c>
       <c r="K81" s="3" t="n"/>
@@ -9462,24 +9477,24 @@
       <c r="R81" s="5" t="n"/>
       <c r="S81" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50% 이상</t>
         </is>
       </c>
       <c r="T81" s="3" t="inlineStr">
         <is>
-          <t>농업회사법인 장수바이오(주)</t>
+          <t>고려바이오㈜</t>
         </is>
       </c>
       <c r="U81" s="3" t="inlineStr">
         <is>
-          <t>063-351-4081</t>
+          <t>031-354-8183</t>
         </is>
       </c>
       <c r="V81" s="4" t="n"/>
       <c r="W81" s="4" t="n"/>
       <c r="X81" s="3" t="inlineStr">
         <is>
-          <t>공시-3-6-054(공시-1-6-036)</t>
+          <t>공시-2-6-061</t>
         </is>
       </c>
       <c r="Y81" s="3" t="inlineStr">
@@ -9489,35 +9504,35 @@
       </c>
       <c r="Z81" s="3" t="inlineStr">
         <is>
-          <t>식물추출물+파라핀오일</t>
+          <t>식물성오일+식물추출물</t>
         </is>
       </c>
       <c r="AA81" s="8" t="n"/>
       <c r="AB81" s="9" t="n">
-        <v>43518</v>
+        <v>44280</v>
       </c>
       <c r="AC81" s="9" t="n">
-        <v>45710</v>
+        <v>45376</v>
       </c>
       <c r="AD81" s="9" t="n">
-        <v>46804</v>
+        <v>46470</v>
       </c>
       <c r="AE81" s="3" t="inlineStr">
         <is>
-          <t>330-87-00896</t>
-        </is>
-      </c>
-      <c r="AF81" s="3" t="inlineStr">
-        <is>
-          <t>- (미기재)</t>
+          <t>124-86-37020</t>
+        </is>
+      </c>
+      <c r="AF81" s="5" t="inlineStr">
+        <is>
+          <t>있음</t>
         </is>
       </c>
       <c r="AG81" s="4" t="inlineStr">
         <is>
-          <t>전북특별자치도 장수군 장수읍 논개로 242-10</t>
-        </is>
-      </c>
-      <c r="AH81" s="3" t="inlineStr">
+          <t>경기도 화성시 효행구 정남면 정남동로 346</t>
+        </is>
+      </c>
+      <c r="AH81" s="5" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
@@ -9526,7 +9541,7 @@
       <c r="AJ81" s="3" t="n"/>
       <c r="AK81" s="4" t="inlineStr">
         <is>
-          <t>PART 3. 유기농업자재 &gt; 한방싹충도사 (병해충관리용)</t>
+          <t>PART 3. 유기농업자재 &gt; 뉴응칠이 (병해충관리용)</t>
         </is>
       </c>
       <c r="AL81" s="4" t="inlineStr">
@@ -9538,7 +9553,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="82" ht="33" customHeight="1">
+    <row r="82" ht="34" customHeight="1">
       <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
@@ -9554,25 +9569,25 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>꽃매미</t>
+          <t>아메리카잎굴파리</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>포도</t>
+          <t>오이(시험)</t>
         </is>
       </c>
       <c r="F82" s="2" t="n"/>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>한방싹충도사</t>
+          <t>뉴응칠이</t>
         </is>
       </c>
       <c r="H82" s="5" t="n"/>
       <c r="I82" s="5" t="n"/>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>오렌지추출물 15%, 파라핀오일 65%</t>
+          <t>유칼립투스오일 30%, 고삼추출물 50%</t>
         </is>
       </c>
       <c r="K82" s="3" t="n"/>
@@ -9585,24 +9600,24 @@
       <c r="R82" s="5" t="n"/>
       <c r="S82" s="3" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>50% 이상</t>
         </is>
       </c>
       <c r="T82" s="3" t="inlineStr">
         <is>
-          <t>농업회사법인 장수바이오(주)</t>
+          <t>고려바이오㈜</t>
         </is>
       </c>
       <c r="U82" s="3" t="inlineStr">
         <is>
-          <t>063-351-4081</t>
+          <t>031-354-8183</t>
         </is>
       </c>
       <c r="V82" s="4" t="n"/>
       <c r="W82" s="4" t="n"/>
       <c r="X82" s="3" t="inlineStr">
         <is>
-          <t>공시-3-6-054(공시-1-6-036)</t>
+          <t>공시-2-6-061</t>
         </is>
       </c>
       <c r="Y82" s="3" t="inlineStr">
@@ -9612,35 +9627,35 @@
       </c>
       <c r="Z82" s="3" t="inlineStr">
         <is>
-          <t>식물추출물+파라핀오일</t>
+          <t>식물성오일+식물추출물</t>
         </is>
       </c>
       <c r="AA82" s="8" t="n"/>
       <c r="AB82" s="9" t="n">
-        <v>43518</v>
+        <v>44280</v>
       </c>
       <c r="AC82" s="9" t="n">
-        <v>45710</v>
+        <v>45376</v>
       </c>
       <c r="AD82" s="9" t="n">
-        <v>46804</v>
+        <v>46470</v>
       </c>
       <c r="AE82" s="3" t="inlineStr">
         <is>
-          <t>330-87-00896</t>
-        </is>
-      </c>
-      <c r="AF82" s="3" t="inlineStr">
-        <is>
-          <t>- (미기재)</t>
+          <t>124-86-37020</t>
+        </is>
+      </c>
+      <c r="AF82" s="5" t="inlineStr">
+        <is>
+          <t>있음</t>
         </is>
       </c>
       <c r="AG82" s="4" t="inlineStr">
         <is>
-          <t>전북특별자치도 장수군 장수읍 논개로 242-10</t>
-        </is>
-      </c>
-      <c r="AH82" s="3" t="inlineStr">
+          <t>경기도 화성시 효행구 정남면 정남동로 346</t>
+        </is>
+      </c>
+      <c r="AH82" s="5" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
@@ -9649,7 +9664,7 @@
       <c r="AJ82" s="3" t="n"/>
       <c r="AK82" s="4" t="inlineStr">
         <is>
-          <t>PART 3. 유기농업자재 &gt; 한방싹충도사 (병해충관리용)</t>
+          <t>PART 3. 유기농업자재 &gt; 뉴응칠이 (병해충관리용)</t>
         </is>
       </c>
       <c r="AL82" s="4" t="inlineStr">
@@ -9661,7 +9676,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="83" ht="33" customHeight="1">
+    <row r="83" ht="34" customHeight="1">
       <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
@@ -9677,25 +9692,25 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>갈색날개매미충</t>
+          <t>온실가루이</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>사과</t>
+          <t>오이(시험)</t>
         </is>
       </c>
       <c r="F83" s="2" t="n"/>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>한방싹충도사</t>
+          <t>뉴응칠이</t>
         </is>
       </c>
       <c r="H83" s="5" t="n"/>
       <c r="I83" s="5" t="n"/>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>오렌지추출물 15%, 파라핀오일 65%</t>
+          <t>유칼립투스오일 30%, 고삼추출물 50%</t>
         </is>
       </c>
       <c r="K83" s="3" t="n"/>
@@ -9708,24 +9723,24 @@
       <c r="R83" s="5" t="n"/>
       <c r="S83" s="3" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>50% 이상</t>
         </is>
       </c>
       <c r="T83" s="3" t="inlineStr">
         <is>
-          <t>농업회사법인 장수바이오(주)</t>
+          <t>고려바이오㈜</t>
         </is>
       </c>
       <c r="U83" s="3" t="inlineStr">
         <is>
-          <t>063-351-4081</t>
+          <t>031-354-8183</t>
         </is>
       </c>
       <c r="V83" s="4" t="n"/>
       <c r="W83" s="4" t="n"/>
       <c r="X83" s="3" t="inlineStr">
         <is>
-          <t>공시-3-6-054(공시-1-6-036)</t>
+          <t>공시-2-6-061</t>
         </is>
       </c>
       <c r="Y83" s="3" t="inlineStr">
@@ -9735,35 +9750,35 @@
       </c>
       <c r="Z83" s="3" t="inlineStr">
         <is>
-          <t>식물추출물+파라핀오일</t>
+          <t>식물성오일+식물추출물</t>
         </is>
       </c>
       <c r="AA83" s="8" t="n"/>
       <c r="AB83" s="9" t="n">
-        <v>43518</v>
+        <v>44280</v>
       </c>
       <c r="AC83" s="9" t="n">
-        <v>45710</v>
+        <v>45376</v>
       </c>
       <c r="AD83" s="9" t="n">
-        <v>46804</v>
+        <v>46470</v>
       </c>
       <c r="AE83" s="3" t="inlineStr">
         <is>
-          <t>330-87-00896</t>
-        </is>
-      </c>
-      <c r="AF83" s="3" t="inlineStr">
-        <is>
-          <t>- (미기재)</t>
+          <t>124-86-37020</t>
+        </is>
+      </c>
+      <c r="AF83" s="5" t="inlineStr">
+        <is>
+          <t>있음</t>
         </is>
       </c>
       <c r="AG83" s="4" t="inlineStr">
         <is>
-          <t>전북특별자치도 장수군 장수읍 논개로 242-10</t>
-        </is>
-      </c>
-      <c r="AH83" s="3" t="inlineStr">
+          <t>경기도 화성시 효행구 정남면 정남동로 346</t>
+        </is>
+      </c>
+      <c r="AH83" s="5" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
@@ -9772,7 +9787,7 @@
       <c r="AJ83" s="3" t="n"/>
       <c r="AK83" s="4" t="inlineStr">
         <is>
-          <t>PART 3. 유기농업자재 &gt; 한방싹충도사 (병해충관리용)</t>
+          <t>PART 3. 유기농업자재 &gt; 뉴응칠이 (병해충관리용)</t>
         </is>
       </c>
       <c r="AL83" s="4" t="inlineStr">
@@ -9784,7 +9799,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="84" ht="33" customHeight="1">
+    <row r="84" ht="34" customHeight="1">
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
@@ -9800,25 +9815,25 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>온실가루이</t>
+          <t>흰가루병</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>오이</t>
+          <t>오이(시험)</t>
         </is>
       </c>
       <c r="F84" s="2" t="n"/>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>한방싹충도사</t>
+          <t>뉴응칠이</t>
         </is>
       </c>
       <c r="H84" s="5" t="n"/>
       <c r="I84" s="5" t="n"/>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>오렌지추출물 15%, 파라핀오일 65%</t>
+          <t>유칼립투스오일 30%, 고삼추출물 50%</t>
         </is>
       </c>
       <c r="K84" s="3" t="n"/>
@@ -9831,24 +9846,24 @@
       <c r="R84" s="5" t="n"/>
       <c r="S84" s="3" t="inlineStr">
         <is>
-          <t>60%이상</t>
+          <t>50% 이상</t>
         </is>
       </c>
       <c r="T84" s="3" t="inlineStr">
         <is>
-          <t>농업회사법인 장수바이오(주)</t>
+          <t>고려바이오㈜</t>
         </is>
       </c>
       <c r="U84" s="3" t="inlineStr">
         <is>
-          <t>063-351-4081</t>
+          <t>031-354-8183</t>
         </is>
       </c>
       <c r="V84" s="4" t="n"/>
       <c r="W84" s="4" t="n"/>
       <c r="X84" s="3" t="inlineStr">
         <is>
-          <t>공시-3-6-054(공시-1-6-036)</t>
+          <t>공시-2-6-061</t>
         </is>
       </c>
       <c r="Y84" s="3" t="inlineStr">
@@ -9858,35 +9873,35 @@
       </c>
       <c r="Z84" s="3" t="inlineStr">
         <is>
-          <t>식물추출물+파라핀오일</t>
+          <t>식물성오일+식물추출물</t>
         </is>
       </c>
       <c r="AA84" s="8" t="n"/>
       <c r="AB84" s="9" t="n">
-        <v>43518</v>
+        <v>44280</v>
       </c>
       <c r="AC84" s="9" t="n">
-        <v>45710</v>
+        <v>45376</v>
       </c>
       <c r="AD84" s="9" t="n">
-        <v>46804</v>
+        <v>46470</v>
       </c>
       <c r="AE84" s="3" t="inlineStr">
         <is>
-          <t>330-87-00896</t>
-        </is>
-      </c>
-      <c r="AF84" s="3" t="inlineStr">
-        <is>
-          <t>- (미기재)</t>
+          <t>124-86-37020</t>
+        </is>
+      </c>
+      <c r="AF84" s="5" t="inlineStr">
+        <is>
+          <t>있음</t>
         </is>
       </c>
       <c r="AG84" s="4" t="inlineStr">
         <is>
-          <t>전북특별자치도 장수군 장수읍 논개로 242-10</t>
-        </is>
-      </c>
-      <c r="AH84" s="3" t="inlineStr">
+          <t>경기도 화성시 효행구 정남면 정남동로 346</t>
+        </is>
+      </c>
+      <c r="AH84" s="5" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
@@ -9895,7 +9910,7 @@
       <c r="AJ84" s="3" t="n"/>
       <c r="AK84" s="4" t="inlineStr">
         <is>
-          <t>PART 3. 유기농업자재 &gt; 한방싹충도사 (병해충관리용)</t>
+          <t>PART 3. 유기농업자재 &gt; 뉴응칠이 (병해충관리용)</t>
         </is>
       </c>
       <c r="AL84" s="4" t="inlineStr">
@@ -9907,7 +9922,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="85" ht="33" customHeight="1">
+    <row r="85" ht="34" customHeight="1">
       <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
@@ -9923,25 +9938,25 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>이세리아깍지벌레</t>
+          <t>미국선녀벌레</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>감귤</t>
+          <t>블루베리</t>
         </is>
       </c>
       <c r="F85" s="2" t="n"/>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>한방싹충도사</t>
+          <t>뉴응칠이</t>
         </is>
       </c>
       <c r="H85" s="5" t="n"/>
       <c r="I85" s="5" t="n"/>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>오렌지추출물 15%, 파라핀오일 65%</t>
+          <t>유칼립투스오일 30%, 고삼추출물 50%</t>
         </is>
       </c>
       <c r="K85" s="3" t="n"/>
@@ -9954,24 +9969,24 @@
       <c r="R85" s="5" t="n"/>
       <c r="S85" s="3" t="inlineStr">
         <is>
-          <t>60%이상</t>
+          <t>50% 이상</t>
         </is>
       </c>
       <c r="T85" s="3" t="inlineStr">
         <is>
-          <t>농업회사법인 장수바이오(주)</t>
+          <t>고려바이오㈜</t>
         </is>
       </c>
       <c r="U85" s="3" t="inlineStr">
         <is>
-          <t>063-351-4081</t>
+          <t>031-354-8183</t>
         </is>
       </c>
       <c r="V85" s="4" t="n"/>
       <c r="W85" s="4" t="n"/>
       <c r="X85" s="3" t="inlineStr">
         <is>
-          <t>공시-3-6-054(공시-1-6-036)</t>
+          <t>공시-2-6-061</t>
         </is>
       </c>
       <c r="Y85" s="3" t="inlineStr">
@@ -9981,35 +9996,35 @@
       </c>
       <c r="Z85" s="3" t="inlineStr">
         <is>
-          <t>식물추출물+파라핀오일</t>
+          <t>식물성오일+식물추출물</t>
         </is>
       </c>
       <c r="AA85" s="8" t="n"/>
       <c r="AB85" s="9" t="n">
-        <v>43518</v>
+        <v>44280</v>
       </c>
       <c r="AC85" s="9" t="n">
-        <v>45710</v>
+        <v>45376</v>
       </c>
       <c r="AD85" s="9" t="n">
-        <v>46804</v>
+        <v>46470</v>
       </c>
       <c r="AE85" s="3" t="inlineStr">
         <is>
-          <t>330-87-00896</t>
-        </is>
-      </c>
-      <c r="AF85" s="3" t="inlineStr">
-        <is>
-          <t>- (미기재)</t>
+          <t>124-86-37020</t>
+        </is>
+      </c>
+      <c r="AF85" s="5" t="inlineStr">
+        <is>
+          <t>있음</t>
         </is>
       </c>
       <c r="AG85" s="4" t="inlineStr">
         <is>
-          <t>전북특별자치도 장수군 장수읍 논개로 242-10</t>
-        </is>
-      </c>
-      <c r="AH85" s="3" t="inlineStr">
+          <t>경기도 화성시 효행구 정남면 정남동로 346</t>
+        </is>
+      </c>
+      <c r="AH85" s="5" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
@@ -10018,7 +10033,7 @@
       <c r="AJ85" s="3" t="n"/>
       <c r="AK85" s="4" t="inlineStr">
         <is>
-          <t>PART 3. 유기농업자재 &gt; 한방싹충도사 (병해충관리용)</t>
+          <t>PART 3. 유기농업자재 &gt; 뉴응칠이 (병해충관리용)</t>
         </is>
       </c>
       <c r="AL85" s="4" t="inlineStr">
@@ -10030,622 +10045,432 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="86" ht="33" customHeight="1">
+    <row r="86" ht="34" customHeight="1">
       <c r="A86" s="2" t="n">
         <v>85</v>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>유기농업자재(기타 방제효과)</t>
+          <t>혼용 가능 조합</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>유기농업자재</t>
+          <t>혼용정보</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>꽃노랑총채벌레</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>오이(시험)</t>
-        </is>
-      </c>
+          <t>갈색무늬병</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n"/>
       <c r="F86" s="2" t="n"/>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>뉴응칠이</t>
+          <t>모스피란</t>
         </is>
       </c>
       <c r="H86" s="5" t="n"/>
       <c r="I86" s="5" t="n"/>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>유칼립투스오일 30%, 고삼추출물 50%</t>
-        </is>
-      </c>
+      <c r="J86" s="4" t="n"/>
       <c r="K86" s="3" t="n"/>
       <c r="L86" s="6" t="n"/>
       <c r="M86" s="3" t="n"/>
       <c r="N86" s="3" t="n"/>
       <c r="O86" s="7" t="n"/>
       <c r="P86" s="4" t="n"/>
-      <c r="Q86" s="3" t="n"/>
-      <c r="R86" s="5" t="n"/>
-      <c r="S86" s="3" t="inlineStr">
-        <is>
-          <t>50% 이상</t>
-        </is>
-      </c>
-      <c r="T86" s="3" t="inlineStr">
-        <is>
-          <t>고려바이오㈜</t>
-        </is>
-      </c>
-      <c r="U86" s="3" t="inlineStr">
-        <is>
-          <t>031-354-8183</t>
-        </is>
-      </c>
-      <c r="V86" s="4" t="n"/>
-      <c r="W86" s="4" t="n"/>
-      <c r="X86" s="3" t="inlineStr">
-        <is>
-          <t>공시-2-6-061</t>
-        </is>
-      </c>
-      <c r="Y86" s="3" t="inlineStr">
-        <is>
-          <t>병해충관리용</t>
-        </is>
-      </c>
-      <c r="Z86" s="3" t="inlineStr">
-        <is>
-          <t>식물성오일+식물추출물</t>
-        </is>
-      </c>
+      <c r="Q86" s="3" t="inlineStr">
+        <is>
+          <t>탄쟈비상</t>
+        </is>
+      </c>
+      <c r="R86" s="5" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="S86" s="3" t="n"/>
+      <c r="T86" s="3" t="n"/>
+      <c r="U86" s="3" t="n"/>
+      <c r="V86" s="4" t="inlineStr">
+        <is>
+          <t>가이드 내 위치: 갈색무늬병 1순위</t>
+        </is>
+      </c>
+      <c r="W86" s="4" t="inlineStr">
+        <is>
+          <t>살균제(탄쟈비상) 학교 미보유 - 구매 필요</t>
+        </is>
+      </c>
+      <c r="X86" s="3" t="n"/>
+      <c r="Y86" s="3" t="n"/>
+      <c r="Z86" s="3" t="n"/>
       <c r="AA86" s="8" t="n"/>
-      <c r="AB86" s="9" t="n">
-        <v>44280</v>
-      </c>
-      <c r="AC86" s="9" t="n">
-        <v>45376</v>
-      </c>
-      <c r="AD86" s="9" t="n">
-        <v>46470</v>
-      </c>
-      <c r="AE86" s="3" t="inlineStr">
-        <is>
-          <t>124-86-37020</t>
-        </is>
-      </c>
-      <c r="AF86" s="3" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="AG86" s="4" t="inlineStr">
-        <is>
-          <t>경기도 화성시 효행구 정남면 정남동로 346</t>
-        </is>
-      </c>
-      <c r="AH86" s="3" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="AB86" s="9" t="n"/>
+      <c r="AC86" s="9" t="n"/>
+      <c r="AD86" s="9" t="n"/>
+      <c r="AE86" s="3" t="n"/>
+      <c r="AF86" s="5" t="n"/>
+      <c r="AG86" s="4" t="n"/>
+      <c r="AH86" s="5" t="n"/>
       <c r="AI86" s="3" t="n"/>
       <c r="AJ86" s="3" t="n"/>
       <c r="AK86" s="4" t="inlineStr">
         <is>
-          <t>PART 3. 유기농업자재 &gt; 뉴응칠이 (병해충관리용)</t>
+          <t>PART 4. 혼용 가능 조합 &gt; 확인된 조합</t>
         </is>
       </c>
       <c r="AL86" s="4" t="inlineStr">
         <is>
-          <t>국립농산물품질관리원 유기농업자재 공시현황(naqs.go.kr)</t>
+          <t>knco.co.kr/product/product_09 (경농 혼용안내, 고추 기준)</t>
         </is>
       </c>
       <c r="AM86" s="9" t="n">
         <v>46283</v>
       </c>
     </row>
-    <row r="87" ht="33" customHeight="1">
+    <row r="87" ht="34" customHeight="1">
       <c r="A87" s="2" t="n">
         <v>86</v>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>유기농업자재(기타 방제효과)</t>
+          <t>혼용 가능 조합</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>유기농업자재</t>
+          <t>혼용정보</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>아메리카잎굴파리</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>오이(시험)</t>
-        </is>
-      </c>
+          <t>탄저병</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="n"/>
       <c r="F87" s="2" t="n"/>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>뉴응칠이</t>
+          <t>모스피란</t>
         </is>
       </c>
       <c r="H87" s="5" t="n"/>
       <c r="I87" s="5" t="n"/>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>유칼립투스오일 30%, 고삼추출물 50%</t>
-        </is>
-      </c>
+      <c r="J87" s="4" t="n"/>
       <c r="K87" s="3" t="n"/>
       <c r="L87" s="6" t="n"/>
       <c r="M87" s="3" t="n"/>
       <c r="N87" s="3" t="n"/>
       <c r="O87" s="7" t="n"/>
       <c r="P87" s="4" t="n"/>
-      <c r="Q87" s="3" t="n"/>
-      <c r="R87" s="5" t="n"/>
-      <c r="S87" s="3" t="inlineStr">
-        <is>
-          <t>50% 이상</t>
-        </is>
-      </c>
-      <c r="T87" s="3" t="inlineStr">
-        <is>
-          <t>고려바이오㈜</t>
-        </is>
-      </c>
-      <c r="U87" s="3" t="inlineStr">
-        <is>
-          <t>031-354-8183</t>
-        </is>
-      </c>
-      <c r="V87" s="4" t="n"/>
-      <c r="W87" s="4" t="n"/>
-      <c r="X87" s="3" t="inlineStr">
-        <is>
-          <t>공시-2-6-061</t>
-        </is>
-      </c>
-      <c r="Y87" s="3" t="inlineStr">
-        <is>
-          <t>병해충관리용</t>
-        </is>
-      </c>
-      <c r="Z87" s="3" t="inlineStr">
-        <is>
-          <t>식물성오일+식물추출물</t>
-        </is>
-      </c>
+      <c r="Q87" s="3" t="inlineStr">
+        <is>
+          <t>벨리스플러스</t>
+        </is>
+      </c>
+      <c r="R87" s="5" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="S87" s="3" t="n"/>
+      <c r="T87" s="3" t="n"/>
+      <c r="U87" s="3" t="n"/>
+      <c r="V87" s="4" t="inlineStr">
+        <is>
+          <t>가이드 내 위치: 탄저병 1순위</t>
+        </is>
+      </c>
+      <c r="W87" s="4" t="inlineStr">
+        <is>
+          <t>살균제(벨리스플러스) 학교 보유 중</t>
+        </is>
+      </c>
+      <c r="X87" s="3" t="n"/>
+      <c r="Y87" s="3" t="n"/>
+      <c r="Z87" s="3" t="n"/>
       <c r="AA87" s="8" t="n"/>
-      <c r="AB87" s="9" t="n">
-        <v>44280</v>
-      </c>
-      <c r="AC87" s="9" t="n">
-        <v>45376</v>
-      </c>
-      <c r="AD87" s="9" t="n">
-        <v>46470</v>
-      </c>
-      <c r="AE87" s="3" t="inlineStr">
-        <is>
-          <t>124-86-37020</t>
-        </is>
-      </c>
-      <c r="AF87" s="3" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="AG87" s="4" t="inlineStr">
-        <is>
-          <t>경기도 화성시 효행구 정남면 정남동로 346</t>
-        </is>
-      </c>
-      <c r="AH87" s="3" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="AB87" s="9" t="n"/>
+      <c r="AC87" s="9" t="n"/>
+      <c r="AD87" s="9" t="n"/>
+      <c r="AE87" s="3" t="n"/>
+      <c r="AF87" s="5" t="n"/>
+      <c r="AG87" s="4" t="n"/>
+      <c r="AH87" s="5" t="n"/>
       <c r="AI87" s="3" t="n"/>
       <c r="AJ87" s="3" t="n"/>
       <c r="AK87" s="4" t="inlineStr">
         <is>
-          <t>PART 3. 유기농업자재 &gt; 뉴응칠이 (병해충관리용)</t>
+          <t>PART 4. 혼용 가능 조합 &gt; 확인된 조합</t>
         </is>
       </c>
       <c r="AL87" s="4" t="inlineStr">
         <is>
-          <t>국립농산물품질관리원 유기농업자재 공시현황(naqs.go.kr)</t>
+          <t>knco.co.kr/product/product_09 (경농 혼용안내, 고추 기준)</t>
         </is>
       </c>
       <c r="AM87" s="9" t="n">
         <v>46283</v>
       </c>
     </row>
-    <row r="88" ht="33" customHeight="1">
+    <row r="88" ht="34" customHeight="1">
       <c r="A88" s="2" t="n">
         <v>87</v>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>유기농업자재(기타 방제효과)</t>
+          <t>혼용 가능 조합</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>유기농업자재</t>
+          <t>혼용정보</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>온실가루이</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>오이(시험)</t>
-        </is>
-      </c>
+          <t>탄저병</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="n"/>
       <c r="F88" s="2" t="n"/>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>뉴응칠이</t>
+          <t>모스피란</t>
         </is>
       </c>
       <c r="H88" s="5" t="n"/>
       <c r="I88" s="5" t="n"/>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>유칼립투스오일 30%, 고삼추출물 50%</t>
-        </is>
-      </c>
+      <c r="J88" s="4" t="n"/>
       <c r="K88" s="3" t="n"/>
       <c r="L88" s="6" t="n"/>
       <c r="M88" s="3" t="n"/>
       <c r="N88" s="3" t="n"/>
       <c r="O88" s="7" t="n"/>
       <c r="P88" s="4" t="n"/>
-      <c r="Q88" s="3" t="n"/>
-      <c r="R88" s="5" t="n"/>
-      <c r="S88" s="3" t="inlineStr">
-        <is>
-          <t>50% 이상</t>
-        </is>
-      </c>
-      <c r="T88" s="3" t="inlineStr">
-        <is>
-          <t>고려바이오㈜</t>
-        </is>
-      </c>
-      <c r="U88" s="3" t="inlineStr">
-        <is>
-          <t>031-354-8183</t>
-        </is>
-      </c>
-      <c r="V88" s="4" t="n"/>
-      <c r="W88" s="4" t="n"/>
-      <c r="X88" s="3" t="inlineStr">
-        <is>
-          <t>공시-2-6-061</t>
-        </is>
-      </c>
-      <c r="Y88" s="3" t="inlineStr">
-        <is>
-          <t>병해충관리용</t>
-        </is>
-      </c>
-      <c r="Z88" s="3" t="inlineStr">
-        <is>
-          <t>식물성오일+식물추출물</t>
-        </is>
-      </c>
+      <c r="Q88" s="3" t="inlineStr">
+        <is>
+          <t>다놀라</t>
+        </is>
+      </c>
+      <c r="R88" s="5" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="S88" s="3" t="n"/>
+      <c r="T88" s="3" t="n"/>
+      <c r="U88" s="3" t="n"/>
+      <c r="V88" s="4" t="inlineStr">
+        <is>
+          <t>가이드 내 위치: 탄저병 2순위</t>
+        </is>
+      </c>
+      <c r="W88" s="4" t="inlineStr">
+        <is>
+          <t>살균제(다놀라) 학교 보유 중</t>
+        </is>
+      </c>
+      <c r="X88" s="3" t="n"/>
+      <c r="Y88" s="3" t="n"/>
+      <c r="Z88" s="3" t="n"/>
       <c r="AA88" s="8" t="n"/>
-      <c r="AB88" s="9" t="n">
-        <v>44280</v>
-      </c>
-      <c r="AC88" s="9" t="n">
-        <v>45376</v>
-      </c>
-      <c r="AD88" s="9" t="n">
-        <v>46470</v>
-      </c>
-      <c r="AE88" s="3" t="inlineStr">
-        <is>
-          <t>124-86-37020</t>
-        </is>
-      </c>
-      <c r="AF88" s="3" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="AG88" s="4" t="inlineStr">
-        <is>
-          <t>경기도 화성시 효행구 정남면 정남동로 346</t>
-        </is>
-      </c>
-      <c r="AH88" s="3" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="AB88" s="9" t="n"/>
+      <c r="AC88" s="9" t="n"/>
+      <c r="AD88" s="9" t="n"/>
+      <c r="AE88" s="3" t="n"/>
+      <c r="AF88" s="5" t="n"/>
+      <c r="AG88" s="4" t="n"/>
+      <c r="AH88" s="5" t="n"/>
       <c r="AI88" s="3" t="n"/>
       <c r="AJ88" s="3" t="n"/>
       <c r="AK88" s="4" t="inlineStr">
         <is>
-          <t>PART 3. 유기농업자재 &gt; 뉴응칠이 (병해충관리용)</t>
+          <t>PART 4. 혼용 가능 조합 &gt; 확인된 조합</t>
         </is>
       </c>
       <c r="AL88" s="4" t="inlineStr">
         <is>
-          <t>국립농산물품질관리원 유기농업자재 공시현황(naqs.go.kr)</t>
+          <t>knco.co.kr/product/product_09 (경농 혼용안내, 고추 기준)</t>
         </is>
       </c>
       <c r="AM88" s="9" t="n">
         <v>46283</v>
       </c>
     </row>
-    <row r="89" ht="33" customHeight="1">
+    <row r="89" ht="34" customHeight="1">
       <c r="A89" s="2" t="n">
         <v>88</v>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>유기농업자재(기타 방제효과)</t>
+          <t>혼용 가능 조합</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>유기농업자재</t>
+          <t>혼용정보</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>흰가루병</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>오이(시험)</t>
-        </is>
-      </c>
+          <t>탄저병</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="n"/>
       <c r="F89" s="2" t="n"/>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>뉴응칠이</t>
+          <t>모스피란</t>
         </is>
       </c>
       <c r="H89" s="5" t="n"/>
       <c r="I89" s="5" t="n"/>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>유칼립투스오일 30%, 고삼추출물 50%</t>
-        </is>
-      </c>
+      <c r="J89" s="4" t="n"/>
       <c r="K89" s="3" t="n"/>
       <c r="L89" s="6" t="n"/>
       <c r="M89" s="3" t="n"/>
       <c r="N89" s="3" t="n"/>
       <c r="O89" s="7" t="n"/>
       <c r="P89" s="4" t="n"/>
-      <c r="Q89" s="3" t="n"/>
-      <c r="R89" s="5" t="n"/>
-      <c r="S89" s="3" t="inlineStr">
-        <is>
-          <t>50% 이상</t>
-        </is>
-      </c>
-      <c r="T89" s="3" t="inlineStr">
-        <is>
-          <t>고려바이오㈜</t>
-        </is>
-      </c>
-      <c r="U89" s="3" t="inlineStr">
-        <is>
-          <t>031-354-8183</t>
-        </is>
-      </c>
-      <c r="V89" s="4" t="n"/>
-      <c r="W89" s="4" t="n"/>
-      <c r="X89" s="3" t="inlineStr">
-        <is>
-          <t>공시-2-6-061</t>
-        </is>
-      </c>
-      <c r="Y89" s="3" t="inlineStr">
-        <is>
-          <t>병해충관리용</t>
-        </is>
-      </c>
-      <c r="Z89" s="3" t="inlineStr">
-        <is>
-          <t>식물성오일+식물추출물</t>
-        </is>
-      </c>
+      <c r="Q89" s="3" t="inlineStr">
+        <is>
+          <t>벨쿠트</t>
+        </is>
+      </c>
+      <c r="R89" s="5" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="S89" s="3" t="n"/>
+      <c r="T89" s="3" t="n"/>
+      <c r="U89" s="3" t="n"/>
+      <c r="V89" s="4" t="inlineStr">
+        <is>
+          <t>가이드 내 위치: 탄저병 4순위</t>
+        </is>
+      </c>
+      <c r="W89" s="4" t="inlineStr">
+        <is>
+          <t>살균제(벨쿠트) 학교 보유 중</t>
+        </is>
+      </c>
+      <c r="X89" s="3" t="n"/>
+      <c r="Y89" s="3" t="n"/>
+      <c r="Z89" s="3" t="n"/>
       <c r="AA89" s="8" t="n"/>
-      <c r="AB89" s="9" t="n">
-        <v>44280</v>
-      </c>
-      <c r="AC89" s="9" t="n">
-        <v>45376</v>
-      </c>
-      <c r="AD89" s="9" t="n">
-        <v>46470</v>
-      </c>
-      <c r="AE89" s="3" t="inlineStr">
-        <is>
-          <t>124-86-37020</t>
-        </is>
-      </c>
-      <c r="AF89" s="3" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="AG89" s="4" t="inlineStr">
-        <is>
-          <t>경기도 화성시 효행구 정남면 정남동로 346</t>
-        </is>
-      </c>
-      <c r="AH89" s="3" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="AB89" s="9" t="n"/>
+      <c r="AC89" s="9" t="n"/>
+      <c r="AD89" s="9" t="n"/>
+      <c r="AE89" s="3" t="n"/>
+      <c r="AF89" s="5" t="n"/>
+      <c r="AG89" s="4" t="n"/>
+      <c r="AH89" s="5" t="n"/>
       <c r="AI89" s="3" t="n"/>
       <c r="AJ89" s="3" t="n"/>
       <c r="AK89" s="4" t="inlineStr">
         <is>
-          <t>PART 3. 유기농업자재 &gt; 뉴응칠이 (병해충관리용)</t>
+          <t>PART 4. 혼용 가능 조합 &gt; 확인된 조합</t>
         </is>
       </c>
       <c r="AL89" s="4" t="inlineStr">
         <is>
-          <t>국립농산물품질관리원 유기농업자재 공시현황(naqs.go.kr)</t>
+          <t>knco.co.kr/product/product_09 (경농 혼용안내, 고추 기준)</t>
         </is>
       </c>
       <c r="AM89" s="9" t="n">
         <v>46283</v>
       </c>
     </row>
-    <row r="90" ht="33" customHeight="1">
+    <row r="90" ht="34" customHeight="1">
       <c r="A90" s="2" t="n">
         <v>89</v>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>유기농업자재(기타 방제효과)</t>
+          <t>혼용 가능 조합</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>유기농업자재</t>
+          <t>혼용정보</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>미국선녀벌레</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>블루베리</t>
-        </is>
-      </c>
+          <t>세균점무늬병</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="n"/>
       <c r="F90" s="2" t="n"/>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>뉴응칠이</t>
+          <t>모스피란</t>
         </is>
       </c>
       <c r="H90" s="5" t="n"/>
       <c r="I90" s="5" t="n"/>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>유칼립투스오일 30%, 고삼추출물 50%</t>
-        </is>
-      </c>
+      <c r="J90" s="4" t="n"/>
       <c r="K90" s="3" t="n"/>
       <c r="L90" s="6" t="n"/>
       <c r="M90" s="3" t="n"/>
       <c r="N90" s="3" t="n"/>
       <c r="O90" s="7" t="n"/>
       <c r="P90" s="4" t="n"/>
-      <c r="Q90" s="3" t="n"/>
-      <c r="R90" s="5" t="n"/>
-      <c r="S90" s="3" t="inlineStr">
-        <is>
-          <t>50% 이상</t>
-        </is>
-      </c>
-      <c r="T90" s="3" t="inlineStr">
-        <is>
-          <t>고려바이오㈜</t>
-        </is>
-      </c>
-      <c r="U90" s="3" t="inlineStr">
-        <is>
-          <t>031-354-8183</t>
-        </is>
-      </c>
-      <c r="V90" s="4" t="n"/>
-      <c r="W90" s="4" t="n"/>
-      <c r="X90" s="3" t="inlineStr">
-        <is>
-          <t>공시-2-6-061</t>
-        </is>
-      </c>
-      <c r="Y90" s="3" t="inlineStr">
-        <is>
-          <t>병해충관리용</t>
-        </is>
-      </c>
-      <c r="Z90" s="3" t="inlineStr">
-        <is>
-          <t>식물성오일+식물추출물</t>
-        </is>
-      </c>
+      <c r="Q90" s="3" t="inlineStr">
+        <is>
+          <t>가스란</t>
+        </is>
+      </c>
+      <c r="R90" s="5" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="S90" s="3" t="n"/>
+      <c r="T90" s="3" t="n"/>
+      <c r="U90" s="3" t="n"/>
+      <c r="V90" s="4" t="inlineStr">
+        <is>
+          <t>가이드 내 위치: 세균점무늬병 3순위</t>
+        </is>
+      </c>
+      <c r="W90" s="4" t="inlineStr">
+        <is>
+          <t>살균제(가스란) 학교 미보유 - 구매 필요</t>
+        </is>
+      </c>
+      <c r="X90" s="3" t="n"/>
+      <c r="Y90" s="3" t="n"/>
+      <c r="Z90" s="3" t="n"/>
       <c r="AA90" s="8" t="n"/>
-      <c r="AB90" s="9" t="n">
-        <v>44280</v>
-      </c>
-      <c r="AC90" s="9" t="n">
-        <v>45376</v>
-      </c>
-      <c r="AD90" s="9" t="n">
-        <v>46470</v>
-      </c>
-      <c r="AE90" s="3" t="inlineStr">
-        <is>
-          <t>124-86-37020</t>
-        </is>
-      </c>
-      <c r="AF90" s="3" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="AG90" s="4" t="inlineStr">
-        <is>
-          <t>경기도 화성시 효행구 정남면 정남동로 346</t>
-        </is>
-      </c>
-      <c r="AH90" s="3" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="AB90" s="9" t="n"/>
+      <c r="AC90" s="9" t="n"/>
+      <c r="AD90" s="9" t="n"/>
+      <c r="AE90" s="3" t="n"/>
+      <c r="AF90" s="5" t="n"/>
+      <c r="AG90" s="4" t="n"/>
+      <c r="AH90" s="5" t="n"/>
       <c r="AI90" s="3" t="n"/>
       <c r="AJ90" s="3" t="n"/>
       <c r="AK90" s="4" t="inlineStr">
         <is>
-          <t>PART 3. 유기농업자재 &gt; 뉴응칠이 (병해충관리용)</t>
+          <t>PART 4. 혼용 가능 조합 &gt; 확인된 조합</t>
         </is>
       </c>
       <c r="AL90" s="4" t="inlineStr">
         <is>
-          <t>국립농산물품질관리원 유기농업자재 공시현황(naqs.go.kr)</t>
+          <t>knco.co.kr/product/product_09 (경농 혼용안내, 고추 기준)</t>
         </is>
       </c>
       <c r="AM90" s="9" t="n">
         <v>46283</v>
       </c>
     </row>
-    <row r="91" ht="33" customHeight="1">
+    <row r="91" ht="49" customHeight="1">
       <c r="A91" s="2" t="n">
         <v>90</v>
       </c>
@@ -10661,14 +10486,14 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>갈색무늬병</t>
+          <t>탄저병</t>
         </is>
       </c>
       <c r="E91" s="5" t="n"/>
       <c r="F91" s="2" t="n"/>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>모스피란</t>
+          <t>코니도</t>
         </is>
       </c>
       <c r="H91" s="5" t="n"/>
@@ -10682,7 +10507,7 @@
       <c r="P91" s="4" t="n"/>
       <c r="Q91" s="3" t="inlineStr">
         <is>
-          <t>탄쟈비상</t>
+          <t>벨쿠트</t>
         </is>
       </c>
       <c r="R91" s="5" t="inlineStr">
@@ -10695,12 +10520,12 @@
       <c r="U91" s="3" t="n"/>
       <c r="V91" s="4" t="inlineStr">
         <is>
-          <t>가이드 내 위치: 갈색무늬병 1순위</t>
+          <t>가이드 내 위치: 탄저병 4순위</t>
         </is>
       </c>
       <c r="W91" s="4" t="inlineStr">
         <is>
-          <t>살균제(탄쟈비상) 학교 미보유 - 구매 필요</t>
+          <t>살균제(벨쿠트) 학교 보유 중</t>
         </is>
       </c>
       <c r="X91" s="3" t="n"/>
@@ -10711,26 +10536,26 @@
       <c r="AC91" s="9" t="n"/>
       <c r="AD91" s="9" t="n"/>
       <c r="AE91" s="3" t="n"/>
-      <c r="AF91" s="3" t="n"/>
+      <c r="AF91" s="5" t="n"/>
       <c r="AG91" s="4" t="n"/>
-      <c r="AH91" s="3" t="n"/>
+      <c r="AH91" s="5" t="n"/>
       <c r="AI91" s="3" t="n"/>
       <c r="AJ91" s="3" t="n"/>
       <c r="AK91" s="4" t="inlineStr">
         <is>
-          <t>PART 4. 혼용 가능 조합 &gt; 확인된 조합</t>
+          <t>PART 4. 혼용 가능 조합 &gt; 바이엘(코니도·타스타) 공식 혼용정보</t>
         </is>
       </c>
       <c r="AL91" s="4" t="inlineStr">
         <is>
-          <t>knco.co.kr/product/product_09 (경농 혼용안내, 고추 기준)</t>
+          <t>farmhannong.com/kor/product/mix-info (바이엘 혼용기술정보 2025)</t>
         </is>
       </c>
       <c r="AM91" s="9" t="n">
         <v>46283</v>
       </c>
     </row>
-    <row r="92" ht="33" customHeight="1">
+    <row r="92" ht="49" customHeight="1">
       <c r="A92" s="2" t="n">
         <v>91</v>
       </c>
@@ -10744,16 +10569,12 @@
           <t>혼용정보</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
-        <is>
-          <t>탄저병</t>
-        </is>
-      </c>
+      <c r="D92" s="4" t="n"/>
       <c r="E92" s="5" t="n"/>
       <c r="F92" s="2" t="n"/>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>모스피란</t>
+          <t>타스타</t>
         </is>
       </c>
       <c r="H92" s="5" t="n"/>
@@ -10765,27 +10586,19 @@
       <c r="N92" s="3" t="n"/>
       <c r="O92" s="7" t="n"/>
       <c r="P92" s="4" t="n"/>
-      <c r="Q92" s="3" t="inlineStr">
-        <is>
-          <t>벨리스플러스</t>
-        </is>
-      </c>
+      <c r="Q92" s="3" t="n"/>
       <c r="R92" s="5" t="inlineStr">
         <is>
-          <t>가능</t>
+          <t>조합 없음(섞지 말 것)</t>
         </is>
       </c>
       <c r="S92" s="3" t="n"/>
       <c r="T92" s="3" t="n"/>
       <c r="U92" s="3" t="n"/>
-      <c r="V92" s="4" t="inlineStr">
-        <is>
-          <t>가이드 내 위치: 탄저병 1순위</t>
-        </is>
-      </c>
+      <c r="V92" s="4" t="n"/>
       <c r="W92" s="4" t="inlineStr">
         <is>
-          <t>살균제(벨리스플러스) 학교 보유 중</t>
+          <t>살균제 조합 자체가 공식 자료에 없음. 살균제와 섞지 말 것</t>
         </is>
       </c>
       <c r="X92" s="3" t="n"/>
@@ -10796,32 +10609,32 @@
       <c r="AC92" s="9" t="n"/>
       <c r="AD92" s="9" t="n"/>
       <c r="AE92" s="3" t="n"/>
-      <c r="AF92" s="3" t="n"/>
+      <c r="AF92" s="5" t="n"/>
       <c r="AG92" s="4" t="n"/>
-      <c r="AH92" s="3" t="n"/>
+      <c r="AH92" s="5" t="n"/>
       <c r="AI92" s="3" t="n"/>
       <c r="AJ92" s="3" t="n"/>
       <c r="AK92" s="4" t="inlineStr">
         <is>
-          <t>PART 4. 혼용 가능 조합 &gt; 확인된 조합</t>
+          <t>PART 4. 혼용 가능 조합 &gt; 바이엘(코니도·타스타) 공식 혼용정보</t>
         </is>
       </c>
       <c r="AL92" s="4" t="inlineStr">
         <is>
-          <t>knco.co.kr/product/product_09 (경농 혼용안내, 고추 기준)</t>
+          <t>farmhannong.com/kor/product/mix-info (바이엘 혼용기술정보 2025)</t>
         </is>
       </c>
       <c r="AM92" s="9" t="n">
         <v>46283</v>
       </c>
     </row>
-    <row r="93" ht="33" customHeight="1">
+    <row r="93" ht="49" customHeight="1">
       <c r="A93" s="2" t="n">
         <v>92</v>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>혼용 가능 조합</t>
+          <t>혼용정보 확인결과</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -10829,16 +10642,12 @@
           <t>혼용정보</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>탄저병</t>
-        </is>
-      </c>
+      <c r="D93" s="4" t="n"/>
       <c r="E93" s="5" t="n"/>
       <c r="F93" s="2" t="n"/>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>모스피란</t>
+          <t>버픽스</t>
         </is>
       </c>
       <c r="H93" s="5" t="n"/>
@@ -10850,29 +10659,29 @@
       <c r="N93" s="3" t="n"/>
       <c r="O93" s="7" t="n"/>
       <c r="P93" s="4" t="n"/>
-      <c r="Q93" s="3" t="inlineStr">
-        <is>
-          <t>다놀라</t>
-        </is>
-      </c>
+      <c r="Q93" s="3" t="n"/>
       <c r="R93" s="5" t="inlineStr">
         <is>
-          <t>가능</t>
+          <t>미확인</t>
         </is>
       </c>
       <c r="S93" s="3" t="n"/>
-      <c r="T93" s="3" t="n"/>
-      <c r="U93" s="3" t="n"/>
+      <c r="T93" s="3" t="inlineStr">
+        <is>
+          <t>동방아그로</t>
+        </is>
+      </c>
+      <c r="U93" s="3" t="inlineStr">
+        <is>
+          <t>1644-7337</t>
+        </is>
+      </c>
       <c r="V93" s="4" t="inlineStr">
         <is>
-          <t>가이드 내 위치: 탄저병 2순위</t>
-        </is>
-      </c>
-      <c r="W93" s="4" t="inlineStr">
-        <is>
-          <t>살균제(다놀라) 학교 보유 중</t>
-        </is>
-      </c>
+          <t>자사 제품혼용표 도구에서 "버픽스"로 검색 → 전체 작물 통틀어 0건. 아직 표에 등록이 안 된 신제품으로 보임</t>
+        </is>
+      </c>
+      <c r="W93" s="4" t="n"/>
       <c r="X93" s="3" t="n"/>
       <c r="Y93" s="3" t="n"/>
       <c r="Z93" s="3" t="n"/>
@@ -10881,32 +10690,32 @@
       <c r="AC93" s="9" t="n"/>
       <c r="AD93" s="9" t="n"/>
       <c r="AE93" s="3" t="n"/>
-      <c r="AF93" s="3" t="n"/>
+      <c r="AF93" s="5" t="n"/>
       <c r="AG93" s="4" t="n"/>
-      <c r="AH93" s="3" t="n"/>
+      <c r="AH93" s="5" t="n"/>
       <c r="AI93" s="3" t="n"/>
       <c r="AJ93" s="3" t="n"/>
       <c r="AK93" s="4" t="inlineStr">
         <is>
-          <t>PART 4. 혼용 가능 조합 &gt; 확인된 조합</t>
+          <t>PART 4. 혼용 가능 조합 &gt; 나머지 3개(버픽스·무름반점뚝·강철비) 끝까지 확인한 결과</t>
         </is>
       </c>
       <c r="AL93" s="4" t="inlineStr">
         <is>
-          <t>knco.co.kr/product/product_09 (경농 혼용안내, 고추 기준)</t>
+          <t>dongbangagro.co.kr/product_combined.php · dae-yu.co.kr · enbio.co.kr</t>
         </is>
       </c>
       <c r="AM93" s="9" t="n">
         <v>46283</v>
       </c>
     </row>
-    <row r="94" ht="33" customHeight="1">
+    <row r="94" ht="49" customHeight="1">
       <c r="A94" s="2" t="n">
         <v>93</v>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>혼용 가능 조합</t>
+          <t>혼용정보 확인결과</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -10914,16 +10723,12 @@
           <t>혼용정보</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
-        <is>
-          <t>탄저병</t>
-        </is>
-      </c>
+      <c r="D94" s="4" t="n"/>
       <c r="E94" s="5" t="n"/>
       <c r="F94" s="2" t="n"/>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>모스피란</t>
+          <t>무름반점뚝</t>
         </is>
       </c>
       <c r="H94" s="5" t="n"/>
@@ -10935,29 +10740,25 @@
       <c r="N94" s="3" t="n"/>
       <c r="O94" s="7" t="n"/>
       <c r="P94" s="4" t="n"/>
-      <c r="Q94" s="3" t="inlineStr">
-        <is>
-          <t>벨쿠트</t>
-        </is>
-      </c>
+      <c r="Q94" s="3" t="n"/>
       <c r="R94" s="5" t="inlineStr">
         <is>
-          <t>가능</t>
+          <t>미확인</t>
         </is>
       </c>
       <c r="S94" s="3" t="n"/>
-      <c r="T94" s="3" t="n"/>
+      <c r="T94" s="3" t="inlineStr">
+        <is>
+          <t>대유</t>
+        </is>
+      </c>
       <c r="U94" s="3" t="n"/>
       <c r="V94" s="4" t="inlineStr">
         <is>
-          <t>가이드 내 위치: 탄저병 4순위</t>
-        </is>
-      </c>
-      <c r="W94" s="4" t="inlineStr">
-        <is>
-          <t>살균제(벨쿠트) 학교 보유 중</t>
-        </is>
-      </c>
+          <t>회사 사이트에 혼용정보 코너 자체가 없음. 제품 상세페이지에도 혼용 관련 내용 없음</t>
+        </is>
+      </c>
+      <c r="W94" s="4" t="n"/>
       <c r="X94" s="3" t="n"/>
       <c r="Y94" s="3" t="n"/>
       <c r="Z94" s="3" t="n"/>
@@ -10966,32 +10767,32 @@
       <c r="AC94" s="9" t="n"/>
       <c r="AD94" s="9" t="n"/>
       <c r="AE94" s="3" t="n"/>
-      <c r="AF94" s="3" t="n"/>
+      <c r="AF94" s="5" t="n"/>
       <c r="AG94" s="4" t="n"/>
-      <c r="AH94" s="3" t="n"/>
+      <c r="AH94" s="5" t="n"/>
       <c r="AI94" s="3" t="n"/>
       <c r="AJ94" s="3" t="n"/>
       <c r="AK94" s="4" t="inlineStr">
         <is>
-          <t>PART 4. 혼용 가능 조합 &gt; 확인된 조합</t>
+          <t>PART 4. 혼용 가능 조합 &gt; 나머지 3개(버픽스·무름반점뚝·강철비) 끝까지 확인한 결과</t>
         </is>
       </c>
       <c r="AL94" s="4" t="inlineStr">
         <is>
-          <t>knco.co.kr/product/product_09 (경농 혼용안내, 고추 기준)</t>
+          <t>dongbangagro.co.kr/product_combined.php · dae-yu.co.kr · enbio.co.kr</t>
         </is>
       </c>
       <c r="AM94" s="9" t="n">
         <v>46283</v>
       </c>
     </row>
-    <row r="95" ht="33" customHeight="1">
+    <row r="95" ht="49" customHeight="1">
       <c r="A95" s="2" t="n">
         <v>94</v>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>혼용 가능 조합</t>
+          <t>혼용정보 확인결과</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -10999,16 +10800,12 @@
           <t>혼용정보</t>
         </is>
       </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>세균점무늬병</t>
-        </is>
-      </c>
+      <c r="D95" s="4" t="n"/>
       <c r="E95" s="5" t="n"/>
       <c r="F95" s="2" t="n"/>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>모스피란</t>
+          <t>강철비</t>
         </is>
       </c>
       <c r="H95" s="5" t="n"/>
@@ -11020,29 +10817,29 @@
       <c r="N95" s="3" t="n"/>
       <c r="O95" s="7" t="n"/>
       <c r="P95" s="4" t="n"/>
-      <c r="Q95" s="3" t="inlineStr">
-        <is>
-          <t>가스란</t>
-        </is>
-      </c>
+      <c r="Q95" s="3" t="n"/>
       <c r="R95" s="5" t="inlineStr">
         <is>
-          <t>가능</t>
+          <t>미확인</t>
         </is>
       </c>
       <c r="S95" s="3" t="n"/>
-      <c r="T95" s="3" t="n"/>
-      <c r="U95" s="3" t="n"/>
+      <c r="T95" s="3" t="inlineStr">
+        <is>
+          <t>인바이오</t>
+        </is>
+      </c>
+      <c r="U95" s="3" t="inlineStr">
+        <is>
+          <t>031-477-6011</t>
+        </is>
+      </c>
       <c r="V95" s="4" t="inlineStr">
         <is>
-          <t>가이드 내 위치: 세균점무늬병 3순위</t>
-        </is>
-      </c>
-      <c r="W95" s="4" t="inlineStr">
-        <is>
-          <t>살균제(가스란) 학교 미보유 - 구매 필요</t>
-        </is>
-      </c>
+          <t>자사 혼용가부표(살균제용·살충제용 두 장, 도합 300개 이상 조합 수록)를 처음부터 끝까지 다 읽었으나 "강철비"는 어디에도 없음</t>
+        </is>
+      </c>
+      <c r="W95" s="4" t="n"/>
       <c r="X95" s="3" t="n"/>
       <c r="Y95" s="3" t="n"/>
       <c r="Z95" s="3" t="n"/>
@@ -11051,2391 +10848,1403 @@
       <c r="AC95" s="9" t="n"/>
       <c r="AD95" s="9" t="n"/>
       <c r="AE95" s="3" t="n"/>
-      <c r="AF95" s="3" t="n"/>
+      <c r="AF95" s="5" t="n"/>
       <c r="AG95" s="4" t="n"/>
-      <c r="AH95" s="3" t="n"/>
+      <c r="AH95" s="5" t="n"/>
       <c r="AI95" s="3" t="n"/>
       <c r="AJ95" s="3" t="n"/>
       <c r="AK95" s="4" t="inlineStr">
         <is>
-          <t>PART 4. 혼용 가능 조합 &gt; 확인된 조합</t>
+          <t>PART 4. 혼용 가능 조합 &gt; 나머지 3개(버픽스·무름반점뚝·강철비) 끝까지 확인한 결과</t>
         </is>
       </c>
       <c r="AL95" s="4" t="inlineStr">
         <is>
-          <t>knco.co.kr/product/product_09 (경농 혼용안내, 고추 기준)</t>
+          <t>dongbangagro.co.kr/product_combined.php · dae-yu.co.kr · enbio.co.kr</t>
         </is>
       </c>
       <c r="AM95" s="9" t="n">
         <v>46283</v>
       </c>
     </row>
-    <row r="96" ht="48" customHeight="1">
-      <c r="A96" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>혼용 가능 조합</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보</t>
-        </is>
-      </c>
-      <c r="D96" s="4" t="inlineStr">
-        <is>
-          <t>탄저병</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="n"/>
-      <c r="F96" s="2" t="n"/>
-      <c r="G96" s="3" t="inlineStr">
-        <is>
-          <t>코니도</t>
-        </is>
-      </c>
-      <c r="H96" s="5" t="n"/>
-      <c r="I96" s="5" t="n"/>
-      <c r="J96" s="4" t="n"/>
-      <c r="K96" s="3" t="n"/>
-      <c r="L96" s="6" t="n"/>
-      <c r="M96" s="3" t="n"/>
-      <c r="N96" s="3" t="n"/>
-      <c r="O96" s="7" t="n"/>
-      <c r="P96" s="4" t="n"/>
-      <c r="Q96" s="3" t="inlineStr">
-        <is>
-          <t>벨쿠트</t>
-        </is>
-      </c>
-      <c r="R96" s="5" t="inlineStr">
-        <is>
-          <t>가능</t>
-        </is>
-      </c>
-      <c r="S96" s="3" t="n"/>
-      <c r="T96" s="3" t="n"/>
-      <c r="U96" s="3" t="n"/>
-      <c r="V96" s="4" t="inlineStr">
-        <is>
-          <t>가이드 내 위치: 탄저병 4순위</t>
-        </is>
-      </c>
-      <c r="W96" s="4" t="inlineStr">
-        <is>
-          <t>살균제(벨쿠트) 학교 보유 중</t>
-        </is>
-      </c>
-      <c r="X96" s="3" t="n"/>
-      <c r="Y96" s="3" t="n"/>
-      <c r="Z96" s="3" t="n"/>
-      <c r="AA96" s="8" t="n"/>
-      <c r="AB96" s="9" t="n"/>
-      <c r="AC96" s="9" t="n"/>
-      <c r="AD96" s="9" t="n"/>
-      <c r="AE96" s="3" t="n"/>
-      <c r="AF96" s="3" t="n"/>
-      <c r="AG96" s="4" t="n"/>
-      <c r="AH96" s="3" t="n"/>
-      <c r="AI96" s="3" t="n"/>
-      <c r="AJ96" s="3" t="n"/>
-      <c r="AK96" s="4" t="inlineStr">
-        <is>
-          <t>PART 4. 혼용 가능 조합 &gt; 바이엘(코니도·타스타) 공식 혼용정보</t>
-        </is>
-      </c>
-      <c r="AL96" s="4" t="inlineStr">
-        <is>
-          <t>farmhannong.com/kor/product/mix-info (바이엘 혼용기술정보 2025)</t>
-        </is>
-      </c>
-      <c r="AM96" s="9" t="n">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="97" ht="48" customHeight="1">
-      <c r="A97" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>혼용 가능 조합</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보</t>
-        </is>
-      </c>
-      <c r="D97" s="4" t="n"/>
-      <c r="E97" s="5" t="n"/>
-      <c r="F97" s="2" t="n"/>
-      <c r="G97" s="3" t="inlineStr">
-        <is>
-          <t>타스타</t>
-        </is>
-      </c>
-      <c r="H97" s="5" t="n"/>
-      <c r="I97" s="5" t="n"/>
-      <c r="J97" s="4" t="n"/>
-      <c r="K97" s="3" t="n"/>
-      <c r="L97" s="6" t="n"/>
-      <c r="M97" s="3" t="n"/>
-      <c r="N97" s="3" t="n"/>
-      <c r="O97" s="7" t="n"/>
-      <c r="P97" s="4" t="n"/>
-      <c r="Q97" s="3" t="n"/>
-      <c r="R97" s="5" t="inlineStr">
-        <is>
-          <t>조합 없음(섞지 말 것)</t>
-        </is>
-      </c>
-      <c r="S97" s="3" t="n"/>
-      <c r="T97" s="3" t="n"/>
-      <c r="U97" s="3" t="n"/>
-      <c r="V97" s="4" t="n"/>
-      <c r="W97" s="4" t="inlineStr">
-        <is>
-          <t>살균제 조합 자체가 공식 자료에 없음. 살균제와 섞지 말 것</t>
-        </is>
-      </c>
-      <c r="X97" s="3" t="n"/>
-      <c r="Y97" s="3" t="n"/>
-      <c r="Z97" s="3" t="n"/>
-      <c r="AA97" s="8" t="n"/>
-      <c r="AB97" s="9" t="n"/>
-      <c r="AC97" s="9" t="n"/>
-      <c r="AD97" s="9" t="n"/>
-      <c r="AE97" s="3" t="n"/>
-      <c r="AF97" s="3" t="n"/>
-      <c r="AG97" s="4" t="n"/>
-      <c r="AH97" s="3" t="n"/>
-      <c r="AI97" s="3" t="n"/>
-      <c r="AJ97" s="3" t="n"/>
-      <c r="AK97" s="4" t="inlineStr">
-        <is>
-          <t>PART 4. 혼용 가능 조합 &gt; 바이엘(코니도·타스타) 공식 혼용정보</t>
-        </is>
-      </c>
-      <c r="AL97" s="4" t="inlineStr">
-        <is>
-          <t>farmhannong.com/kor/product/mix-info (바이엘 혼용기술정보 2025)</t>
-        </is>
-      </c>
-      <c r="AM97" s="9" t="n">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="98" ht="48" customHeight="1">
-      <c r="A98" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보 확인결과</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보</t>
-        </is>
-      </c>
-      <c r="D98" s="4" t="n"/>
-      <c r="E98" s="5" t="n"/>
-      <c r="F98" s="2" t="n"/>
-      <c r="G98" s="3" t="inlineStr">
-        <is>
-          <t>버픽스</t>
-        </is>
-      </c>
-      <c r="H98" s="5" t="n"/>
-      <c r="I98" s="5" t="n"/>
-      <c r="J98" s="4" t="n"/>
-      <c r="K98" s="3" t="n"/>
-      <c r="L98" s="6" t="n"/>
-      <c r="M98" s="3" t="n"/>
-      <c r="N98" s="3" t="n"/>
-      <c r="O98" s="7" t="n"/>
-      <c r="P98" s="4" t="n"/>
-      <c r="Q98" s="3" t="n"/>
-      <c r="R98" s="5" t="inlineStr">
-        <is>
-          <t>미확인</t>
-        </is>
-      </c>
-      <c r="S98" s="3" t="n"/>
-      <c r="T98" s="3" t="inlineStr">
-        <is>
-          <t>동방아그로</t>
-        </is>
-      </c>
-      <c r="U98" s="3" t="inlineStr">
-        <is>
-          <t>1644-7337</t>
-        </is>
-      </c>
-      <c r="V98" s="4" t="inlineStr">
-        <is>
-          <t>자사 제품혼용표 도구에서 "버픽스"로 검색 → 전체 작물 통틀어 0건. 아직 표에 등록이 안 된 신제품으로 보임</t>
-        </is>
-      </c>
-      <c r="W98" s="4" t="n"/>
-      <c r="X98" s="3" t="n"/>
-      <c r="Y98" s="3" t="n"/>
-      <c r="Z98" s="3" t="n"/>
-      <c r="AA98" s="8" t="n"/>
-      <c r="AB98" s="9" t="n"/>
-      <c r="AC98" s="9" t="n"/>
-      <c r="AD98" s="9" t="n"/>
-      <c r="AE98" s="3" t="n"/>
-      <c r="AF98" s="3" t="n"/>
-      <c r="AG98" s="4" t="n"/>
-      <c r="AH98" s="3" t="n"/>
-      <c r="AI98" s="3" t="n"/>
-      <c r="AJ98" s="3" t="n"/>
-      <c r="AK98" s="4" t="inlineStr">
-        <is>
-          <t>PART 4. 혼용 가능 조합 &gt; 나머지 3개(버픽스·무름반점뚝·강철비) 끝까지 확인한 결과</t>
-        </is>
-      </c>
-      <c r="AL98" s="4" t="inlineStr">
-        <is>
-          <t>dongbangagro.co.kr/product_combined.php · dae-yu.co.kr · enbio.co.kr</t>
-        </is>
-      </c>
-      <c r="AM98" s="9" t="n">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="99" ht="48" customHeight="1">
-      <c r="A99" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보 확인결과</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="n"/>
-      <c r="E99" s="5" t="n"/>
-      <c r="F99" s="2" t="n"/>
-      <c r="G99" s="3" t="inlineStr">
-        <is>
-          <t>무름반점뚝</t>
-        </is>
-      </c>
-      <c r="H99" s="5" t="n"/>
-      <c r="I99" s="5" t="n"/>
-      <c r="J99" s="4" t="n"/>
-      <c r="K99" s="3" t="n"/>
-      <c r="L99" s="6" t="n"/>
-      <c r="M99" s="3" t="n"/>
-      <c r="N99" s="3" t="n"/>
-      <c r="O99" s="7" t="n"/>
-      <c r="P99" s="4" t="n"/>
-      <c r="Q99" s="3" t="n"/>
-      <c r="R99" s="5" t="inlineStr">
-        <is>
-          <t>미확인</t>
-        </is>
-      </c>
-      <c r="S99" s="3" t="n"/>
-      <c r="T99" s="3" t="inlineStr">
-        <is>
-          <t>대유</t>
-        </is>
-      </c>
-      <c r="U99" s="3" t="n"/>
-      <c r="V99" s="4" t="inlineStr">
-        <is>
-          <t>회사 사이트에 혼용정보 코너 자체가 없음. 제품 상세페이지에도 혼용 관련 내용 없음</t>
-        </is>
-      </c>
-      <c r="W99" s="4" t="n"/>
-      <c r="X99" s="3" t="n"/>
-      <c r="Y99" s="3" t="n"/>
-      <c r="Z99" s="3" t="n"/>
-      <c r="AA99" s="8" t="n"/>
-      <c r="AB99" s="9" t="n"/>
-      <c r="AC99" s="9" t="n"/>
-      <c r="AD99" s="9" t="n"/>
-      <c r="AE99" s="3" t="n"/>
-      <c r="AF99" s="3" t="n"/>
-      <c r="AG99" s="4" t="n"/>
-      <c r="AH99" s="3" t="n"/>
-      <c r="AI99" s="3" t="n"/>
-      <c r="AJ99" s="3" t="n"/>
-      <c r="AK99" s="4" t="inlineStr">
-        <is>
-          <t>PART 4. 혼용 가능 조합 &gt; 나머지 3개(버픽스·무름반점뚝·강철비) 끝까지 확인한 결과</t>
-        </is>
-      </c>
-      <c r="AL99" s="4" t="inlineStr">
-        <is>
-          <t>dongbangagro.co.kr/product_combined.php · dae-yu.co.kr · enbio.co.kr</t>
-        </is>
-      </c>
-      <c r="AM99" s="9" t="n">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="100" ht="48" customHeight="1">
-      <c r="A100" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보 확인결과</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보</t>
-        </is>
-      </c>
-      <c r="D100" s="4" t="n"/>
-      <c r="E100" s="5" t="n"/>
-      <c r="F100" s="2" t="n"/>
-      <c r="G100" s="3" t="inlineStr">
-        <is>
-          <t>강철비</t>
-        </is>
-      </c>
-      <c r="H100" s="5" t="n"/>
-      <c r="I100" s="5" t="n"/>
-      <c r="J100" s="4" t="n"/>
-      <c r="K100" s="3" t="n"/>
-      <c r="L100" s="6" t="n"/>
-      <c r="M100" s="3" t="n"/>
-      <c r="N100" s="3" t="n"/>
-      <c r="O100" s="7" t="n"/>
-      <c r="P100" s="4" t="n"/>
-      <c r="Q100" s="3" t="n"/>
-      <c r="R100" s="5" t="inlineStr">
-        <is>
-          <t>미확인</t>
-        </is>
-      </c>
-      <c r="S100" s="3" t="n"/>
-      <c r="T100" s="3" t="inlineStr">
-        <is>
-          <t>인바이오</t>
-        </is>
-      </c>
-      <c r="U100" s="3" t="inlineStr">
-        <is>
-          <t>031-477-6011</t>
-        </is>
-      </c>
-      <c r="V100" s="4" t="inlineStr">
-        <is>
-          <t>자사 혼용가부표(살균제용·살충제용 두 장, 도합 300개 이상 조합 수록)를 처음부터 끝까지 다 읽었으나 "강철비"는 어디에도 없음</t>
-        </is>
-      </c>
-      <c r="W100" s="4" t="n"/>
-      <c r="X100" s="3" t="n"/>
-      <c r="Y100" s="3" t="n"/>
-      <c r="Z100" s="3" t="n"/>
-      <c r="AA100" s="8" t="n"/>
-      <c r="AB100" s="9" t="n"/>
-      <c r="AC100" s="9" t="n"/>
-      <c r="AD100" s="9" t="n"/>
-      <c r="AE100" s="3" t="n"/>
-      <c r="AF100" s="3" t="n"/>
-      <c r="AG100" s="4" t="n"/>
-      <c r="AH100" s="3" t="n"/>
-      <c r="AI100" s="3" t="n"/>
-      <c r="AJ100" s="3" t="n"/>
-      <c r="AK100" s="4" t="inlineStr">
-        <is>
-          <t>PART 4. 혼용 가능 조합 &gt; 나머지 3개(버픽스·무름반점뚝·강철비) 끝까지 확인한 결과</t>
-        </is>
-      </c>
-      <c r="AL100" s="4" t="inlineStr">
-        <is>
-          <t>dongbangagro.co.kr/product_combined.php · dae-yu.co.kr · enbio.co.kr</t>
-        </is>
-      </c>
-      <c r="AM100" s="9" t="n">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="101" ht="33" customHeight="1">
-      <c r="A101" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="n"/>
-      <c r="E101" s="5" t="n"/>
-      <c r="F101" s="2" t="n"/>
-      <c r="G101" s="3" t="n"/>
-      <c r="H101" s="5" t="n"/>
-      <c r="I101" s="5" t="n"/>
-      <c r="J101" s="4" t="n"/>
-      <c r="K101" s="3" t="n"/>
-      <c r="L101" s="6" t="n"/>
-      <c r="M101" s="3" t="n"/>
-      <c r="N101" s="3" t="n"/>
-      <c r="O101" s="7" t="n"/>
-      <c r="P101" s="4" t="n"/>
-      <c r="Q101" s="3" t="n"/>
-      <c r="R101" s="5" t="n"/>
-      <c r="S101" s="3" t="n"/>
-      <c r="T101" s="3" t="n"/>
-      <c r="U101" s="3" t="n"/>
-      <c r="V101" s="4" t="inlineStr">
-        <is>
-          <t>파프리카 재배 현장 방제 가이드</t>
-        </is>
-      </c>
-      <c r="W101" s="4" t="n"/>
-      <c r="X101" s="3" t="n"/>
-      <c r="Y101" s="3" t="n"/>
-      <c r="Z101" s="3" t="n"/>
-      <c r="AA101" s="8" t="n"/>
-      <c r="AB101" s="9" t="n"/>
-      <c r="AC101" s="9" t="n"/>
-      <c r="AD101" s="9" t="n"/>
-      <c r="AE101" s="3" t="n"/>
-      <c r="AF101" s="3" t="n"/>
-      <c r="AG101" s="4" t="n"/>
-      <c r="AH101" s="3" t="n"/>
-      <c r="AI101" s="3" t="n"/>
-      <c r="AJ101" s="3" t="n"/>
-      <c r="AK101" s="4" t="inlineStr">
-        <is>
-          <t>개요 &gt; 파프리카 재배 현장 방제 가이드</t>
-        </is>
-      </c>
-      <c r="AL101" s="4" t="n"/>
-      <c r="AM101" s="9" t="n"/>
-    </row>
-    <row r="102" ht="33" customHeight="1">
-      <c r="A102" s="2" t="n">
-        <v>101</v>
-      </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="D102" s="4" t="n"/>
-      <c r="E102" s="5" t="n"/>
-      <c r="F102" s="2" t="n"/>
-      <c r="G102" s="3" t="n"/>
-      <c r="H102" s="5" t="n"/>
-      <c r="I102" s="5" t="n"/>
-      <c r="J102" s="4" t="n"/>
-      <c r="K102" s="3" t="n"/>
-      <c r="L102" s="6" t="n"/>
-      <c r="M102" s="3" t="n"/>
-      <c r="N102" s="3" t="n"/>
-      <c r="O102" s="7" t="n"/>
-      <c r="P102" s="4" t="n"/>
-      <c r="Q102" s="3" t="n"/>
-      <c r="R102" s="5" t="n"/>
-      <c r="S102" s="3" t="n"/>
-      <c r="T102" s="3" t="n"/>
-      <c r="U102" s="3" t="n"/>
-      <c r="V102" s="4" t="inlineStr">
-        <is>
-          <t>연암대학교 스마트팜 유리온실</t>
-        </is>
-      </c>
-      <c r="W102" s="4" t="n"/>
-      <c r="X102" s="3" t="n"/>
-      <c r="Y102" s="3" t="n"/>
-      <c r="Z102" s="3" t="n"/>
-      <c r="AA102" s="8" t="n"/>
-      <c r="AB102" s="9" t="n"/>
-      <c r="AC102" s="9" t="n"/>
-      <c r="AD102" s="9" t="n"/>
-      <c r="AE102" s="3" t="n"/>
-      <c r="AF102" s="3" t="n"/>
-      <c r="AG102" s="4" t="n"/>
-      <c r="AH102" s="3" t="n"/>
-      <c r="AI102" s="3" t="n"/>
-      <c r="AJ102" s="3" t="n"/>
-      <c r="AK102" s="4" t="inlineStr">
-        <is>
-          <t>개요 &gt; 파프리카 재배 현장 방제 가이드</t>
-        </is>
-      </c>
-      <c r="AL102" s="4" t="n"/>
-      <c r="AM102" s="9" t="n"/>
-    </row>
-    <row r="103" ht="33" customHeight="1">
-      <c r="A103" s="2" t="n">
-        <v>102</v>
-      </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="n"/>
-      <c r="E103" s="5" t="n"/>
-      <c r="F103" s="2" t="n"/>
-      <c r="G103" s="3" t="n"/>
-      <c r="H103" s="5" t="n"/>
-      <c r="I103" s="5" t="n"/>
-      <c r="J103" s="4" t="n"/>
-      <c r="K103" s="3" t="n"/>
-      <c r="L103" s="6" t="n"/>
-      <c r="M103" s="3" t="n"/>
-      <c r="N103" s="3" t="n"/>
-      <c r="O103" s="7" t="n"/>
-      <c r="P103" s="4" t="n"/>
-      <c r="Q103" s="3" t="n"/>
-      <c r="R103" s="5" t="n"/>
-      <c r="S103" s="3" t="n"/>
-      <c r="T103" s="3" t="n"/>
-      <c r="U103" s="3" t="n"/>
-      <c r="V103" s="4" t="inlineStr">
-        <is>
-          <t>선정 기준: ① 학교 보유 약제  ②  여러 병해충에 겸용 가능한 약제</t>
-        </is>
-      </c>
-      <c r="W103" s="4" t="n"/>
-      <c r="X103" s="3" t="n"/>
-      <c r="Y103" s="3" t="n"/>
-      <c r="Z103" s="3" t="n"/>
-      <c r="AA103" s="8" t="n"/>
-      <c r="AB103" s="9" t="n"/>
-      <c r="AC103" s="9" t="n"/>
-      <c r="AD103" s="9" t="n"/>
-      <c r="AE103" s="3" t="n"/>
-      <c r="AF103" s="3" t="n"/>
-      <c r="AG103" s="4" t="n"/>
-      <c r="AH103" s="3" t="n"/>
-      <c r="AI103" s="3" t="n"/>
-      <c r="AJ103" s="3" t="n"/>
-      <c r="AK103" s="4" t="inlineStr">
-        <is>
-          <t>개요 &gt; 파프리카 재배 현장 방제 가이드</t>
-        </is>
-      </c>
-      <c r="AL103" s="4" t="n"/>
-      <c r="AM103" s="9" t="n"/>
-    </row>
-    <row r="104" ht="33" customHeight="1">
-      <c r="A104" s="2" t="n">
-        <v>103</v>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="D104" s="4" t="n"/>
-      <c r="E104" s="5" t="n"/>
-      <c r="F104" s="2" t="n"/>
-      <c r="G104" s="3" t="n"/>
-      <c r="H104" s="5" t="n"/>
-      <c r="I104" s="5" t="n"/>
-      <c r="J104" s="4" t="n"/>
-      <c r="K104" s="3" t="n"/>
-      <c r="L104" s="6" t="n"/>
-      <c r="M104" s="3" t="n"/>
-      <c r="N104" s="3" t="n"/>
-      <c r="O104" s="7" t="n"/>
-      <c r="P104" s="4" t="n"/>
-      <c r="Q104" s="3" t="n"/>
-      <c r="R104" s="5" t="n"/>
-      <c r="S104" s="3" t="n"/>
-      <c r="T104" s="3" t="n"/>
-      <c r="U104" s="3" t="n"/>
-      <c r="V104" s="4" t="inlineStr">
-        <is>
-          <t>같은 작용기작(코드)을 연속 사용하면 저항성이 생기니, 2회 이상 살포 시 표의 2~4순위로 바꿔가며 로테이션</t>
-        </is>
-      </c>
-      <c r="W104" s="4" t="n"/>
-      <c r="X104" s="3" t="n"/>
-      <c r="Y104" s="3" t="n"/>
-      <c r="Z104" s="3" t="n"/>
-      <c r="AA104" s="8" t="n"/>
-      <c r="AB104" s="9" t="n"/>
-      <c r="AC104" s="9" t="n"/>
-      <c r="AD104" s="9" t="n"/>
-      <c r="AE104" s="3" t="n"/>
-      <c r="AF104" s="3" t="n"/>
-      <c r="AG104" s="4" t="n"/>
-      <c r="AH104" s="3" t="n"/>
-      <c r="AI104" s="3" t="n"/>
-      <c r="AJ104" s="3" t="n"/>
-      <c r="AK104" s="4" t="inlineStr">
-        <is>
-          <t>개요 &gt; 파프리카 재배 현장 방제 가이드</t>
-        </is>
-      </c>
-      <c r="AL104" s="4" t="n"/>
-      <c r="AM104" s="9" t="n"/>
-    </row>
-    <row r="105" ht="33" customHeight="1">
-      <c r="A105" s="2" t="n">
-        <v>104</v>
-      </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="n"/>
-      <c r="E105" s="5" t="n"/>
-      <c r="F105" s="2" t="n"/>
-      <c r="G105" s="3" t="n"/>
-      <c r="H105" s="5" t="n"/>
-      <c r="I105" s="5" t="n"/>
-      <c r="J105" s="4" t="n"/>
-      <c r="K105" s="3" t="n"/>
-      <c r="L105" s="6" t="n"/>
-      <c r="M105" s="3" t="n"/>
-      <c r="N105" s="3" t="n"/>
-      <c r="O105" s="7" t="n"/>
-      <c r="P105" s="4" t="n"/>
-      <c r="Q105" s="3" t="n"/>
-      <c r="R105" s="5" t="n"/>
-      <c r="S105" s="3" t="n"/>
-      <c r="T105" s="3" t="n"/>
-      <c r="U105" s="3" t="n"/>
-      <c r="V105" s="4" t="inlineStr">
-        <is>
-          <t>총 14개 — 뒤쪽 병해충별 추천표에 나온 약제 중 현재 연암대 재고에 없는 것을 전부 모았습니다. 구매 시 참고하세요.</t>
-        </is>
-      </c>
-      <c r="W105" s="4" t="n"/>
-      <c r="X105" s="3" t="n"/>
-      <c r="Y105" s="3" t="n"/>
-      <c r="Z105" s="3" t="n"/>
-      <c r="AA105" s="8" t="n"/>
-      <c r="AB105" s="9" t="n"/>
-      <c r="AC105" s="9" t="n"/>
-      <c r="AD105" s="9" t="n"/>
-      <c r="AE105" s="3" t="n"/>
-      <c r="AF105" s="3" t="n"/>
-      <c r="AG105" s="4" t="n"/>
-      <c r="AH105" s="3" t="n"/>
-      <c r="AI105" s="3" t="n"/>
-      <c r="AJ105" s="3" t="n"/>
-      <c r="AK105" s="4" t="inlineStr">
-        <is>
-          <t>개요 &gt; 구매 약제 전체 목록 (추천표 중 학교 미보유분)</t>
-        </is>
-      </c>
-      <c r="AL105" s="4" t="n"/>
-      <c r="AM105" s="9" t="n"/>
-    </row>
-    <row r="106" ht="33" customHeight="1">
-      <c r="A106" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="D106" s="4" t="n"/>
-      <c r="E106" s="5" t="n"/>
-      <c r="F106" s="2" t="n"/>
-      <c r="G106" s="3" t="n"/>
-      <c r="H106" s="5" t="n"/>
-      <c r="I106" s="5" t="n"/>
-      <c r="J106" s="4" t="n"/>
-      <c r="K106" s="3" t="n"/>
-      <c r="L106" s="6" t="n"/>
-      <c r="M106" s="3" t="n"/>
-      <c r="N106" s="3" t="n"/>
-      <c r="O106" s="7" t="n"/>
-      <c r="P106" s="4" t="n"/>
-      <c r="Q106" s="3" t="n"/>
-      <c r="R106" s="5" t="n"/>
-      <c r="S106" s="3" t="n"/>
-      <c r="T106" s="3" t="n"/>
-      <c r="U106" s="3" t="n"/>
-      <c r="V106" s="4" t="inlineStr">
-        <is>
-          <t>유기농업자재 (친환경 공시자재)_보조 방제수단</t>
-        </is>
-      </c>
-      <c r="W106" s="4" t="n"/>
-      <c r="X106" s="3" t="n"/>
-      <c r="Y106" s="3" t="n"/>
-      <c r="Z106" s="3" t="n"/>
-      <c r="AA106" s="8" t="n"/>
-      <c r="AB106" s="9" t="n"/>
-      <c r="AC106" s="9" t="n"/>
-      <c r="AD106" s="9" t="n"/>
-      <c r="AE106" s="3" t="n"/>
-      <c r="AF106" s="3" t="n"/>
-      <c r="AG106" s="4" t="n"/>
-      <c r="AH106" s="3" t="n"/>
-      <c r="AI106" s="3" t="n"/>
-      <c r="AJ106" s="3" t="n"/>
-      <c r="AK106" s="4" t="inlineStr">
-        <is>
-          <t>개요 &gt; 구매 약제 전체 목록 (추천표 중 학교 미보유분)</t>
-        </is>
-      </c>
-      <c r="AL106" s="4" t="n"/>
-      <c r="AM106" s="9" t="n"/>
-    </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="2" t="n">
-        <v>106</v>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t>유기농업자재</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="n"/>
-      <c r="E107" s="5" t="n"/>
-      <c r="F107" s="2" t="n"/>
-      <c r="G107" s="3" t="n"/>
-      <c r="H107" s="5" t="n"/>
-      <c r="I107" s="5" t="n"/>
-      <c r="J107" s="4" t="n"/>
-      <c r="K107" s="3" t="n"/>
-      <c r="L107" s="6" t="n"/>
-      <c r="M107" s="3" t="n"/>
-      <c r="N107" s="3" t="n"/>
-      <c r="O107" s="7" t="n"/>
-      <c r="P107" s="4" t="n"/>
-      <c r="Q107" s="3" t="n"/>
-      <c r="R107" s="5" t="n"/>
-      <c r="S107" s="3" t="n"/>
-      <c r="T107" s="3" t="n"/>
-      <c r="U107" s="3" t="n"/>
-      <c r="V107" s="4" t="inlineStr">
-        <is>
-          <t>선정 기준</t>
-        </is>
-      </c>
-      <c r="W107" s="4" t="n"/>
-      <c r="X107" s="3" t="n"/>
-      <c r="Y107" s="3" t="n"/>
-      <c r="Z107" s="3" t="n"/>
-      <c r="AA107" s="8" t="n"/>
-      <c r="AB107" s="9" t="n"/>
-      <c r="AC107" s="9" t="n"/>
-      <c r="AD107" s="9" t="n"/>
-      <c r="AE107" s="3" t="n"/>
-      <c r="AF107" s="3" t="n"/>
-      <c r="AG107" s="4" t="n"/>
-      <c r="AH107" s="3" t="n"/>
-      <c r="AI107" s="3" t="n"/>
-      <c r="AJ107" s="3" t="n"/>
-      <c r="AK107" s="4" t="inlineStr">
-        <is>
-          <t>PART 3. 유기농업자재</t>
-        </is>
-      </c>
-      <c r="AL107" s="4" t="n"/>
-      <c r="AM107" s="9" t="n"/>
-    </row>
-    <row r="108" ht="33" customHeight="1">
-      <c r="A108" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="inlineStr">
-        <is>
-          <t>유기농업자재</t>
-        </is>
-      </c>
-      <c r="D108" s="4" t="n"/>
-      <c r="E108" s="5" t="n"/>
-      <c r="F108" s="2" t="n"/>
-      <c r="G108" s="3" t="n"/>
-      <c r="H108" s="5" t="n"/>
-      <c r="I108" s="5" t="n"/>
-      <c r="J108" s="4" t="n"/>
-      <c r="K108" s="3" t="n"/>
-      <c r="L108" s="6" t="n"/>
-      <c r="M108" s="3" t="n"/>
-      <c r="N108" s="3" t="n"/>
-      <c r="O108" s="7" t="n"/>
-      <c r="P108" s="4" t="n"/>
-      <c r="Q108" s="3" t="n"/>
-      <c r="R108" s="5" t="n"/>
-      <c r="S108" s="3" t="n"/>
-      <c r="T108" s="3" t="n"/>
-      <c r="U108" s="3" t="n"/>
-      <c r="V108" s="4" t="inlineStr">
-        <is>
-          <t>① 이 가이드가 다루는 고추 병해충(꽃노랑총채벌레·온실가루이·복숭아혹진딧물)에 실제 방제시험 데이터가 있는 제품만</t>
-        </is>
-      </c>
-      <c r="W108" s="4" t="n"/>
-      <c r="X108" s="3" t="n"/>
-      <c r="Y108" s="3" t="n"/>
-      <c r="Z108" s="3" t="n"/>
-      <c r="AA108" s="8" t="n"/>
-      <c r="AB108" s="9" t="n"/>
-      <c r="AC108" s="9" t="n"/>
-      <c r="AD108" s="9" t="n"/>
-      <c r="AE108" s="3" t="n"/>
-      <c r="AF108" s="3" t="n"/>
-      <c r="AG108" s="4" t="n"/>
-      <c r="AH108" s="3" t="n"/>
-      <c r="AI108" s="3" t="n"/>
-      <c r="AJ108" s="3" t="n"/>
-      <c r="AK108" s="4" t="inlineStr">
-        <is>
-          <t>PART 3. 유기농업자재</t>
-        </is>
-      </c>
-      <c r="AL108" s="4" t="n"/>
-      <c r="AM108" s="9" t="n"/>
-    </row>
-    <row r="109" ht="33" customHeight="1">
-      <c r="A109" s="2" t="n">
-        <v>108</v>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="inlineStr">
-        <is>
-          <t>유기농업자재</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="n"/>
-      <c r="E109" s="5" t="n"/>
-      <c r="F109" s="2" t="n"/>
-      <c r="G109" s="3" t="n"/>
-      <c r="H109" s="5" t="n"/>
-      <c r="I109" s="5" t="n"/>
-      <c r="J109" s="4" t="n"/>
-      <c r="K109" s="3" t="n"/>
-      <c r="L109" s="6" t="n"/>
-      <c r="M109" s="3" t="n"/>
-      <c r="N109" s="3" t="n"/>
-      <c r="O109" s="7" t="n"/>
-      <c r="P109" s="4" t="n"/>
-      <c r="Q109" s="3" t="n"/>
-      <c r="R109" s="5" t="n"/>
-      <c r="S109" s="3" t="n"/>
-      <c r="T109" s="3" t="n"/>
-      <c r="U109" s="3" t="n"/>
-      <c r="V109" s="4" t="inlineStr">
-        <is>
-          <t>② 국립농산물품질관리원 공시자재(naqs.go.kr)에 정식 등재된 것만 — 출처 불명확한 자료는 제외</t>
-        </is>
-      </c>
-      <c r="W109" s="4" t="n"/>
-      <c r="X109" s="3" t="n"/>
-      <c r="Y109" s="3" t="n"/>
-      <c r="Z109" s="3" t="n"/>
-      <c r="AA109" s="8" t="n"/>
-      <c r="AB109" s="9" t="n"/>
-      <c r="AC109" s="9" t="n"/>
-      <c r="AD109" s="9" t="n"/>
-      <c r="AE109" s="3" t="n"/>
-      <c r="AF109" s="3" t="n"/>
-      <c r="AG109" s="4" t="n"/>
-      <c r="AH109" s="3" t="n"/>
-      <c r="AI109" s="3" t="n"/>
-      <c r="AJ109" s="3" t="n"/>
-      <c r="AK109" s="4" t="inlineStr">
-        <is>
-          <t>PART 3. 유기농업자재</t>
-        </is>
-      </c>
-      <c r="AL109" s="4" t="n"/>
-      <c r="AM109" s="9" t="n"/>
-    </row>
-    <row r="110" ht="108" customHeight="1">
-      <c r="A110" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="inlineStr">
-        <is>
-          <t>유기농업자재</t>
-        </is>
-      </c>
-      <c r="D110" s="4" t="n"/>
-      <c r="E110" s="5" t="n"/>
-      <c r="F110" s="2" t="n"/>
-      <c r="G110" s="3" t="n"/>
-      <c r="H110" s="5" t="n"/>
-      <c r="I110" s="5" t="n"/>
-      <c r="J110" s="4" t="n"/>
-      <c r="K110" s="3" t="n"/>
-      <c r="L110" s="6" t="n"/>
-      <c r="M110" s="3" t="n"/>
-      <c r="N110" s="3" t="n"/>
-      <c r="O110" s="7" t="n"/>
-      <c r="P110" s="4" t="n"/>
-      <c r="Q110" s="3" t="n"/>
-      <c r="R110" s="5" t="n"/>
-      <c r="S110" s="3" t="n"/>
-      <c r="T110" s="3" t="n"/>
-      <c r="U110" s="3" t="n"/>
-      <c r="V110" s="4" t="inlineStr">
-        <is>
-          <t>아래 2개 제품은 국립농산물품질관리원 유기농업자재 공시현황(naqs.go.kr)에 등재된 병해충관리용 공시자재입니다. 정식 등록 '농약'이 아니라 효능시험을 거쳐 공시된 친환경 자재이며, 본 가이드의 고추 재배 병해충(꽃노랑총채벌레·온실가루이·복숭아혹진딧물)과 직접 관련된 항목만 정리했습니다. 무농약·유기재배 인증 포장이나 수확 임박 시기, 로테이션 보조 수단으로 참고하시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="W110" s="4" t="n"/>
-      <c r="X110" s="3" t="n"/>
-      <c r="Y110" s="3" t="n"/>
-      <c r="Z110" s="3" t="n"/>
-      <c r="AA110" s="8" t="n"/>
-      <c r="AB110" s="9" t="n"/>
-      <c r="AC110" s="9" t="n"/>
-      <c r="AD110" s="9" t="n"/>
-      <c r="AE110" s="3" t="n"/>
-      <c r="AF110" s="3" t="n"/>
-      <c r="AG110" s="4" t="n"/>
-      <c r="AH110" s="3" t="n"/>
-      <c r="AI110" s="3" t="n"/>
-      <c r="AJ110" s="3" t="n"/>
-      <c r="AK110" s="4" t="inlineStr">
-        <is>
-          <t>PART 3. 유기농업자재</t>
-        </is>
-      </c>
-      <c r="AL110" s="4" t="n"/>
-      <c r="AM110" s="9" t="n"/>
-    </row>
-    <row r="111" ht="63" customHeight="1">
-      <c r="A111" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t>유기농업자재</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="n"/>
-      <c r="E111" s="5" t="n"/>
-      <c r="F111" s="2" t="n"/>
-      <c r="G111" s="3" t="n"/>
-      <c r="H111" s="5" t="n"/>
-      <c r="I111" s="5" t="n"/>
-      <c r="J111" s="4" t="n"/>
-      <c r="K111" s="3" t="n"/>
-      <c r="L111" s="6" t="n"/>
-      <c r="M111" s="3" t="n"/>
-      <c r="N111" s="3" t="n"/>
-      <c r="O111" s="7" t="n"/>
-      <c r="P111" s="4" t="n"/>
-      <c r="Q111" s="3" t="n"/>
-      <c r="R111" s="5" t="n"/>
-      <c r="S111" s="3" t="n"/>
-      <c r="T111" s="3" t="n"/>
-      <c r="U111" s="3" t="n"/>
-      <c r="V111" s="4" t="inlineStr">
-        <is>
-          <t>⚠ 화학농약이 아닌 유기농업자재입니다 — 등록 농약과 안전사용기준·법적 지위가 다릅니다. 표시구분 '농약효과'는 효능시험 결과일 뿐 '농약등록'과는 별개이며, 두 제품 모두 농약/비료 등록여부는 '없음'입니다.</t>
-        </is>
-      </c>
-      <c r="W111" s="4" t="n"/>
-      <c r="X111" s="3" t="n"/>
-      <c r="Y111" s="3" t="n"/>
-      <c r="Z111" s="3" t="n"/>
-      <c r="AA111" s="8" t="n"/>
-      <c r="AB111" s="9" t="n"/>
-      <c r="AC111" s="9" t="n"/>
-      <c r="AD111" s="9" t="n"/>
-      <c r="AE111" s="3" t="n"/>
-      <c r="AF111" s="3" t="n"/>
-      <c r="AG111" s="4" t="n"/>
-      <c r="AH111" s="3" t="n"/>
-      <c r="AI111" s="3" t="n"/>
-      <c r="AJ111" s="3" t="n"/>
-      <c r="AK111" s="4" t="inlineStr">
-        <is>
-          <t>PART 3. 유기농업자재</t>
-        </is>
-      </c>
-      <c r="AL111" s="4" t="n"/>
-      <c r="AM111" s="9" t="n"/>
-    </row>
-    <row r="112" ht="33" customHeight="1">
-      <c r="A112" s="2" t="n">
-        <v>111</v>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="inlineStr">
-        <is>
-          <t>유기농업자재</t>
-        </is>
-      </c>
-      <c r="D112" s="4" t="n"/>
-      <c r="E112" s="5" t="n"/>
-      <c r="F112" s="2" t="n"/>
-      <c r="G112" s="3" t="n"/>
-      <c r="H112" s="5" t="n"/>
-      <c r="I112" s="5" t="n"/>
-      <c r="J112" s="4" t="n"/>
-      <c r="K112" s="3" t="n"/>
-      <c r="L112" s="6" t="n"/>
-      <c r="M112" s="3" t="n"/>
-      <c r="N112" s="3" t="n"/>
-      <c r="O112" s="7" t="n"/>
-      <c r="P112" s="4" t="n"/>
-      <c r="Q112" s="3" t="n"/>
-      <c r="R112" s="5" t="n"/>
-      <c r="S112" s="3" t="n"/>
-      <c r="T112" s="3" t="n"/>
-      <c r="U112" s="3" t="n"/>
-      <c r="V112" s="4" t="inlineStr">
-        <is>
-          <t>고추 관련 사용법: 꽃노랑총채벌레, 발생초기, 1,000배 희석, 경엽처리 — 무처리구 대비 방제가 61.7%</t>
-        </is>
-      </c>
-      <c r="W112" s="4" t="n"/>
-      <c r="X112" s="3" t="n"/>
-      <c r="Y112" s="3" t="n"/>
-      <c r="Z112" s="3" t="n"/>
-      <c r="AA112" s="8" t="n"/>
-      <c r="AB112" s="9" t="n"/>
-      <c r="AC112" s="9" t="n"/>
-      <c r="AD112" s="9" t="n"/>
-      <c r="AE112" s="3" t="n"/>
-      <c r="AF112" s="3" t="n"/>
-      <c r="AG112" s="4" t="n"/>
-      <c r="AH112" s="3" t="n"/>
-      <c r="AI112" s="3" t="n"/>
-      <c r="AJ112" s="3" t="n"/>
-      <c r="AK112" s="4" t="inlineStr">
-        <is>
-          <t>PART 3. 유기농업자재 &gt; 한방싹충도사 (병해충관리용)</t>
-        </is>
-      </c>
-      <c r="AL112" s="4" t="n"/>
-      <c r="AM112" s="9" t="n"/>
-    </row>
-    <row r="113" ht="63" customHeight="1">
-      <c r="A113" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="inlineStr">
-        <is>
-          <t>유기농업자재</t>
-        </is>
-      </c>
-      <c r="D113" s="4" t="n"/>
-      <c r="E113" s="5" t="n"/>
-      <c r="F113" s="2" t="n"/>
-      <c r="G113" s="3" t="n"/>
-      <c r="H113" s="5" t="n"/>
-      <c r="I113" s="5" t="n"/>
-      <c r="J113" s="4" t="n"/>
-      <c r="K113" s="3" t="n"/>
-      <c r="L113" s="6" t="n"/>
-      <c r="M113" s="3" t="n"/>
-      <c r="N113" s="3" t="n"/>
-      <c r="O113" s="7" t="n"/>
-      <c r="P113" s="4" t="n"/>
-      <c r="Q113" s="3" t="n"/>
-      <c r="R113" s="5" t="n"/>
-      <c r="S113" s="3" t="n"/>
-      <c r="T113" s="3" t="n"/>
-      <c r="U113" s="3" t="n"/>
-      <c r="V113" s="4" t="inlineStr">
-        <is>
-          <t>그 외 방제효과: 딸기 점박이응애 67.5% · 배 조팝나무진딧물 77.4% · 양배추 배추흰나비 65.9% · 복숭아 복숭아순나방 60.0% · 포도 꽃매미 62.8% · 사과 갈색날개매미충 65.8% · 오이 온실가루이 60%이상 · 감귤 이세리아깍지벌레 60%이상</t>
-        </is>
-      </c>
-      <c r="W113" s="4" t="n"/>
-      <c r="X113" s="3" t="n"/>
-      <c r="Y113" s="3" t="n"/>
-      <c r="Z113" s="3" t="n"/>
-      <c r="AA113" s="8" t="n"/>
-      <c r="AB113" s="9" t="n"/>
-      <c r="AC113" s="9" t="n"/>
-      <c r="AD113" s="9" t="n"/>
-      <c r="AE113" s="3" t="n"/>
-      <c r="AF113" s="3" t="n"/>
-      <c r="AG113" s="4" t="n"/>
-      <c r="AH113" s="3" t="n"/>
-      <c r="AI113" s="3" t="n"/>
-      <c r="AJ113" s="3" t="n"/>
-      <c r="AK113" s="4" t="inlineStr">
-        <is>
-          <t>PART 3. 유기농업자재 &gt; 한방싹충도사 (병해충관리용)</t>
-        </is>
-      </c>
-      <c r="AL113" s="4" t="n"/>
-      <c r="AM113" s="9" t="n"/>
-    </row>
-    <row r="114" ht="33" customHeight="1">
-      <c r="A114" s="2" t="n">
-        <v>113</v>
-      </c>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="inlineStr">
-        <is>
-          <t>유기농업자재</t>
-        </is>
-      </c>
-      <c r="D114" s="4" t="n"/>
-      <c r="E114" s="5" t="n"/>
-      <c r="F114" s="2" t="n"/>
-      <c r="G114" s="3" t="n"/>
-      <c r="H114" s="5" t="n"/>
-      <c r="I114" s="5" t="n"/>
-      <c r="J114" s="4" t="n"/>
-      <c r="K114" s="3" t="n"/>
-      <c r="L114" s="6" t="n"/>
-      <c r="M114" s="3" t="n"/>
-      <c r="N114" s="3" t="n"/>
-      <c r="O114" s="7" t="n"/>
-      <c r="P114" s="4" t="n"/>
-      <c r="Q114" s="3" t="n"/>
-      <c r="R114" s="5" t="n"/>
-      <c r="S114" s="3" t="n"/>
-      <c r="T114" s="3" t="n"/>
-      <c r="U114" s="3" t="n"/>
-      <c r="V114" s="4" t="inlineStr">
-        <is>
-          <t>고추 관련 사용법: 복숭아혹진딧물, 생육기, 1,000배 희석, 경엽처리 — 무처리구 대비 방제가 50% 이상</t>
-        </is>
-      </c>
-      <c r="W114" s="4" t="n"/>
-      <c r="X114" s="3" t="n"/>
-      <c r="Y114" s="3" t="n"/>
-      <c r="Z114" s="3" t="n"/>
-      <c r="AA114" s="8" t="n"/>
-      <c r="AB114" s="9" t="n"/>
-      <c r="AC114" s="9" t="n"/>
-      <c r="AD114" s="9" t="n"/>
-      <c r="AE114" s="3" t="n"/>
-      <c r="AF114" s="3" t="n"/>
-      <c r="AG114" s="4" t="n"/>
-      <c r="AH114" s="3" t="n"/>
-      <c r="AI114" s="3" t="n"/>
-      <c r="AJ114" s="3" t="n"/>
-      <c r="AK114" s="4" t="inlineStr">
-        <is>
-          <t>PART 3. 유기농업자재 &gt; 뉴응칠이 (병해충관리용)</t>
-        </is>
-      </c>
-      <c r="AL114" s="4" t="n"/>
-      <c r="AM114" s="9" t="n"/>
-    </row>
-    <row r="115" ht="48" customHeight="1">
-      <c r="A115" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="inlineStr">
-        <is>
-          <t>유기농업자재</t>
-        </is>
-      </c>
-      <c r="D115" s="4" t="n"/>
-      <c r="E115" s="5" t="n"/>
-      <c r="F115" s="2" t="n"/>
-      <c r="G115" s="3" t="n"/>
-      <c r="H115" s="5" t="n"/>
-      <c r="I115" s="5" t="n"/>
-      <c r="J115" s="4" t="n"/>
-      <c r="K115" s="3" t="n"/>
-      <c r="L115" s="6" t="n"/>
-      <c r="M115" s="3" t="n"/>
-      <c r="N115" s="3" t="n"/>
-      <c r="O115" s="7" t="n"/>
-      <c r="P115" s="4" t="n"/>
-      <c r="Q115" s="3" t="n"/>
-      <c r="R115" s="5" t="n"/>
-      <c r="S115" s="3" t="n"/>
-      <c r="T115" s="3" t="n"/>
-      <c r="U115" s="3" t="n"/>
-      <c r="V115" s="4" t="inlineStr">
-        <is>
-          <t>그 외 방제효과(오이 시험): 꽃노랑총채벌레·아메리카잎굴파리·온실가루이·흰가루병 — 무처리구 대비 50% 이상 / 블루베리 미국선녀벌레 50% 이상</t>
-        </is>
-      </c>
-      <c r="W115" s="4" t="n"/>
-      <c r="X115" s="3" t="n"/>
-      <c r="Y115" s="3" t="n"/>
-      <c r="Z115" s="3" t="n"/>
-      <c r="AA115" s="8" t="n"/>
-      <c r="AB115" s="9" t="n"/>
-      <c r="AC115" s="9" t="n"/>
-      <c r="AD115" s="9" t="n"/>
-      <c r="AE115" s="3" t="n"/>
-      <c r="AF115" s="3" t="n"/>
-      <c r="AG115" s="4" t="n"/>
-      <c r="AH115" s="3" t="n"/>
-      <c r="AI115" s="3" t="n"/>
-      <c r="AJ115" s="3" t="n"/>
-      <c r="AK115" s="4" t="inlineStr">
-        <is>
-          <t>PART 3. 유기농업자재 &gt; 뉴응칠이 (병해충관리용)</t>
-        </is>
-      </c>
-      <c r="AL115" s="4" t="n"/>
-      <c r="AM115" s="9" t="n"/>
-    </row>
-    <row r="116" ht="48" customHeight="1">
-      <c r="A116" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="inlineStr">
-        <is>
-          <t>유기농업자재</t>
-        </is>
-      </c>
-      <c r="D116" s="4" t="n"/>
-      <c r="E116" s="5" t="n"/>
-      <c r="F116" s="2" t="n"/>
-      <c r="G116" s="3" t="n"/>
-      <c r="H116" s="5" t="n"/>
-      <c r="I116" s="5" t="n"/>
-      <c r="J116" s="4" t="n"/>
-      <c r="K116" s="3" t="n"/>
-      <c r="L116" s="6" t="n"/>
-      <c r="M116" s="3" t="n"/>
-      <c r="N116" s="3" t="n"/>
-      <c r="O116" s="7" t="n"/>
-      <c r="P116" s="4" t="n"/>
-      <c r="Q116" s="3" t="n"/>
-      <c r="R116" s="5" t="n"/>
-      <c r="S116" s="3" t="n"/>
-      <c r="T116" s="3" t="n"/>
-      <c r="U116" s="3" t="n"/>
-      <c r="V116" s="4" t="inlineStr">
-        <is>
-          <t>주의: 접촉성 제제(잎 뒷면까지 흠뻑 살포) · 강알칼리성 제제·석회보르도액·유황합제 혼용 금지 · 꿀벌 활동에 영향 가능</t>
-        </is>
-      </c>
-      <c r="W116" s="4" t="n"/>
-      <c r="X116" s="3" t="n"/>
-      <c r="Y116" s="3" t="n"/>
-      <c r="Z116" s="3" t="n"/>
-      <c r="AA116" s="8" t="n"/>
-      <c r="AB116" s="9" t="n"/>
-      <c r="AC116" s="9" t="n"/>
-      <c r="AD116" s="9" t="n"/>
-      <c r="AE116" s="3" t="n"/>
-      <c r="AF116" s="3" t="n"/>
-      <c r="AG116" s="4" t="n"/>
-      <c r="AH116" s="3" t="n"/>
-      <c r="AI116" s="3" t="n"/>
-      <c r="AJ116" s="3" t="n"/>
-      <c r="AK116" s="4" t="inlineStr">
-        <is>
-          <t>PART 3. 유기농업자재 &gt; 뉴응칠이 (병해충관리용)</t>
-        </is>
-      </c>
-      <c r="AL116" s="4" t="n"/>
-      <c r="AM116" s="9" t="n"/>
-    </row>
-    <row r="117" ht="48" customHeight="1">
-      <c r="A117" s="2" t="n">
-        <v>116</v>
-      </c>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="inlineStr">
-        <is>
-          <t>유기농업자재</t>
-        </is>
-      </c>
-      <c r="D117" s="4" t="n"/>
-      <c r="E117" s="5" t="n"/>
-      <c r="F117" s="2" t="n"/>
-      <c r="G117" s="3" t="n"/>
-      <c r="H117" s="5" t="n"/>
-      <c r="I117" s="5" t="n"/>
-      <c r="J117" s="4" t="n"/>
-      <c r="K117" s="3" t="n"/>
-      <c r="L117" s="6" t="n"/>
-      <c r="M117" s="3" t="n"/>
-      <c r="N117" s="3" t="n"/>
-      <c r="O117" s="7" t="n"/>
-      <c r="P117" s="4" t="n"/>
-      <c r="Q117" s="3" t="n"/>
-      <c r="R117" s="5" t="n"/>
-      <c r="S117" s="3" t="n"/>
-      <c r="T117" s="3" t="n"/>
-      <c r="U117" s="3" t="n"/>
-      <c r="V117" s="4" t="inlineStr">
-        <is>
-          <t>자료 출처: 국립농산물품질관리원 유기농업자재 공시현황(naqs.go.kr), 조회일 2026-09-18. 실제 사용 전 최신 공시정보 재확인 요망.</t>
-        </is>
-      </c>
-      <c r="W117" s="4" t="n"/>
-      <c r="X117" s="3" t="n"/>
-      <c r="Y117" s="3" t="n"/>
-      <c r="Z117" s="3" t="n"/>
-      <c r="AA117" s="8" t="n"/>
-      <c r="AB117" s="9" t="n"/>
-      <c r="AC117" s="9" t="n"/>
-      <c r="AD117" s="9" t="n"/>
-      <c r="AE117" s="3" t="n"/>
-      <c r="AF117" s="3" t="n"/>
-      <c r="AG117" s="4" t="n"/>
-      <c r="AH117" s="3" t="n"/>
-      <c r="AI117" s="3" t="n"/>
-      <c r="AJ117" s="3" t="n"/>
-      <c r="AK117" s="4" t="inlineStr">
-        <is>
-          <t>PART 3. 유기농업자재 &gt; 뉴응칠이 (병해충관리용)</t>
-        </is>
-      </c>
-      <c r="AL117" s="4" t="n"/>
-      <c r="AM117" s="9" t="n">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="2" t="n">
-        <v>117</v>
-      </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보</t>
-        </is>
-      </c>
-      <c r="D118" s="4" t="n"/>
-      <c r="E118" s="5" t="n"/>
-      <c r="F118" s="2" t="n"/>
-      <c r="G118" s="3" t="n"/>
-      <c r="H118" s="5" t="n"/>
-      <c r="I118" s="5" t="n"/>
-      <c r="J118" s="4" t="n"/>
-      <c r="K118" s="3" t="n"/>
-      <c r="L118" s="6" t="n"/>
-      <c r="M118" s="3" t="n"/>
-      <c r="N118" s="3" t="n"/>
-      <c r="O118" s="7" t="n"/>
-      <c r="P118" s="4" t="n"/>
-      <c r="Q118" s="3" t="n"/>
-      <c r="R118" s="5" t="n"/>
-      <c r="S118" s="3" t="n"/>
-      <c r="T118" s="3" t="n"/>
-      <c r="U118" s="3" t="n"/>
-      <c r="V118" s="4" t="inlineStr">
-        <is>
-          <t>선정 기준</t>
-        </is>
-      </c>
-      <c r="W118" s="4" t="n"/>
-      <c r="X118" s="3" t="n"/>
-      <c r="Y118" s="3" t="n"/>
-      <c r="Z118" s="3" t="n"/>
-      <c r="AA118" s="8" t="n"/>
-      <c r="AB118" s="9" t="n"/>
-      <c r="AC118" s="9" t="n"/>
-      <c r="AD118" s="9" t="n"/>
-      <c r="AE118" s="3" t="n"/>
-      <c r="AF118" s="3" t="n"/>
-      <c r="AG118" s="4" t="n"/>
-      <c r="AH118" s="3" t="n"/>
-      <c r="AI118" s="3" t="n"/>
-      <c r="AJ118" s="3" t="n"/>
-      <c r="AK118" s="4" t="inlineStr">
-        <is>
-          <t>PART 4. 혼용 가능 조합</t>
-        </is>
-      </c>
-      <c r="AL118" s="4" t="n"/>
-      <c r="AM118" s="9" t="n"/>
-    </row>
-    <row r="119" ht="33" customHeight="1">
-      <c r="A119" s="2" t="n">
-        <v>118</v>
-      </c>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보</t>
-        </is>
-      </c>
-      <c r="D119" s="4" t="n"/>
-      <c r="E119" s="5" t="n"/>
-      <c r="F119" s="2" t="n"/>
-      <c r="G119" s="3" t="n"/>
-      <c r="H119" s="5" t="n"/>
-      <c r="I119" s="5" t="n"/>
-      <c r="J119" s="4" t="n"/>
-      <c r="K119" s="3" t="n"/>
-      <c r="L119" s="6" t="n"/>
-      <c r="M119" s="3" t="n"/>
-      <c r="N119" s="3" t="n"/>
-      <c r="O119" s="7" t="n"/>
-      <c r="P119" s="4" t="n"/>
-      <c r="Q119" s="3" t="n"/>
-      <c r="R119" s="5" t="n"/>
-      <c r="S119" s="3" t="n"/>
-      <c r="T119" s="3" t="n"/>
-      <c r="U119" s="3" t="n"/>
-      <c r="V119" s="4" t="inlineStr">
-        <is>
-          <t>① 가이드의 교내 보유 약제 살충제를 기준 축으로 삼음 — 학교가 실제로 쓸 확률이 가장 높은 제품이라서</t>
-        </is>
-      </c>
-      <c r="W119" s="4" t="n"/>
-      <c r="X119" s="3" t="n"/>
-      <c r="Y119" s="3" t="n"/>
-      <c r="Z119" s="3" t="n"/>
-      <c r="AA119" s="8" t="n"/>
-      <c r="AB119" s="9" t="n"/>
-      <c r="AC119" s="9" t="n"/>
-      <c r="AD119" s="9" t="n"/>
-      <c r="AE119" s="3" t="n"/>
-      <c r="AF119" s="3" t="n"/>
-      <c r="AG119" s="4" t="n"/>
-      <c r="AH119" s="3" t="n"/>
-      <c r="AI119" s="3" t="n"/>
-      <c r="AJ119" s="3" t="n"/>
-      <c r="AK119" s="4" t="inlineStr">
-        <is>
-          <t>PART 4. 혼용 가능 조합</t>
-        </is>
-      </c>
-      <c r="AL119" s="4" t="n"/>
-      <c r="AM119" s="9" t="n"/>
-    </row>
-    <row r="120" ht="33" customHeight="1">
-      <c r="A120" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보</t>
-        </is>
-      </c>
-      <c r="D120" s="4" t="n"/>
-      <c r="E120" s="5" t="n"/>
-      <c r="F120" s="2" t="n"/>
-      <c r="G120" s="3" t="n"/>
-      <c r="H120" s="5" t="n"/>
-      <c r="I120" s="5" t="n"/>
-      <c r="J120" s="4" t="n"/>
-      <c r="K120" s="3" t="n"/>
-      <c r="L120" s="6" t="n"/>
-      <c r="M120" s="3" t="n"/>
-      <c r="N120" s="3" t="n"/>
-      <c r="O120" s="7" t="n"/>
-      <c r="P120" s="4" t="n"/>
-      <c r="Q120" s="3" t="n"/>
-      <c r="R120" s="5" t="n"/>
-      <c r="S120" s="3" t="n"/>
-      <c r="T120" s="3" t="n"/>
-      <c r="U120" s="3" t="n"/>
-      <c r="V120" s="4" t="inlineStr">
-        <is>
-          <t>② 제조사 1차 자료(공식 혼용정보 도구)에 “혼용가능(○)”로 명시된 조합만 — 추정이나 일반론은 배제</t>
-        </is>
-      </c>
-      <c r="W120" s="4" t="n"/>
-      <c r="X120" s="3" t="n"/>
-      <c r="Y120" s="3" t="n"/>
-      <c r="Z120" s="3" t="n"/>
-      <c r="AA120" s="8" t="n"/>
-      <c r="AB120" s="9" t="n"/>
-      <c r="AC120" s="9" t="n"/>
-      <c r="AD120" s="9" t="n"/>
-      <c r="AE120" s="3" t="n"/>
-      <c r="AF120" s="3" t="n"/>
-      <c r="AG120" s="4" t="n"/>
-      <c r="AH120" s="3" t="n"/>
-      <c r="AI120" s="3" t="n"/>
-      <c r="AJ120" s="3" t="n"/>
-      <c r="AK120" s="4" t="inlineStr">
-        <is>
-          <t>PART 4. 혼용 가능 조합</t>
-        </is>
-      </c>
-      <c r="AL120" s="4" t="n"/>
-      <c r="AM120" s="9" t="n"/>
-    </row>
-    <row r="121" ht="33" customHeight="1">
-      <c r="A121" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="n"/>
-      <c r="E121" s="5" t="n"/>
-      <c r="F121" s="2" t="n"/>
-      <c r="G121" s="3" t="n"/>
-      <c r="H121" s="5" t="n"/>
-      <c r="I121" s="5" t="n"/>
-      <c r="J121" s="4" t="n"/>
-      <c r="K121" s="3" t="n"/>
-      <c r="L121" s="6" t="n"/>
-      <c r="M121" s="3" t="n"/>
-      <c r="N121" s="3" t="n"/>
-      <c r="O121" s="7" t="n"/>
-      <c r="P121" s="4" t="n"/>
-      <c r="Q121" s="3" t="n"/>
-      <c r="R121" s="5" t="n"/>
-      <c r="S121" s="3" t="n"/>
-      <c r="T121" s="3" t="n"/>
-      <c r="U121" s="3" t="n"/>
-      <c r="V121" s="4" t="inlineStr">
-        <is>
-          <t>③ 궁합이 확인된 살균제가 이 가이드에 이미 나오는 제품일 때만 우선 표기 — 가이드 밖 제품과의 궁합은 실용성이 낮음</t>
-        </is>
-      </c>
-      <c r="W121" s="4" t="n"/>
-      <c r="X121" s="3" t="n"/>
-      <c r="Y121" s="3" t="n"/>
-      <c r="Z121" s="3" t="n"/>
-      <c r="AA121" s="8" t="n"/>
-      <c r="AB121" s="9" t="n"/>
-      <c r="AC121" s="9" t="n"/>
-      <c r="AD121" s="9" t="n"/>
-      <c r="AE121" s="3" t="n"/>
-      <c r="AF121" s="3" t="n"/>
-      <c r="AG121" s="4" t="n"/>
-      <c r="AH121" s="3" t="n"/>
-      <c r="AI121" s="3" t="n"/>
-      <c r="AJ121" s="3" t="n"/>
-      <c r="AK121" s="4" t="inlineStr">
-        <is>
-          <t>PART 4. 혼용 가능 조합</t>
-        </is>
-      </c>
-      <c r="AL121" s="4" t="n"/>
-      <c r="AM121" s="9" t="n"/>
-    </row>
-    <row r="122" ht="33" customHeight="1">
-      <c r="A122" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보</t>
-        </is>
-      </c>
-      <c r="D122" s="4" t="n"/>
-      <c r="E122" s="5" t="n"/>
-      <c r="F122" s="2" t="n"/>
-      <c r="G122" s="3" t="n"/>
-      <c r="H122" s="5" t="n"/>
-      <c r="I122" s="5" t="n"/>
-      <c r="J122" s="4" t="n"/>
-      <c r="K122" s="3" t="n"/>
-      <c r="L122" s="6" t="n"/>
-      <c r="M122" s="3" t="n"/>
-      <c r="N122" s="3" t="n"/>
-      <c r="O122" s="7" t="n"/>
-      <c r="P122" s="4" t="n"/>
-      <c r="Q122" s="3" t="n"/>
-      <c r="R122" s="5" t="n"/>
-      <c r="S122" s="3" t="n"/>
-      <c r="T122" s="3" t="n"/>
-      <c r="U122" s="3" t="n"/>
-      <c r="V122" s="4" t="inlineStr">
-        <is>
-          <t>④ 못 찾은 건 억지로 채우지 않고 “미확인”으로 명시 (버픽스·무름반점뚝·강철비)</t>
-        </is>
-      </c>
-      <c r="W122" s="4" t="n"/>
-      <c r="X122" s="3" t="n"/>
-      <c r="Y122" s="3" t="n"/>
-      <c r="Z122" s="3" t="n"/>
-      <c r="AA122" s="8" t="n"/>
-      <c r="AB122" s="9" t="n"/>
-      <c r="AC122" s="9" t="n"/>
-      <c r="AD122" s="9" t="n"/>
-      <c r="AE122" s="3" t="n"/>
-      <c r="AF122" s="3" t="n"/>
-      <c r="AG122" s="4" t="n"/>
-      <c r="AH122" s="3" t="n"/>
-      <c r="AI122" s="3" t="n"/>
-      <c r="AJ122" s="3" t="n"/>
-      <c r="AK122" s="4" t="inlineStr">
-        <is>
-          <t>PART 4. 혼용 가능 조합</t>
-        </is>
-      </c>
-      <c r="AL122" s="4" t="n"/>
-      <c r="AM122" s="9" t="n"/>
-    </row>
-    <row r="123" ht="63" customHeight="1">
-      <c r="A123" s="2" t="n">
-        <v>122</v>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보</t>
-        </is>
-      </c>
-      <c r="D123" s="4" t="n"/>
-      <c r="E123" s="5" t="n"/>
-      <c r="F123" s="2" t="n"/>
-      <c r="G123" s="3" t="n"/>
-      <c r="H123" s="5" t="n"/>
-      <c r="I123" s="5" t="n"/>
-      <c r="J123" s="4" t="n"/>
-      <c r="K123" s="3" t="n"/>
-      <c r="L123" s="6" t="n"/>
-      <c r="M123" s="3" t="n"/>
-      <c r="N123" s="3" t="n"/>
-      <c r="O123" s="7" t="n"/>
-      <c r="P123" s="4" t="n"/>
-      <c r="Q123" s="3" t="n"/>
-      <c r="R123" s="5" t="n"/>
-      <c r="S123" s="3" t="n"/>
-      <c r="T123" s="3" t="n"/>
-      <c r="U123" s="3" t="n"/>
-      <c r="V123" s="4" t="inlineStr">
-        <is>
-          <t>경농 혼용안내(knco.co.kr, 고추 기준)에서 학교 최우선 살충제 모스피란(아세타미프리드)을 조회한 결과, 아래 살균제와는 동시 살포(탱크믹스)가 가능하다고 나온다. 전부 이 가이드에 이미 나오는 제품들이다.</t>
-        </is>
-      </c>
-      <c r="W123" s="4" t="n"/>
-      <c r="X123" s="3" t="n"/>
-      <c r="Y123" s="3" t="n"/>
-      <c r="Z123" s="3" t="n"/>
-      <c r="AA123" s="8" t="n"/>
-      <c r="AB123" s="9" t="n"/>
-      <c r="AC123" s="9" t="n"/>
-      <c r="AD123" s="9" t="n"/>
-      <c r="AE123" s="3" t="n"/>
-      <c r="AF123" s="3" t="n"/>
-      <c r="AG123" s="4" t="n"/>
-      <c r="AH123" s="3" t="n"/>
-      <c r="AI123" s="3" t="n"/>
-      <c r="AJ123" s="3" t="n"/>
-      <c r="AK123" s="4" t="inlineStr">
-        <is>
-          <t>PART 4. 혼용 가능 조합</t>
-        </is>
-      </c>
-      <c r="AL123" s="4" t="n"/>
-      <c r="AM123" s="9" t="n"/>
-    </row>
-    <row r="124" ht="93" customHeight="1">
-      <c r="A124" s="2" t="n">
-        <v>123</v>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보</t>
-        </is>
-      </c>
-      <c r="D124" s="4" t="n"/>
-      <c r="E124" s="5" t="n"/>
-      <c r="F124" s="2" t="n"/>
-      <c r="G124" s="3" t="n"/>
-      <c r="H124" s="5" t="n"/>
-      <c r="I124" s="5" t="n"/>
-      <c r="J124" s="4" t="n"/>
-      <c r="K124" s="3" t="n"/>
-      <c r="L124" s="6" t="n"/>
-      <c r="M124" s="3" t="n"/>
-      <c r="N124" s="3" t="n"/>
-      <c r="O124" s="7" t="n"/>
-      <c r="P124" s="4" t="n"/>
-      <c r="Q124" s="3" t="n"/>
-      <c r="R124" s="5" t="n"/>
-      <c r="S124" s="3" t="n"/>
-      <c r="T124" s="3" t="n"/>
-      <c r="U124" s="3" t="n"/>
-      <c r="V124" s="4" t="inlineStr">
-        <is>
-          <t>위 5개는 모두 경농 제품이라 같은 회사 조회 결과 안에서 확인이 된 것이다. 스포르곤·코니도·타스타·강철비·쏘버린처럼 다른 회사(팜한농·바이엘·신젠타 등) 제품은 이 방식으로는 조회되지 않는다. 회사가 다르면 각 제조사 홈페이지 혼용정보나 고객센터로 직접 확인해야 하고, 확인 안 된 조합은 섞지 않는 게 원칙이다.</t>
-        </is>
-      </c>
-      <c r="W124" s="4" t="n"/>
-      <c r="X124" s="3" t="n"/>
-      <c r="Y124" s="3" t="n"/>
-      <c r="Z124" s="3" t="n"/>
-      <c r="AA124" s="8" t="n"/>
-      <c r="AB124" s="9" t="n"/>
-      <c r="AC124" s="9" t="n"/>
-      <c r="AD124" s="9" t="n"/>
-      <c r="AE124" s="3" t="n"/>
-      <c r="AF124" s="3" t="n"/>
-      <c r="AG124" s="4" t="n"/>
-      <c r="AH124" s="3" t="n"/>
-      <c r="AI124" s="3" t="n"/>
-      <c r="AJ124" s="3" t="n"/>
-      <c r="AK124" s="4" t="inlineStr">
-        <is>
-          <t>PART 4. 혼용 가능 조합 &gt; 확인된 조합</t>
-        </is>
-      </c>
-      <c r="AL124" s="4" t="n"/>
-      <c r="AM124" s="9" t="n"/>
-    </row>
-    <row r="125" ht="48" customHeight="1">
-      <c r="A125" s="2" t="n">
-        <v>124</v>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보</t>
-        </is>
-      </c>
-      <c r="D125" s="4" t="n"/>
-      <c r="E125" s="5" t="n"/>
-      <c r="F125" s="2" t="n"/>
-      <c r="G125" s="3" t="n"/>
-      <c r="H125" s="5" t="n"/>
-      <c r="I125" s="5" t="n"/>
-      <c r="J125" s="4" t="n"/>
-      <c r="K125" s="3" t="n"/>
-      <c r="L125" s="6" t="n"/>
-      <c r="M125" s="3" t="n"/>
-      <c r="N125" s="3" t="n"/>
-      <c r="O125" s="7" t="n"/>
-      <c r="P125" s="4" t="n"/>
-      <c r="Q125" s="3" t="n"/>
-      <c r="R125" s="5" t="n"/>
-      <c r="S125" s="3" t="n"/>
-      <c r="T125" s="3" t="n"/>
-      <c r="U125" s="3" t="n"/>
-      <c r="V125" s="4" t="inlineStr">
-        <is>
-          <t>제조사별 혼용정보 조회처: 경농 knco.co.kr/product/product_09 · 팜한농 farmhannong.com/kor/product/mix-info · 한국삼공 30agro.co.kr · 신젠타코리아 syngenta.co.kr</t>
-        </is>
-      </c>
-      <c r="W125" s="4" t="n"/>
-      <c r="X125" s="3" t="n"/>
-      <c r="Y125" s="3" t="n"/>
-      <c r="Z125" s="3" t="n"/>
-      <c r="AA125" s="8" t="n"/>
-      <c r="AB125" s="9" t="n"/>
-      <c r="AC125" s="9" t="n"/>
-      <c r="AD125" s="9" t="n"/>
-      <c r="AE125" s="3" t="n"/>
-      <c r="AF125" s="3" t="n"/>
-      <c r="AG125" s="4" t="n"/>
-      <c r="AH125" s="3" t="n"/>
-      <c r="AI125" s="3" t="n"/>
-      <c r="AJ125" s="3" t="n"/>
-      <c r="AK125" s="4" t="inlineStr">
-        <is>
-          <t>PART 4. 혼용 가능 조합 &gt; 확인된 조합</t>
-        </is>
-      </c>
-      <c r="AL125" s="4" t="n"/>
-      <c r="AM125" s="9" t="n"/>
-    </row>
-    <row r="126" ht="33" customHeight="1">
-      <c r="A126" s="2" t="n">
-        <v>125</v>
-      </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보</t>
-        </is>
-      </c>
-      <c r="D126" s="4" t="n"/>
-      <c r="E126" s="5" t="n"/>
-      <c r="F126" s="2" t="n"/>
-      <c r="G126" s="3" t="n"/>
-      <c r="H126" s="5" t="n"/>
-      <c r="I126" s="5" t="n"/>
-      <c r="J126" s="4" t="n"/>
-      <c r="K126" s="3" t="n"/>
-      <c r="L126" s="6" t="n"/>
-      <c r="M126" s="3" t="n"/>
-      <c r="N126" s="3" t="n"/>
-      <c r="O126" s="7" t="n"/>
-      <c r="P126" s="4" t="n"/>
-      <c r="Q126" s="3" t="n"/>
-      <c r="R126" s="5" t="n"/>
-      <c r="S126" s="3" t="n"/>
-      <c r="T126" s="3" t="n"/>
-      <c r="U126" s="3" t="n"/>
-      <c r="V126" s="4" t="inlineStr">
-        <is>
-          <t>조회일 2026-09-18</t>
-        </is>
-      </c>
-      <c r="W126" s="4" t="n"/>
-      <c r="X126" s="3" t="n"/>
-      <c r="Y126" s="3" t="n"/>
-      <c r="Z126" s="3" t="n"/>
-      <c r="AA126" s="8" t="n"/>
-      <c r="AB126" s="9" t="n"/>
-      <c r="AC126" s="9" t="n"/>
-      <c r="AD126" s="9" t="n"/>
-      <c r="AE126" s="3" t="n"/>
-      <c r="AF126" s="3" t="n"/>
-      <c r="AG126" s="4" t="n"/>
-      <c r="AH126" s="3" t="n"/>
-      <c r="AI126" s="3" t="n"/>
-      <c r="AJ126" s="3" t="n"/>
-      <c r="AK126" s="4" t="inlineStr">
-        <is>
-          <t>PART 4. 혼용 가능 조합 &gt; 확인된 조합</t>
-        </is>
-      </c>
-      <c r="AL126" s="4" t="n"/>
-      <c r="AM126" s="9" t="n">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="127" ht="48" customHeight="1">
-      <c r="A127" s="2" t="n">
-        <v>126</v>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보</t>
-        </is>
-      </c>
-      <c r="D127" s="4" t="n"/>
-      <c r="E127" s="5" t="n"/>
-      <c r="F127" s="2" t="n"/>
-      <c r="G127" s="3" t="n"/>
-      <c r="H127" s="5" t="n"/>
-      <c r="I127" s="5" t="n"/>
-      <c r="J127" s="4" t="n"/>
-      <c r="K127" s="3" t="n"/>
-      <c r="L127" s="6" t="n"/>
-      <c r="M127" s="3" t="n"/>
-      <c r="N127" s="3" t="n"/>
-      <c r="O127" s="7" t="n"/>
-      <c r="P127" s="4" t="n"/>
-      <c r="Q127" s="3" t="n"/>
-      <c r="R127" s="5" t="n"/>
-      <c r="S127" s="3" t="n"/>
-      <c r="T127" s="3" t="n"/>
-      <c r="U127" s="3" t="n"/>
-      <c r="V127" s="4" t="inlineStr">
-        <is>
-          <t>팜한농 혼용정보(farmhannong.com, 고추 기준) 조회 결과. 코니도는 살균제 벨쿠트와 짝이 맞고, 타스타는 고추에서 같이 쓸 살균제가 공식적으로 하나도 없다.</t>
-        </is>
-      </c>
-      <c r="W127" s="4" t="n"/>
-      <c r="X127" s="3" t="n"/>
-      <c r="Y127" s="3" t="n"/>
-      <c r="Z127" s="3" t="n"/>
-      <c r="AA127" s="8" t="n"/>
-      <c r="AB127" s="9" t="n"/>
-      <c r="AC127" s="9" t="n"/>
-      <c r="AD127" s="9" t="n"/>
-      <c r="AE127" s="3" t="n"/>
-      <c r="AF127" s="3" t="n"/>
-      <c r="AG127" s="4" t="n"/>
-      <c r="AH127" s="3" t="n"/>
-      <c r="AI127" s="3" t="n"/>
-      <c r="AJ127" s="3" t="n"/>
-      <c r="AK127" s="4" t="inlineStr">
-        <is>
-          <t>PART 4. 혼용 가능 조합 &gt; 바이엘(코니도·타스타) 공식 혼용정보</t>
-        </is>
-      </c>
-      <c r="AL127" s="4" t="n"/>
-      <c r="AM127" s="9" t="n"/>
-    </row>
-    <row r="128" ht="93" customHeight="1">
-      <c r="A128" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보</t>
-        </is>
-      </c>
-      <c r="D128" s="4" t="n"/>
-      <c r="E128" s="5" t="n"/>
-      <c r="F128" s="2" t="n"/>
-      <c r="G128" s="3" t="n"/>
-      <c r="H128" s="5" t="n"/>
-      <c r="I128" s="5" t="n"/>
-      <c r="J128" s="4" t="n"/>
-      <c r="K128" s="3" t="n"/>
-      <c r="L128" s="6" t="n"/>
-      <c r="M128" s="3" t="n"/>
-      <c r="N128" s="3" t="n"/>
-      <c r="O128" s="7" t="n"/>
-      <c r="P128" s="4" t="n"/>
-      <c r="Q128" s="3" t="n"/>
-      <c r="R128" s="5" t="n"/>
-      <c r="S128" s="3" t="n"/>
-      <c r="T128" s="3" t="n"/>
-      <c r="U128" s="3" t="n"/>
-      <c r="V128" s="4" t="inlineStr">
-        <is>
-          <t>스포르곤(팜한농)은 이 표에서 바이고·시반토·신기록-D 같은 다른 바이엘 살충제와는 짝이 맞지만, 가이드가 쓰는 모스피란·코니도·타스타 중 누구와도 짝으로 나오지 않는다. 쏘버린(팜한농, 카보설판)은 정식할 때 흙에 뿌리는 입제라 이 혼용정보표 자체에 없다 — 원래 스프레이통에 섞어 쓰는 제품이 아니다.</t>
-        </is>
-      </c>
-      <c r="W128" s="4" t="n"/>
-      <c r="X128" s="3" t="n"/>
-      <c r="Y128" s="3" t="n"/>
-      <c r="Z128" s="3" t="n"/>
-      <c r="AA128" s="8" t="n"/>
-      <c r="AB128" s="9" t="n"/>
-      <c r="AC128" s="9" t="n"/>
-      <c r="AD128" s="9" t="n"/>
-      <c r="AE128" s="3" t="n"/>
-      <c r="AF128" s="3" t="n"/>
-      <c r="AG128" s="4" t="n"/>
-      <c r="AH128" s="3" t="n"/>
-      <c r="AI128" s="3" t="n"/>
-      <c r="AJ128" s="3" t="n"/>
-      <c r="AK128" s="4" t="inlineStr">
-        <is>
-          <t>PART 4. 혼용 가능 조합 &gt; 바이엘(코니도·타스타) 공식 혼용정보</t>
-        </is>
-      </c>
-      <c r="AL128" s="4" t="n"/>
-      <c r="AM128" s="9" t="n"/>
-    </row>
-    <row r="129" ht="63" customHeight="1">
-      <c r="A129" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보</t>
-        </is>
-      </c>
-      <c r="D129" s="4" t="n"/>
-      <c r="E129" s="5" t="n"/>
-      <c r="F129" s="2" t="n"/>
-      <c r="G129" s="3" t="n"/>
-      <c r="H129" s="5" t="n"/>
-      <c r="I129" s="5" t="n"/>
-      <c r="J129" s="4" t="n"/>
-      <c r="K129" s="3" t="n"/>
-      <c r="L129" s="6" t="n"/>
-      <c r="M129" s="3" t="n"/>
-      <c r="N129" s="3" t="n"/>
-      <c r="O129" s="7" t="n"/>
-      <c r="P129" s="4" t="n"/>
-      <c r="Q129" s="3" t="n"/>
-      <c r="R129" s="5" t="n"/>
-      <c r="S129" s="3" t="n"/>
-      <c r="T129" s="3" t="n"/>
-      <c r="U129" s="3" t="n"/>
-      <c r="V129" s="4" t="inlineStr">
-        <is>
-          <t>버픽스(동방아그로), 무름반점뚝(대유), 강철비(인바이오)는 제조사는 확인했지만 온라인에 공개된 혼용정보 도구가 없어 짝을 못 찾았다. 이 세 개는 쓰기 전에 제조사 고객센터에 직접 물어봐야 한다.</t>
-        </is>
-      </c>
-      <c r="W129" s="4" t="n"/>
-      <c r="X129" s="3" t="n"/>
-      <c r="Y129" s="3" t="n"/>
-      <c r="Z129" s="3" t="n"/>
-      <c r="AA129" s="8" t="n"/>
-      <c r="AB129" s="9" t="n"/>
-      <c r="AC129" s="9" t="n"/>
-      <c r="AD129" s="9" t="n"/>
-      <c r="AE129" s="3" t="n"/>
-      <c r="AF129" s="3" t="n"/>
-      <c r="AG129" s="4" t="n"/>
-      <c r="AH129" s="3" t="n"/>
-      <c r="AI129" s="3" t="n"/>
-      <c r="AJ129" s="3" t="n"/>
-      <c r="AK129" s="4" t="inlineStr">
-        <is>
-          <t>PART 4. 혼용 가능 조합 &gt; 바이엘(코니도·타스타) 공식 혼용정보</t>
-        </is>
-      </c>
-      <c r="AL129" s="4" t="n"/>
-      <c r="AM129" s="9" t="n"/>
-    </row>
-    <row r="130" ht="48" customHeight="1">
-      <c r="A130" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보</t>
-        </is>
-      </c>
-      <c r="D130" s="4" t="n"/>
-      <c r="E130" s="5" t="n"/>
-      <c r="F130" s="2" t="n"/>
-      <c r="G130" s="3" t="n"/>
-      <c r="H130" s="5" t="n"/>
-      <c r="I130" s="5" t="n"/>
-      <c r="J130" s="4" t="n"/>
-      <c r="K130" s="3" t="n"/>
-      <c r="L130" s="6" t="n"/>
-      <c r="M130" s="3" t="n"/>
-      <c r="N130" s="3" t="n"/>
-      <c r="O130" s="7" t="n"/>
-      <c r="P130" s="4" t="n"/>
-      <c r="Q130" s="3" t="n"/>
-      <c r="R130" s="5" t="n"/>
-      <c r="S130" s="3" t="n"/>
-      <c r="T130" s="3" t="n"/>
-      <c r="U130" s="3" t="n"/>
-      <c r="V130" s="4" t="inlineStr">
-        <is>
-          <t>출처: farmhannong.com/kor/product/mix-info (바이엘 혼용기술정보 2025), 조회일 2026-09-18</t>
-        </is>
-      </c>
-      <c r="W130" s="4" t="n"/>
-      <c r="X130" s="3" t="n"/>
-      <c r="Y130" s="3" t="n"/>
-      <c r="Z130" s="3" t="n"/>
-      <c r="AA130" s="8" t="n"/>
-      <c r="AB130" s="9" t="n"/>
-      <c r="AC130" s="9" t="n"/>
-      <c r="AD130" s="9" t="n"/>
-      <c r="AE130" s="3" t="n"/>
-      <c r="AF130" s="3" t="n"/>
-      <c r="AG130" s="4" t="n"/>
-      <c r="AH130" s="3" t="n"/>
-      <c r="AI130" s="3" t="n"/>
-      <c r="AJ130" s="3" t="n"/>
-      <c r="AK130" s="4" t="inlineStr">
-        <is>
-          <t>PART 4. 혼용 가능 조합 &gt; 바이엘(코니도·타스타) 공식 혼용정보</t>
-        </is>
-      </c>
-      <c r="AL130" s="4" t="n"/>
-      <c r="AM130" s="9" t="n">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="131" ht="63" customHeight="1">
-      <c r="A131" s="2" t="n">
-        <v>130</v>
-      </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보</t>
-        </is>
-      </c>
-      <c r="D131" s="4" t="n"/>
-      <c r="E131" s="5" t="n"/>
-      <c r="F131" s="2" t="n"/>
-      <c r="G131" s="3" t="n"/>
-      <c r="H131" s="5" t="n"/>
-      <c r="I131" s="5" t="n"/>
-      <c r="J131" s="4" t="n"/>
-      <c r="K131" s="3" t="n"/>
-      <c r="L131" s="6" t="n"/>
-      <c r="M131" s="3" t="n"/>
-      <c r="N131" s="3" t="n"/>
-      <c r="O131" s="7" t="n"/>
-      <c r="P131" s="4" t="n"/>
-      <c r="Q131" s="3" t="n"/>
-      <c r="R131" s="5" t="n"/>
-      <c r="S131" s="3" t="n"/>
-      <c r="T131" s="3" t="n"/>
-      <c r="U131" s="3" t="n"/>
-      <c r="V131" s="4" t="inlineStr">
-        <is>
-          <t>제조사를 알아낸 뒤 각 회사 홈페이지의 혼용정보를 끝까지 뒤졌다. 결과는 아래와 같다 — 도구가 없어서 못 찾은 게 아니라, 도구는 있는데 그 안에 이 제품 자체가 없는 경우가 대부분이다.</t>
-        </is>
-      </c>
-      <c r="W131" s="4" t="n"/>
-      <c r="X131" s="3" t="n"/>
-      <c r="Y131" s="3" t="n"/>
-      <c r="Z131" s="3" t="n"/>
-      <c r="AA131" s="8" t="n"/>
-      <c r="AB131" s="9" t="n"/>
-      <c r="AC131" s="9" t="n"/>
-      <c r="AD131" s="9" t="n"/>
-      <c r="AE131" s="3" t="n"/>
-      <c r="AF131" s="3" t="n"/>
-      <c r="AG131" s="4" t="n"/>
-      <c r="AH131" s="3" t="n"/>
-      <c r="AI131" s="3" t="n"/>
-      <c r="AJ131" s="3" t="n"/>
-      <c r="AK131" s="4" t="inlineStr">
-        <is>
-          <t>PART 4. 혼용 가능 조합 &gt; 나머지 3개(버픽스·무름반점뚝·강철비) 끝까지 확인한 결과</t>
-        </is>
-      </c>
-      <c r="AL131" s="4" t="n"/>
-      <c r="AM131" s="9" t="n"/>
-    </row>
-    <row r="132" ht="63" customHeight="1">
-      <c r="A132" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보</t>
-        </is>
-      </c>
-      <c r="D132" s="4" t="n"/>
-      <c r="E132" s="5" t="n"/>
-      <c r="F132" s="2" t="n"/>
-      <c r="G132" s="3" t="n"/>
-      <c r="H132" s="5" t="n"/>
-      <c r="I132" s="5" t="n"/>
-      <c r="J132" s="4" t="n"/>
-      <c r="K132" s="3" t="n"/>
-      <c r="L132" s="6" t="n"/>
-      <c r="M132" s="3" t="n"/>
-      <c r="N132" s="3" t="n"/>
-      <c r="O132" s="7" t="n"/>
-      <c r="P132" s="4" t="n"/>
-      <c r="Q132" s="3" t="n"/>
-      <c r="R132" s="5" t="n"/>
-      <c r="S132" s="3" t="n"/>
-      <c r="T132" s="3" t="n"/>
-      <c r="U132" s="3" t="n"/>
-      <c r="V132" s="4" t="inlineStr">
-        <is>
-          <t>셋 다 온라인에 공개된 자료로는 답이 안 나온다는 뜻이다. 이 이상은 제조사 고객센터에 직접 전화해서 "이 제품, 저 살균제/살충제랑 섞어도 되나요"라고 물어보는 수밖에 없다 — 동방아그로 1644-7337 · 대유 · 인바이오 031-477-6011.</t>
-        </is>
-      </c>
-      <c r="W132" s="4" t="n"/>
-      <c r="X132" s="3" t="n"/>
-      <c r="Y132" s="3" t="n"/>
-      <c r="Z132" s="3" t="n"/>
-      <c r="AA132" s="8" t="n"/>
-      <c r="AB132" s="9" t="n"/>
-      <c r="AC132" s="9" t="n"/>
-      <c r="AD132" s="9" t="n"/>
-      <c r="AE132" s="3" t="n"/>
-      <c r="AF132" s="3" t="n"/>
-      <c r="AG132" s="4" t="n"/>
-      <c r="AH132" s="3" t="n"/>
-      <c r="AI132" s="3" t="n"/>
-      <c r="AJ132" s="3" t="n"/>
-      <c r="AK132" s="4" t="inlineStr">
-        <is>
-          <t>PART 4. 혼용 가능 조합 &gt; 나머지 3개(버픽스·무름반점뚝·강철비) 끝까지 확인한 결과</t>
-        </is>
-      </c>
-      <c r="AL132" s="4" t="n"/>
-      <c r="AM132" s="9" t="n"/>
-    </row>
-    <row r="133" ht="48" customHeight="1">
-      <c r="A133" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>안내·참고</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>혼용정보</t>
-        </is>
-      </c>
-      <c r="D133" s="4" t="n"/>
-      <c r="E133" s="5" t="n"/>
-      <c r="F133" s="2" t="n"/>
-      <c r="G133" s="3" t="n"/>
-      <c r="H133" s="5" t="n"/>
-      <c r="I133" s="5" t="n"/>
-      <c r="J133" s="4" t="n"/>
-      <c r="K133" s="3" t="n"/>
-      <c r="L133" s="6" t="n"/>
-      <c r="M133" s="3" t="n"/>
-      <c r="N133" s="3" t="n"/>
-      <c r="O133" s="7" t="n"/>
-      <c r="P133" s="4" t="n"/>
-      <c r="Q133" s="3" t="n"/>
-      <c r="R133" s="5" t="n"/>
-      <c r="S133" s="3" t="n"/>
-      <c r="T133" s="3" t="n"/>
-      <c r="U133" s="3" t="n"/>
-      <c r="V133" s="4" t="inlineStr">
-        <is>
-          <t>확인 경로: dongbangagro.co.kr/product_combined.php · dae-yu.co.kr · enbio.co.kr(혼용정보 게시판, 살균제·살충제 혼용가부표 전체), 조회일 2026-09-18</t>
-        </is>
-      </c>
-      <c r="W133" s="4" t="n"/>
-      <c r="X133" s="3" t="n"/>
-      <c r="Y133" s="3" t="n"/>
-      <c r="Z133" s="3" t="n"/>
-      <c r="AA133" s="8" t="n"/>
-      <c r="AB133" s="9" t="n"/>
-      <c r="AC133" s="9" t="n"/>
-      <c r="AD133" s="9" t="n"/>
-      <c r="AE133" s="3" t="n"/>
-      <c r="AF133" s="3" t="n"/>
-      <c r="AG133" s="4" t="n"/>
-      <c r="AH133" s="3" t="n"/>
-      <c r="AI133" s="3" t="n"/>
-      <c r="AJ133" s="3" t="n"/>
-      <c r="AK133" s="4" t="inlineStr">
-        <is>
-          <t>PART 4. 혼용 가능 조합 &gt; 나머지 3개(버픽스·무름반점뚝·강철비) 끝까지 확인한 결과</t>
-        </is>
-      </c>
-      <c r="AL133" s="4" t="n"/>
-      <c r="AM133" s="9" t="n">
-        <v>46283</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="I2:I5000">
+  <conditionalFormatting sqref="I2:I3000">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$I2="보유"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F5000">
+  <conditionalFormatting sqref="F2:F3000">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>$F2=1</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="6">
+    <dataValidation sqref="B2:B3000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력값 확인" error="[분류 기준] 시트의 목록에 있는 값을 선택하세요." promptTitle="정보 구분" prompt="목록에서 선택하세요." type="list" errorStyle="stop">
+      <formula1>=목록_정보구분</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C3000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력값 확인" error="[분류 기준] 시트의 목록에 있는 값을 선택하세요." promptTitle="방제 분류" prompt="목록에서 선택하세요." type="list" errorStyle="stop">
+      <formula1>=목록_방제분류</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I3000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력값 확인" error="[분류 기준] 시트의 목록에 있는 값을 선택하세요." promptTitle="학교 보유" prompt="목록에서 선택하세요." type="list" errorStyle="stop">
+      <formula1>=목록_학교보유</formula1>
+    </dataValidation>
+    <dataValidation sqref="R2:R3000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력값 확인" error="[분류 기준] 시트의 목록에 있는 값을 선택하세요." promptTitle="혼용 가능 여부" prompt="목록에서 선택하세요." type="list" errorStyle="stop">
+      <formula1>=목록_혼용가능여부</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H3000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력값 확인" error="[분류 기준] 시트의 목록에 있는 값을 선택하세요." promptTitle="제형" prompt="목록에서 선택하세요." type="list" errorStyle="warning">
+      <formula1>=목록_제형</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M3000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력값 확인" error="[분류 기준] 시트의 목록에 있는 값을 선택하세요." promptTitle="사용방법" prompt="목록에서 선택하세요." type="list" errorStyle="warning">
+      <formula1>=목록_사용방법</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>■ 사용 방법</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>1. [방제 정보 목록] 시트에서 원하는 열 머리글의 ▼(필터) 단추를 누릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>2. 검색 칸에 병해충명(예: 꽃노랑총채벌레)이나 약제명을 입력하거나 목록에서 선택합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>3. 확인을 누르면 해당 항목만 표시됩니다. 필터 해제: [데이터] 탭 → [지우기].</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>4. 새 자료는 표 바로 아래 행에 입력하면 표·필터·서식이 자동으로 확장됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>5. 분류 열(정보 구분·방제 분류·학교 보유·혼용 가능 여부·제형·사용방법)은 아래 목록에서 선택해 입력합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>■ 표시 규칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>• 학교 보유 = "보유" 셀은 노란색으로 표시됩니다. (원본 가이드의 노란색 = 학교 보유 약제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>• 추천 순위 = 1 은 빨간 굵은 글씨로 표시됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>• 원본에 값이 없는 칸(예: 희석배수 "-")은 빈칸으로 두었습니다. 임의로 채우지 않았습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>■ 분류 값 목록 (드롭다운 원본 — 새 분류가 필요하면 각 목록 아래 빈칸에 추가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>정보 구분</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>방제 분류</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>학교 보유</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>혼용 가능 여부</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>제형</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>사용방법</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>추천 약제(로테이션)</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>병해(살균제)</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>보유</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>수화제</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>경엽처리</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>구매 필요 약제</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>해충(살충제)</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>미보유</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>조합 없음(섞지 말 것)</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>액상</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>관주처리</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>유기농업자재</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>유기농업자재</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>액상수화제</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>관주처리(양액재배)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>유기농업자재(기타 방제효과)</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>혼용정보</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>유제</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>정식 4주일 전 토양처리</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>혼용 가능 조합</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>입상수화제</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>토양처리</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>혼용정보 확인결과</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>입제</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="n"/>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="n"/>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="12" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="n"/>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="12" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="n"/>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="12" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="n"/>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="12" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="n"/>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="12" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>■ 열 설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>열 이름</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="n"/>
+      <c r="D29" s="13" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="13" t="n"/>
+      <c r="G29" s="14" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>행 고유번호 (정렬 후 원래 순서로 되돌릴 때 사용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>정보 구분</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>자료 종류. 추천 약제(로테이션) / 구매 필요 약제 / 유기농업자재 / 유기농업자재(기타 방제효과) / 혼용 가능 조합 / 혼용정보 확인결과</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>방제 분류</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>병해(살균제) · 해충(살충제) · 유기농업자재 · 혼용정보</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>병해충명</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>대상 병해충 1개 (검색·필터의 기준 열). 원본 표기 그대로</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>대상 작물</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>원본에 작물이 명시된 경우만 기재 (유기농업자재 시험 작물 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>추천 순위</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>병해충별 로테이션 순위 (1 = 우선 사용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>상표명</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>제형을 뺀 제품명. 원래 표기는 [상표명(원문)] 열</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>제형</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>수화제 · 액상수화제 · 입상수화제 · 입제 · 유제 · 액상</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>학교 보유</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>연암대 보유 여부 (원본 "O" 표시 = 보유)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>희석배수</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>숫자(배). 원본 "-"는 빈칸</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>안전사용 시기</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>안전사용기준의 시기 부분 (예: 수확3일전, 정식기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>최대 사용횟수</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>안전사용기준의 횟수 부분 (숫자)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>겸용 대상(전체)</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>해당 약제가 등록된 병해충 전체 (원본 표기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>혼용 상대 약제</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>혼용 가능 조합 행에서 함께 섞을 수 있는 살균제</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>혼용 가능 여부</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>가능 / 조합 없음(섞지 말 것) / 미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>방제가(효과)</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>무처리구 대비 방제가 (유기농업자재)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>관련 정보</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>1순위 추천 문구 원문, 가이드 내 위치, 확인 결과 등 부가 설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>원본의 ※ 메모, 원문 병해충 목록 등</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>원본 위치</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>원본 가이드에서 해당 내용이 있던 위치</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>자료 조회일</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="inlineStr">
+        <is>
+          <t>원본에 기재된 자료 조회일</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>■ 원본 가이드 안내·참고 사항 (원문 그대로)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>원본 위치(PART)</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>세부 위치</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="n"/>
+      <c r="E52" s="13" t="n"/>
+      <c r="F52" s="14" t="n"/>
+      <c r="G52" s="1" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="H52" s="1" t="inlineStr">
+        <is>
+          <t>자료 조회일</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="19" customHeight="1">
+      <c r="A53" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" s="18" t="inlineStr">
+        <is>
+          <t>개요</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="n"/>
+      <c r="G53" s="18" t="inlineStr">
+        <is>
+          <t>파프리카 재배 현장 방제 가이드</t>
+        </is>
+      </c>
+      <c r="H53" s="19" t="n"/>
+    </row>
+    <row r="54" ht="19" customHeight="1">
+      <c r="A54" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>개요</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="inlineStr">
+        <is>
+          <t>파프리카 재배 현장 방제 가이드</t>
+        </is>
+      </c>
+      <c r="G54" s="18" t="inlineStr">
+        <is>
+          <t>연암대학교 스마트팜 유리온실</t>
+        </is>
+      </c>
+      <c r="H54" s="19" t="n"/>
+    </row>
+    <row r="55" ht="19" customHeight="1">
+      <c r="A55" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B55" s="18" t="inlineStr">
+        <is>
+          <t>개요</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>파프리카 재배 현장 방제 가이드</t>
+        </is>
+      </c>
+      <c r="G55" s="18" t="inlineStr">
+        <is>
+          <t>선정 기준: ① 학교 보유 약제 ② 여러 병해충에 겸용 가능한 약제</t>
+        </is>
+      </c>
+      <c r="H55" s="19" t="n"/>
+    </row>
+    <row r="56" ht="34" customHeight="1">
+      <c r="A56" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>개요</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>파프리카 재배 현장 방제 가이드</t>
+        </is>
+      </c>
+      <c r="G56" s="18" t="inlineStr">
+        <is>
+          <t>같은 작용기작(코드)을 연속 사용하면 저항성이 생기니, 2회 이상 살포 시 표의 2~4순위로 바꿔가며 로테이션</t>
+        </is>
+      </c>
+      <c r="H56" s="19" t="n"/>
+    </row>
+    <row r="57" ht="34" customHeight="1">
+      <c r="A57" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B57" s="18" t="inlineStr">
+        <is>
+          <t>개요</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>구매 약제 전체 목록 (추천표 중 학교 미보유분)</t>
+        </is>
+      </c>
+      <c r="G57" s="18" t="inlineStr">
+        <is>
+          <t>총 14개 — 뒤쪽 병해충별 추천표에 나온 약제 중 현재 연암대 재고에 없는 것을 전부 모았습니다. 구매 시 참고하세요.</t>
+        </is>
+      </c>
+      <c r="H57" s="19" t="n"/>
+    </row>
+    <row r="58" ht="34" customHeight="1">
+      <c r="A58" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>개요</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>구매 약제 전체 목록 (추천표 중 학교 미보유분)</t>
+        </is>
+      </c>
+      <c r="G58" s="18" t="inlineStr">
+        <is>
+          <t>유기농업자재 (친환경 공시자재)_보조 방제수단</t>
+        </is>
+      </c>
+      <c r="H58" s="19" t="n"/>
+    </row>
+    <row r="59" ht="19" customHeight="1">
+      <c r="A59" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B59" s="18" t="inlineStr">
+        <is>
+          <t>PART 3. 유기농업자재</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="n"/>
+      <c r="G59" s="18" t="inlineStr">
+        <is>
+          <t>선정 기준</t>
+        </is>
+      </c>
+      <c r="H59" s="19" t="n"/>
+    </row>
+    <row r="60" ht="34" customHeight="1">
+      <c r="A60" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>PART 3. 유기농업자재</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="n"/>
+      <c r="G60" s="18" t="inlineStr">
+        <is>
+          <t>① 이 가이드가 다루는 고추 병해충(꽃노랑총채벌레·온실가루이·복숭아혹진딧물)에 실제 방제시험 데이터가 있는 제품만</t>
+        </is>
+      </c>
+      <c r="H60" s="19" t="n"/>
+    </row>
+    <row r="61" ht="34" customHeight="1">
+      <c r="A61" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B61" s="18" t="inlineStr">
+        <is>
+          <t>PART 3. 유기농업자재</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="n"/>
+      <c r="G61" s="18" t="inlineStr">
+        <is>
+          <t>② 국립농산물품질관리원 공시자재(naqs.go.kr)에 정식 등재된 것만 — 출처 불명확한 자료는 제외</t>
+        </is>
+      </c>
+      <c r="H61" s="19" t="n"/>
+    </row>
+    <row r="62" ht="94" customHeight="1">
+      <c r="A62" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B62" s="18" t="inlineStr">
+        <is>
+          <t>PART 3. 유기농업자재</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="n"/>
+      <c r="G62" s="18" t="inlineStr">
+        <is>
+          <t>아래 2개 제품은 국립농산물품질관리원 유기농업자재 공시현황(naqs.go.kr)에 등재된 병해충관리용 공시자재입니다. 정식 등록 '농약'이 아니라 효능시험을 거쳐 공시된 친환경 자재이며, 본 가이드의 고추 재배 병해충(꽃노랑총채벌레·온실가루이·복숭아혹진딧물)과 직접 관련된 항목만 정리했습니다. 무농약·유기재배 인증 포장이나 수확 임박 시기, 로테이션 보조 수단으로 참고하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="H62" s="19" t="n"/>
+    </row>
+    <row r="63" ht="64" customHeight="1">
+      <c r="A63" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B63" s="18" t="inlineStr">
+        <is>
+          <t>PART 3. 유기농업자재</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="n"/>
+      <c r="G63" s="18" t="inlineStr">
+        <is>
+          <t>⚠ 화학농약이 아닌 유기농업자재입니다 — 등록 농약과 안전사용기준·법적 지위가 다릅니다. 표시구분 '농약효과'는 효능시험 결과일 뿐 '농약등록'과는 별개이며, 두 제품 모두 농약/비료 등록여부는 '없음'입니다.</t>
+        </is>
+      </c>
+      <c r="H63" s="19" t="n"/>
+    </row>
+    <row r="64" ht="34" customHeight="1">
+      <c r="A64" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B64" s="18" t="inlineStr">
+        <is>
+          <t>PART 3. 유기농업자재</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="inlineStr">
+        <is>
+          <t>한방싹충도사 (병해충관리용)</t>
+        </is>
+      </c>
+      <c r="G64" s="18" t="inlineStr">
+        <is>
+          <t>고추 관련 사용법: 꽃노랑총채벌레, 발생초기, 1,000배 희석, 경엽처리 — 무처리구 대비 방제가 61.7%</t>
+        </is>
+      </c>
+      <c r="H64" s="19" t="n"/>
+    </row>
+    <row r="65" ht="64" customHeight="1">
+      <c r="A65" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B65" s="18" t="inlineStr">
+        <is>
+          <t>PART 3. 유기농업자재</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="inlineStr">
+        <is>
+          <t>한방싹충도사 (병해충관리용)</t>
+        </is>
+      </c>
+      <c r="G65" s="18" t="inlineStr">
+        <is>
+          <t>그 외 방제효과: 딸기 점박이응애 67.5% · 배 조팝나무진딧물 77.4% · 양배추 배추흰나비 65.9% · 복숭아 복숭아순나방 60.0% · 포도 꽃매미 62.8% · 사과 갈색날개매미충 65.8% · 오이 온실가루이 60%이상 · 감귤 이세리아깍지벌레 60%이상</t>
+        </is>
+      </c>
+      <c r="H65" s="19" t="n"/>
+    </row>
+    <row r="66" ht="34" customHeight="1">
+      <c r="A66" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>PART 3. 유기농업자재</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>뉴응칠이 (병해충관리용)</t>
+        </is>
+      </c>
+      <c r="G66" s="18" t="inlineStr">
+        <is>
+          <t>고추 관련 사용법: 복숭아혹진딧물, 생육기, 1,000배 희석, 경엽처리 — 무처리구 대비 방제가 50% 이상</t>
+        </is>
+      </c>
+      <c r="H66" s="19" t="n"/>
+    </row>
+    <row r="67" ht="49" customHeight="1">
+      <c r="A67" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B67" s="18" t="inlineStr">
+        <is>
+          <t>PART 3. 유기농업자재</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="inlineStr">
+        <is>
+          <t>뉴응칠이 (병해충관리용)</t>
+        </is>
+      </c>
+      <c r="G67" s="18" t="inlineStr">
+        <is>
+          <t>그 외 방제효과(오이 시험): 꽃노랑총채벌레·아메리카잎굴파리·온실가루이·흰가루병 — 무처리구 대비 50% 이상 / 블루베리 미국선녀벌레 50% 이상</t>
+        </is>
+      </c>
+      <c r="H67" s="19" t="n"/>
+    </row>
+    <row r="68" ht="34" customHeight="1">
+      <c r="A68" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>PART 3. 유기농업자재</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>뉴응칠이 (병해충관리용)</t>
+        </is>
+      </c>
+      <c r="G68" s="18" t="inlineStr">
+        <is>
+          <t>주의: 접촉성 제제(잎 뒷면까지 흠뻑 살포) · 강알칼리성 제제·석회보르도액·유황합제 혼용 금지 · 꿀벌 활동에 영향 가능</t>
+        </is>
+      </c>
+      <c r="H68" s="19" t="n"/>
+    </row>
+    <row r="69" ht="34" customHeight="1">
+      <c r="A69" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t>PART 3. 유기농업자재</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
+        <is>
+          <t>뉴응칠이 (병해충관리용)</t>
+        </is>
+      </c>
+      <c r="G69" s="18" t="inlineStr">
+        <is>
+          <t>자료 출처: 국립농산물품질관리원 유기농업자재 공시현황(naqs.go.kr), 조회일 2026-09-18. 실제 사용 전 최신 공시정보 재확인 요망.</t>
+        </is>
+      </c>
+      <c r="H69" s="19" t="n">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="70" ht="19" customHeight="1">
+      <c r="A70" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B70" s="18" t="inlineStr">
+        <is>
+          <t>PART 4. 혼용 가능 조합</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="n"/>
+      <c r="G70" s="18" t="inlineStr">
+        <is>
+          <t>선정 기준</t>
+        </is>
+      </c>
+      <c r="H70" s="19" t="n"/>
+    </row>
+    <row r="71" ht="34" customHeight="1">
+      <c r="A71" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B71" s="18" t="inlineStr">
+        <is>
+          <t>PART 4. 혼용 가능 조합</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="n"/>
+      <c r="G71" s="18" t="inlineStr">
+        <is>
+          <t>① 가이드의 교내 보유 약제 살충제를 기준 축으로 삼음 — 학교가 실제로 쓸 확률이 가장 높은 제품이라서</t>
+        </is>
+      </c>
+      <c r="H71" s="19" t="n"/>
+    </row>
+    <row r="72" ht="34" customHeight="1">
+      <c r="A72" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="B72" s="18" t="inlineStr">
+        <is>
+          <t>PART 4. 혼용 가능 조합</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="n"/>
+      <c r="G72" s="18" t="inlineStr">
+        <is>
+          <t>② 제조사 1차 자료(공식 혼용정보 도구)에 “혼용가능(○)”로 명시된 조합만 — 추정이나 일반론은 배제</t>
+        </is>
+      </c>
+      <c r="H72" s="19" t="n"/>
+    </row>
+    <row r="73" ht="34" customHeight="1">
+      <c r="A73" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="B73" s="18" t="inlineStr">
+        <is>
+          <t>PART 4. 혼용 가능 조합</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="n"/>
+      <c r="G73" s="18" t="inlineStr">
+        <is>
+          <t>③ 궁합이 확인된 살균제가 이 가이드에 이미 나오는 제품일 때만 우선 표기 — 가이드 밖 제품과의 궁합은 실용성이 낮음</t>
+        </is>
+      </c>
+      <c r="H73" s="19" t="n"/>
+    </row>
+    <row r="74" ht="34" customHeight="1">
+      <c r="A74" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="B74" s="18" t="inlineStr">
+        <is>
+          <t>PART 4. 혼용 가능 조합</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="n"/>
+      <c r="G74" s="18" t="inlineStr">
+        <is>
+          <t>④ 못 찾은 건 억지로 채우지 않고 “미확인”으로 명시 (버픽스·무름반점뚝·강철비)</t>
+        </is>
+      </c>
+      <c r="H74" s="19" t="n"/>
+    </row>
+    <row r="75" ht="49" customHeight="1">
+      <c r="A75" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="B75" s="18" t="inlineStr">
+        <is>
+          <t>PART 4. 혼용 가능 조합</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="n"/>
+      <c r="G75" s="18" t="inlineStr">
+        <is>
+          <t>경농 혼용안내(knco.co.kr, 고추 기준)에서 학교 최우선 살충제 모스피란(아세타미프리드)을 조회한 결과, 아래 살균제와는 동시 살포(탱크믹스)가 가능하다고 나온다. 전부 이 가이드에 이미 나오는 제품들이다.</t>
+        </is>
+      </c>
+      <c r="H75" s="19" t="n"/>
+    </row>
+    <row r="76" ht="79" customHeight="1">
+      <c r="A76" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="B76" s="18" t="inlineStr">
+        <is>
+          <t>PART 4. 혼용 가능 조합</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="inlineStr">
+        <is>
+          <t>확인된 조합</t>
+        </is>
+      </c>
+      <c r="G76" s="18" t="inlineStr">
+        <is>
+          <t>위 5개는 모두 경농 제품이라 같은 회사 조회 결과 안에서 확인이 된 것이다. 스포르곤·코니도·타스타·강철비·쏘버린처럼 다른 회사(팜한농·바이엘·신젠타 등) 제품은 이 방식으로는 조회되지 않는다. 회사가 다르면 각 제조사 홈페이지 혼용정보나 고객센터로 직접 확인해야 하고, 확인 안 된 조합은 섞지 않는 게 원칙이다.</t>
+        </is>
+      </c>
+      <c r="H76" s="19" t="n"/>
+    </row>
+    <row r="77" ht="49" customHeight="1">
+      <c r="A77" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="B77" s="18" t="inlineStr">
+        <is>
+          <t>PART 4. 혼용 가능 조합</t>
+        </is>
+      </c>
+      <c r="C77" s="18" t="inlineStr">
+        <is>
+          <t>확인된 조합</t>
+        </is>
+      </c>
+      <c r="G77" s="18" t="inlineStr">
+        <is>
+          <t>제조사별 혼용정보 조회처: 경농 knco.co.kr/product/product_09 · 팜한농 farmhannong.com/kor/product/mix-info · 한국삼공 30agro.co.kr · 신젠타코리아 syngenta.co.kr</t>
+        </is>
+      </c>
+      <c r="H77" s="19" t="n"/>
+    </row>
+    <row r="78" ht="19" customHeight="1">
+      <c r="A78" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="B78" s="18" t="inlineStr">
+        <is>
+          <t>PART 4. 혼용 가능 조합</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="inlineStr">
+        <is>
+          <t>확인된 조합</t>
+        </is>
+      </c>
+      <c r="G78" s="18" t="inlineStr">
+        <is>
+          <t>조회일 2026-09-18</t>
+        </is>
+      </c>
+      <c r="H78" s="19" t="n">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="79" ht="49" customHeight="1">
+      <c r="A79" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="B79" s="18" t="inlineStr">
+        <is>
+          <t>PART 4. 혼용 가능 조합</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="inlineStr">
+        <is>
+          <t>바이엘(코니도·타스타) 공식 혼용정보</t>
+        </is>
+      </c>
+      <c r="G79" s="18" t="inlineStr">
+        <is>
+          <t>팜한농 혼용정보(farmhannong.com, 고추 기준) 조회 결과. 코니도는 살균제 벨쿠트와 짝이 맞고, 타스타는 고추에서 같이 쓸 살균제가 공식적으로 하나도 없다.</t>
+        </is>
+      </c>
+      <c r="H79" s="19" t="n"/>
+    </row>
+    <row r="80" ht="79" customHeight="1">
+      <c r="A80" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="B80" s="18" t="inlineStr">
+        <is>
+          <t>PART 4. 혼용 가능 조합</t>
+        </is>
+      </c>
+      <c r="C80" s="18" t="inlineStr">
+        <is>
+          <t>바이엘(코니도·타스타) 공식 혼용정보</t>
+        </is>
+      </c>
+      <c r="G80" s="18" t="inlineStr">
+        <is>
+          <t>스포르곤(팜한농)은 이 표에서 바이고·시반토·신기록-D 같은 다른 바이엘 살충제와는 짝이 맞지만, 가이드가 쓰는 모스피란·코니도·타스타 중 누구와도 짝으로 나오지 않는다. 쏘버린(팜한농, 카보설판)은 정식할 때 흙에 뿌리는 입제라 이 혼용정보표 자체에 없다 — 원래 스프레이통에 섞어 쓰는 제품이 아니다.</t>
+        </is>
+      </c>
+      <c r="H80" s="19" t="n"/>
+    </row>
+    <row r="81" ht="49" customHeight="1">
+      <c r="A81" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="B81" s="18" t="inlineStr">
+        <is>
+          <t>PART 4. 혼용 가능 조합</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="inlineStr">
+        <is>
+          <t>바이엘(코니도·타스타) 공식 혼용정보</t>
+        </is>
+      </c>
+      <c r="G81" s="18" t="inlineStr">
+        <is>
+          <t>버픽스(동방아그로), 무름반점뚝(대유), 강철비(인바이오)는 제조사는 확인했지만 온라인에 공개된 혼용정보 도구가 없어 짝을 못 찾았다. 이 세 개는 쓰기 전에 제조사 고객센터에 직접 물어봐야 한다.</t>
+        </is>
+      </c>
+      <c r="H81" s="19" t="n"/>
+    </row>
+    <row r="82" ht="34" customHeight="1">
+      <c r="A82" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="B82" s="18" t="inlineStr">
+        <is>
+          <t>PART 4. 혼용 가능 조합</t>
+        </is>
+      </c>
+      <c r="C82" s="18" t="inlineStr">
+        <is>
+          <t>바이엘(코니도·타스타) 공식 혼용정보</t>
+        </is>
+      </c>
+      <c r="G82" s="18" t="inlineStr">
+        <is>
+          <t>출처: farmhannong.com/kor/product/mix-info (바이엘 혼용기술정보 2025), 조회일 2026-09-18</t>
+        </is>
+      </c>
+      <c r="H82" s="19" t="n">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="83" ht="49" customHeight="1">
+      <c r="A83" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="B83" s="18" t="inlineStr">
+        <is>
+          <t>PART 4. 혼용 가능 조합</t>
+        </is>
+      </c>
+      <c r="C83" s="18" t="inlineStr">
+        <is>
+          <t>나머지 3개(버픽스·무름반점뚝·강철비) 끝까지 확인한 결과</t>
+        </is>
+      </c>
+      <c r="G83" s="18" t="inlineStr">
+        <is>
+          <t>제조사를 알아낸 뒤 각 회사 홈페이지의 혼용정보를 끝까지 뒤졌다. 결과는 아래와 같다 — 도구가 없어서 못 찾은 게 아니라, 도구는 있는데 그 안에 이 제품 자체가 없는 경우가 대부분이다.</t>
+        </is>
+      </c>
+      <c r="H83" s="19" t="n"/>
+    </row>
+    <row r="84" ht="64" customHeight="1">
+      <c r="A84" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="B84" s="18" t="inlineStr">
+        <is>
+          <t>PART 4. 혼용 가능 조합</t>
+        </is>
+      </c>
+      <c r="C84" s="18" t="inlineStr">
+        <is>
+          <t>나머지 3개(버픽스·무름반점뚝·강철비) 끝까지 확인한 결과</t>
+        </is>
+      </c>
+      <c r="G84" s="18" t="inlineStr">
+        <is>
+          <t>셋 다 온라인에 공개된 자료로는 답이 안 나온다는 뜻이다. 이 이상은 제조사 고객센터에 직접 전화해서 "이 제품, 저 살균제/살충제랑 섞어도 되나요"라고 물어보는 수밖에 없다 — 동방아그로 1644-7337 · 대유 · 인바이오 031-477-6011.</t>
+        </is>
+      </c>
+      <c r="H84" s="19" t="n"/>
+    </row>
+    <row r="85" ht="49" customHeight="1">
+      <c r="A85" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="B85" s="18" t="inlineStr">
+        <is>
+          <t>PART 4. 혼용 가능 조합</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="inlineStr">
+        <is>
+          <t>나머지 3개(버픽스·무름반점뚝·강철비) 끝까지 확인한 결과</t>
+        </is>
+      </c>
+      <c r="G85" s="18" t="inlineStr">
+        <is>
+          <t>확인 경로: dongbangagro.co.kr/product_combined.php · dae-yu.co.kr · enbio.co.kr(혼용정보 게시판, 살균제·살충제 혼용가부표 전체), 조회일 2026-09-18</t>
+        </is>
+      </c>
+      <c r="H85" s="19" t="n">
+        <v>46283</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="55">
+    <mergeCell ref="C52:F52"/>
+    <mergeCell ref="C70:F70"/>
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="C82:F82"/>
+    <mergeCell ref="C72:F72"/>
+    <mergeCell ref="C67:F67"/>
+    <mergeCell ref="C81:F81"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="C57:F57"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="C66:F66"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="C53:F53"/>
+    <mergeCell ref="C78:F78"/>
+    <mergeCell ref="C69:F69"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="C77:F77"/>
+    <mergeCell ref="C83:F83"/>
+    <mergeCell ref="B49:G49"/>
+    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="C68:F68"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="C58:F58"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="C74:F74"/>
+    <mergeCell ref="C64:F64"/>
+    <mergeCell ref="C79:F79"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="C73:F73"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="C63:F63"/>
+    <mergeCell ref="C65:F65"/>
+    <mergeCell ref="C85:F85"/>
+    <mergeCell ref="C55:F55"/>
+    <mergeCell ref="C84:F84"/>
+    <mergeCell ref="B47:G47"/>
+    <mergeCell ref="C80:F80"/>
+    <mergeCell ref="C75:F75"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="C56:F56"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="C59:F59"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="B48:G48"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="C76:F76"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>